--- a/data/k-props/2026-08-22.xlsx
+++ b/data/k-props/2026-08-22.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="94">
   <si>
     <t>date</t>
   </si>
@@ -142,154 +142,157 @@
     <t>Traditional starter</t>
   </si>
   <si>
+    <t>lineup_unweighted_30d_posted</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>&gt;=7</t>
+  </si>
+  <si>
+    <t>Ryan Weathers</t>
+  </si>
+  <si>
     <t>lineup_unweighted_30d_projected_regulars</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
-    <t>&gt;=7</t>
-  </si>
-  <si>
-    <t>Ryan Weathers</t>
-  </si>
-  <si>
     <t>&lt;6</t>
   </si>
   <si>
+    <t>Martín Pérez</t>
+  </si>
+  <si>
+    <t>Atlanta Braves @ Milwaukee Brewers</t>
+  </si>
+  <si>
+    <t>Logan Henderson</t>
+  </si>
+  <si>
+    <t>6-7</t>
+  </si>
+  <si>
+    <t>Jake Irvin</t>
+  </si>
+  <si>
+    <t>Washington Nationals @ Miami Marlins</t>
+  </si>
+  <si>
+    <t>Eury Pérez</t>
+  </si>
+  <si>
+    <t>Andrew Painter</t>
+  </si>
+  <si>
+    <t>St. Louis Cardinals @ Philadelphia Phillies</t>
+  </si>
+  <si>
+    <t>Shane McClanahan</t>
+  </si>
+  <si>
+    <t>Tampa Bay Rays @ Baltimore Orioles</t>
+  </si>
+  <si>
+    <t>Brandon Young</t>
+  </si>
+  <si>
+    <t>Ryan Johnson</t>
+  </si>
+  <si>
+    <t>Los Angeles Angels @ Texas Rangers</t>
+  </si>
+  <si>
+    <t>Cody Bradford</t>
+  </si>
+  <si>
+    <t>Jacob Lopez</t>
+  </si>
+  <si>
+    <t>Athletics @ Houston Astros</t>
+  </si>
+  <si>
+    <t>Hunter Brown</t>
+  </si>
+  <si>
+    <t>Christian Scott</t>
+  </si>
+  <si>
+    <t>New York Mets @ Chicago White Sox</t>
+  </si>
+  <si>
+    <t>Luis Castillo</t>
+  </si>
+  <si>
+    <t>Drew Anderson</t>
+  </si>
+  <si>
+    <t>Detroit Tigers @ Kansas City Royals</t>
+  </si>
+  <si>
+    <t>Limited starter</t>
+  </si>
+  <si>
+    <t>Michael Wacha</t>
+  </si>
+  <si>
+    <t>Jared Jones</t>
+  </si>
+  <si>
+    <t>Pittsburgh Pirates @ Los Angeles Dodgers</t>
+  </si>
+  <si>
+    <t>Tarik Skubal</t>
+  </si>
+  <si>
+    <t>David Peterson</t>
+  </si>
+  <si>
+    <t>Chicago Cubs @ Seattle Mariners</t>
+  </si>
+  <si>
+    <t>Blade Tidwell</t>
+  </si>
+  <si>
+    <t>San Francisco Giants @ Boston Red Sox</t>
+  </si>
+  <si>
+    <t>Patrick Sandoval</t>
+  </si>
+  <si>
+    <t>Rhett Lowder</t>
+  </si>
+  <si>
+    <t>Cincinnati Reds @ Arizona Diamondbacks</t>
+  </si>
+  <si>
+    <t>Michael Soroka</t>
+  </si>
+  <si>
+    <t>Tanner Bibee</t>
+  </si>
+  <si>
+    <t>Cleveland Guardians @ Colorado Rockies</t>
+  </si>
+  <si>
+    <t>Gabriel Hughes</t>
+  </si>
+  <si>
+    <t>Dean Kremer</t>
+  </si>
+  <si>
+    <t>Minnesota Twins @ San Diego Padres</t>
+  </si>
+  <si>
+    <t>Casey Mize</t>
+  </si>
+  <si>
     <t>Martin Perez</t>
   </si>
   <si>
-    <t>Atlanta Braves @ Milwaukee Brewers</t>
-  </si>
-  <si>
-    <t>Logan Henderson</t>
-  </si>
-  <si>
-    <t>6-7</t>
-  </si>
-  <si>
     <t>Eury Perez</t>
   </si>
   <si>
-    <t>Washington Nationals @ Miami Marlins</t>
-  </si>
-  <si>
-    <t>Jake Irvin</t>
-  </si>
-  <si>
     <t>Quinn Mathews</t>
-  </si>
-  <si>
-    <t>St. Louis Cardinals @ Philadelphia Phillies</t>
-  </si>
-  <si>
-    <t>Andrew Painter</t>
-  </si>
-  <si>
-    <t>Shane McClanahan</t>
-  </si>
-  <si>
-    <t>Tampa Bay Rays @ Baltimore Orioles</t>
-  </si>
-  <si>
-    <t>Brandon Young</t>
-  </si>
-  <si>
-    <t>Cody Bradford</t>
-  </si>
-  <si>
-    <t>Los Angeles Angels @ Texas Rangers</t>
-  </si>
-  <si>
-    <t>Ryan Johnson</t>
-  </si>
-  <si>
-    <t>Christian Scott</t>
-  </si>
-  <si>
-    <t>New York Mets @ Chicago White Sox</t>
-  </si>
-  <si>
-    <t>Luis Castillo</t>
-  </si>
-  <si>
-    <t>Hunter Brown</t>
-  </si>
-  <si>
-    <t>Athletics @ Houston Astros</t>
-  </si>
-  <si>
-    <t>Jacob Lopez</t>
-  </si>
-  <si>
-    <t>Patrick Sandoval</t>
-  </si>
-  <si>
-    <t>San Francisco Giants @ Boston Red Sox</t>
-  </si>
-  <si>
-    <t>Blade Tidwell</t>
-  </si>
-  <si>
-    <t>David Peterson</t>
-  </si>
-  <si>
-    <t>Chicago Cubs @ Seattle Mariners</t>
-  </si>
-  <si>
-    <t>Drew Anderson</t>
-  </si>
-  <si>
-    <t>Detroit Tigers @ Kansas City Royals</t>
-  </si>
-  <si>
-    <t>Limited starter</t>
-  </si>
-  <si>
-    <t>Michael Wacha</t>
-  </si>
-  <si>
-    <t>Jared Jones</t>
-  </si>
-  <si>
-    <t>Pittsburgh Pirates @ Los Angeles Dodgers</t>
-  </si>
-  <si>
-    <t>Tarik Skubal</t>
-  </si>
-  <si>
-    <t>Michael Soroka</t>
-  </si>
-  <si>
-    <t>Cincinnati Reds @ Arizona Diamondbacks</t>
-  </si>
-  <si>
-    <t>Rhett Lowder</t>
-  </si>
-  <si>
-    <t>Gabriel Hughes</t>
-  </si>
-  <si>
-    <t>Cleveland Guardians @ Colorado Rockies</t>
-  </si>
-  <si>
-    <t>Tanner Bibee</t>
-  </si>
-  <si>
-    <t>Casey Mize</t>
-  </si>
-  <si>
-    <t>Minnesota Twins @ San Diego Padres</t>
-  </si>
-  <si>
-    <t>Dean Kremer</t>
-  </si>
-  <si>
-    <t>Martín Pérez</t>
-  </si>
-  <si>
-    <t>Eury Pérez</t>
   </si>
 </sst>
 </file>
@@ -854,10 +857,10 @@
         <v>43</v>
       </c>
       <c r="T2">
-        <v>0.2724</v>
+        <v>0.2744</v>
       </c>
       <c r="U2">
-        <v>0.271</v>
+        <v>0.2725</v>
       </c>
       <c r="V2">
         <v>9</v>
@@ -866,10 +869,10 @@
         <v>0.2473</v>
       </c>
       <c r="X2">
-        <v>0.2203</v>
+        <v>0.2204</v>
       </c>
       <c r="Y2">
-        <v>0.9927</v>
+        <v>1.0348</v>
       </c>
       <c r="AA2" t="s">
         <v>44</v>
@@ -878,7 +881,7 @@
         <v>44</v>
       </c>
       <c r="AD2">
-        <v>10.75</v>
+        <v>11.28</v>
       </c>
       <c r="AE2" t="s">
         <v>45</v>
@@ -887,13 +890,13 @@
         <v>0.3641</v>
       </c>
       <c r="AG2">
-        <v>1.2366</v>
+        <v>1.2453</v>
       </c>
       <c r="AH2">
         <v>0</v>
       </c>
       <c r="AM2">
-        <v>10.75</v>
+        <v>11.28</v>
       </c>
     </row>
     <row r="3" spans="1:39" x14ac:dyDescent="0.25">
@@ -952,7 +955,7 @@
         <v>0.373</v>
       </c>
       <c r="S3" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="T3">
         <v>0.2041</v>
@@ -967,7 +970,7 @@
         <v>0.2108</v>
       </c>
       <c r="X3">
-        <v>0.2203</v>
+        <v>0.2204</v>
       </c>
       <c r="Y3">
         <v>0.9765</v>
@@ -979,22 +982,22 @@
         <v>44</v>
       </c>
       <c r="AD3">
-        <v>4.94</v>
+        <v>4.93</v>
       </c>
       <c r="AE3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="AF3">
         <v>0.2377</v>
       </c>
       <c r="AG3">
-        <v>0.9262</v>
+        <v>0.9259</v>
       </c>
       <c r="AH3">
         <v>0</v>
       </c>
       <c r="AM3">
-        <v>4.94</v>
+        <v>4.93</v>
       </c>
     </row>
     <row r="4" spans="1:39" x14ac:dyDescent="0.25">
@@ -1002,43 +1005,91 @@
         <v>39</v>
       </c>
       <c r="B4" t="s">
+        <v>49</v>
+      </c>
+      <c r="F4" t="s">
+        <v>50</v>
+      </c>
+      <c r="G4">
+        <v>823743</v>
+      </c>
+      <c r="H4" t="s">
+        <v>42</v>
+      </c>
+      <c r="I4">
+        <v>5.1</v>
+      </c>
+      <c r="J4" t="b">
+        <v>0</v>
+      </c>
+      <c r="K4" t="b">
+        <v>0</v>
+      </c>
+      <c r="L4">
+        <v>0</v>
+      </c>
+      <c r="M4">
+        <v>0.1824</v>
+      </c>
+      <c r="N4">
+        <v>5</v>
+      </c>
+      <c r="O4">
+        <v>106</v>
+      </c>
+      <c r="P4">
+        <v>4.09</v>
+      </c>
+      <c r="Q4">
+        <v>0.1698</v>
+      </c>
+      <c r="R4">
+        <v>0.346</v>
+      </c>
+      <c r="S4" t="s">
+        <v>47</v>
+      </c>
+      <c r="T4">
+        <v>0.2293</v>
+      </c>
+      <c r="U4">
+        <v>0.2269</v>
+      </c>
+      <c r="V4">
+        <v>8</v>
+      </c>
+      <c r="W4">
+        <v>0.2223</v>
+      </c>
+      <c r="X4">
+        <v>0.2204</v>
+      </c>
+      <c r="Y4">
+        <v>1.0155</v>
+      </c>
+      <c r="AA4" t="s">
+        <v>44</v>
+      </c>
+      <c r="AC4" t="s">
+        <v>44</v>
+      </c>
+      <c r="AD4">
+        <v>3.92</v>
+      </c>
+      <c r="AE4" t="s">
         <v>48</v>
       </c>
-      <c r="C4">
-        <v>3.5</v>
-      </c>
-      <c r="D4">
-        <v>-111</v>
-      </c>
-      <c r="E4">
-        <v>-110</v>
-      </c>
-      <c r="F4" t="s">
-        <v>49</v>
-      </c>
-      <c r="G4" t="s">
-        <v>44</v>
-      </c>
-      <c r="H4" t="s">
-        <v>44</v>
-      </c>
-      <c r="L4">
-        <v>6</v>
-      </c>
-      <c r="S4" t="s">
-        <v>44</v>
-      </c>
-      <c r="V4" t="s">
-        <v>44</v>
-      </c>
-      <c r="AA4" t="s">
-        <v>44</v>
-      </c>
-      <c r="AC4" t="s">
-        <v>44</v>
-      </c>
-      <c r="AE4" t="s">
-        <v>44</v>
+      <c r="AF4">
+        <v>0.1781</v>
+      </c>
+      <c r="AG4">
+        <v>1.0406</v>
+      </c>
+      <c r="AH4">
+        <v>0</v>
+      </c>
+      <c r="AM4">
+        <v>3.92</v>
       </c>
     </row>
     <row r="5" spans="1:39" x14ac:dyDescent="0.25">
@@ -1046,7 +1097,7 @@
         <v>39</v>
       </c>
       <c r="B5" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C5">
         <v>6.5</v>
@@ -1058,7 +1109,7 @@
         <v>-112</v>
       </c>
       <c r="F5" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G5">
         <v>823743</v>
@@ -1097,7 +1148,7 @@
         <v>0.359</v>
       </c>
       <c r="S5" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="T5">
         <v>0.2437</v>
@@ -1112,7 +1163,7 @@
         <v>0.2201</v>
       </c>
       <c r="X5">
-        <v>0.2203</v>
+        <v>0.2204</v>
       </c>
       <c r="Y5">
         <v>0.9913</v>
@@ -1127,13 +1178,13 @@
         <v>6.99</v>
       </c>
       <c r="AE5" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="AF5">
         <v>0.3189</v>
       </c>
       <c r="AG5">
-        <v>1.1062</v>
+        <v>1.1059</v>
       </c>
       <c r="AH5">
         <v>0.17</v>
@@ -1147,34 +1198,76 @@
         <v>39</v>
       </c>
       <c r="B6" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C6">
-        <v>6.5</v>
+        <v>4.5</v>
       </c>
       <c r="D6">
-        <v>110</v>
+        <v>-102</v>
       </c>
       <c r="E6">
-        <v>-132</v>
+        <v>-110</v>
       </c>
       <c r="F6" t="s">
-        <v>53</v>
-      </c>
-      <c r="G6" t="s">
-        <v>44</v>
+        <v>54</v>
+      </c>
+      <c r="G6">
+        <v>823831</v>
       </c>
       <c r="H6" t="s">
-        <v>44</v>
+        <v>42</v>
+      </c>
+      <c r="I6">
+        <v>4.8</v>
+      </c>
+      <c r="J6" t="b">
+        <v>0</v>
+      </c>
+      <c r="K6" t="b">
+        <v>0</v>
       </c>
       <c r="L6">
         <v>6</v>
       </c>
+      <c r="M6">
+        <v>0.23</v>
+      </c>
+      <c r="N6">
+        <v>5</v>
+      </c>
+      <c r="O6">
+        <v>101</v>
+      </c>
+      <c r="P6">
+        <v>4.39</v>
+      </c>
+      <c r="Q6">
+        <v>0.2079</v>
+      </c>
+      <c r="R6">
+        <v>0.336</v>
+      </c>
       <c r="S6" t="s">
-        <v>44</v>
-      </c>
-      <c r="V6" t="s">
-        <v>44</v>
+        <v>47</v>
+      </c>
+      <c r="T6">
+        <v>0.2194</v>
+      </c>
+      <c r="U6">
+        <v>0.2079</v>
+      </c>
+      <c r="V6">
+        <v>9</v>
+      </c>
+      <c r="W6">
+        <v>0.2121</v>
+      </c>
+      <c r="X6">
+        <v>0.2204</v>
+      </c>
+      <c r="Y6">
+        <v>0.9726</v>
       </c>
       <c r="AA6" t="s">
         <v>44</v>
@@ -1182,8 +1275,23 @@
       <c r="AC6" t="s">
         <v>44</v>
       </c>
+      <c r="AD6">
+        <v>4.5</v>
+      </c>
       <c r="AE6" t="s">
-        <v>44</v>
+        <v>48</v>
+      </c>
+      <c r="AF6">
+        <v>0.2226</v>
+      </c>
+      <c r="AG6">
+        <v>0.9955</v>
+      </c>
+      <c r="AH6">
+        <v>0</v>
+      </c>
+      <c r="AM6">
+        <v>4.5</v>
       </c>
     </row>
     <row r="7" spans="1:39" x14ac:dyDescent="0.25">
@@ -1191,19 +1299,10 @@
         <v>39</v>
       </c>
       <c r="B7" t="s">
+        <v>55</v>
+      </c>
+      <c r="F7" t="s">
         <v>54</v>
-      </c>
-      <c r="C7">
-        <v>4.5</v>
-      </c>
-      <c r="D7">
-        <v>-102</v>
-      </c>
-      <c r="E7">
-        <v>-110</v>
-      </c>
-      <c r="F7" t="s">
-        <v>53</v>
       </c>
       <c r="G7">
         <v>823831</v>
@@ -1212,7 +1311,7 @@
         <v>42</v>
       </c>
       <c r="I7">
-        <v>4.8</v>
+        <v>5.6</v>
       </c>
       <c r="J7" t="b">
         <v>0</v>
@@ -1221,46 +1320,46 @@
         <v>0</v>
       </c>
       <c r="L7">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M7">
-        <v>0.23</v>
+        <v>0.2692</v>
       </c>
       <c r="N7">
         <v>5</v>
       </c>
       <c r="O7">
-        <v>101</v>
+        <v>123</v>
       </c>
       <c r="P7">
-        <v>4.39</v>
+        <v>4.03</v>
       </c>
       <c r="Q7">
-        <v>0.2079</v>
+        <v>0.2358</v>
       </c>
       <c r="R7">
-        <v>0.336</v>
+        <v>0.381</v>
       </c>
       <c r="S7" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="T7">
-        <v>0.2194</v>
+        <v>0.2359</v>
       </c>
       <c r="U7">
-        <v>0.2079</v>
+        <v>0.2361</v>
       </c>
       <c r="V7">
         <v>9</v>
       </c>
       <c r="W7">
-        <v>0.2121</v>
+        <v>0.2076</v>
       </c>
       <c r="X7">
-        <v>0.2203</v>
+        <v>0.2204</v>
       </c>
       <c r="Y7">
-        <v>0.9726</v>
+        <v>1.017</v>
       </c>
       <c r="AA7" t="s">
         <v>44</v>
@@ -1269,22 +1368,22 @@
         <v>44</v>
       </c>
       <c r="AD7">
-        <v>4.5</v>
+        <v>6.27</v>
       </c>
       <c r="AE7" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="AF7">
-        <v>0.2226</v>
+        <v>0.2565</v>
       </c>
       <c r="AG7">
-        <v>0.9958</v>
+        <v>1.0705</v>
       </c>
       <c r="AH7">
-        <v>0</v>
+        <v>0.17</v>
       </c>
       <c r="AM7">
-        <v>4.5</v>
+        <v>6.44</v>
       </c>
     </row>
     <row r="8" spans="1:39" x14ac:dyDescent="0.25">
@@ -1292,34 +1391,76 @@
         <v>39</v>
       </c>
       <c r="B8" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C8">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="D8">
-        <v>105</v>
+        <v>-154</v>
       </c>
       <c r="E8">
-        <v>108</v>
+        <v>125</v>
       </c>
       <c r="F8" t="s">
-        <v>56</v>
-      </c>
-      <c r="G8" t="s">
-        <v>44</v>
+        <v>57</v>
+      </c>
+      <c r="G8">
+        <v>823422</v>
       </c>
       <c r="H8" t="s">
-        <v>44</v>
+        <v>42</v>
+      </c>
+      <c r="I8">
+        <v>4.7</v>
+      </c>
+      <c r="J8" t="b">
+        <v>0</v>
+      </c>
+      <c r="K8" t="b">
+        <v>0</v>
       </c>
       <c r="L8">
         <v>6</v>
       </c>
+      <c r="M8">
+        <v>0.1854</v>
+      </c>
+      <c r="N8">
+        <v>5</v>
+      </c>
+      <c r="O8">
+        <v>98</v>
+      </c>
+      <c r="P8">
+        <v>4.49</v>
+      </c>
+      <c r="Q8">
+        <v>0.2143</v>
+      </c>
+      <c r="R8">
+        <v>0.329</v>
+      </c>
       <c r="S8" t="s">
-        <v>44</v>
-      </c>
-      <c r="V8" t="s">
-        <v>44</v>
+        <v>47</v>
+      </c>
+      <c r="T8">
+        <v>0.1971</v>
+      </c>
+      <c r="U8">
+        <v>0.1985</v>
+      </c>
+      <c r="V8">
+        <v>8</v>
+      </c>
+      <c r="W8">
+        <v>0.2137</v>
+      </c>
+      <c r="X8">
+        <v>0.2204</v>
+      </c>
+      <c r="Y8">
+        <v>0.9561</v>
       </c>
       <c r="AA8" t="s">
         <v>44</v>
@@ -1327,8 +1468,23 @@
       <c r="AC8" t="s">
         <v>44</v>
       </c>
+      <c r="AD8">
+        <v>3.52</v>
+      </c>
       <c r="AE8" t="s">
-        <v>44</v>
+        <v>48</v>
+      </c>
+      <c r="AF8">
+        <v>0.1949</v>
+      </c>
+      <c r="AG8">
+        <v>0.8944</v>
+      </c>
+      <c r="AH8">
+        <v>0</v>
+      </c>
+      <c r="AM8">
+        <v>3.52</v>
       </c>
     </row>
     <row r="9" spans="1:39" x14ac:dyDescent="0.25">
@@ -1336,28 +1492,28 @@
         <v>39</v>
       </c>
       <c r="B9" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C9">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="D9">
-        <v>-154</v>
+        <v>103</v>
       </c>
       <c r="E9">
-        <v>125</v>
+        <v>-125</v>
       </c>
       <c r="F9" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="G9">
-        <v>823422</v>
+        <v>824798</v>
       </c>
       <c r="H9" t="s">
         <v>42</v>
       </c>
       <c r="I9">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="J9" t="b">
         <v>0</v>
@@ -1366,46 +1522,46 @@
         <v>0</v>
       </c>
       <c r="L9">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M9">
-        <v>0.1854</v>
+        <v>0.2222</v>
       </c>
       <c r="N9">
         <v>5</v>
       </c>
       <c r="O9">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="P9">
-        <v>4.49</v>
+        <v>4.13</v>
       </c>
       <c r="Q9">
-        <v>0.2143</v>
+        <v>0.1868</v>
       </c>
       <c r="R9">
-        <v>0.329</v>
+        <v>0.313</v>
       </c>
       <c r="S9" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="T9">
-        <v>0.1971</v>
+        <v>0.2544</v>
       </c>
       <c r="U9">
-        <v>0.1985</v>
+        <v>0.2401</v>
       </c>
       <c r="V9">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W9">
-        <v>0.2137</v>
+        <v>0.2573</v>
       </c>
       <c r="X9">
-        <v>0.2203</v>
+        <v>0.2204</v>
       </c>
       <c r="Y9">
-        <v>0.9561</v>
+        <v>1.0201</v>
       </c>
       <c r="AA9" t="s">
         <v>44</v>
@@ -1414,22 +1570,22 @@
         <v>44</v>
       </c>
       <c r="AD9">
-        <v>3.52</v>
+        <v>5.01</v>
       </c>
       <c r="AE9" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="AF9">
-        <v>0.1949</v>
+        <v>0.2111</v>
       </c>
       <c r="AG9">
-        <v>0.8946</v>
+        <v>1.1546</v>
       </c>
       <c r="AH9">
         <v>0</v>
       </c>
       <c r="AM9">
-        <v>3.52</v>
+        <v>5.01</v>
       </c>
     </row>
     <row r="10" spans="1:39" x14ac:dyDescent="0.25">
@@ -1437,16 +1593,16 @@
         <v>39</v>
       </c>
       <c r="B10" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C10">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="D10">
-        <v>103</v>
+        <v>-125</v>
       </c>
       <c r="E10">
-        <v>-125</v>
+        <v>110</v>
       </c>
       <c r="F10" t="s">
         <v>59</v>
@@ -1458,7 +1614,7 @@
         <v>42</v>
       </c>
       <c r="I10">
-        <v>4.9</v>
+        <v>5.6</v>
       </c>
       <c r="J10" t="b">
         <v>0</v>
@@ -1470,43 +1626,43 @@
         <v>5</v>
       </c>
       <c r="M10">
-        <v>0.2222</v>
+        <v>0.1893</v>
       </c>
       <c r="N10">
         <v>5</v>
       </c>
       <c r="O10">
-        <v>91</v>
+        <v>117</v>
       </c>
       <c r="P10">
-        <v>4.13</v>
+        <v>4.31</v>
       </c>
       <c r="Q10">
-        <v>0.1868</v>
+        <v>0.188</v>
       </c>
       <c r="R10">
-        <v>0.313</v>
+        <v>0.369</v>
       </c>
       <c r="S10" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="T10">
-        <v>0.2544</v>
+        <v>0.1734</v>
       </c>
       <c r="U10">
-        <v>0.2401</v>
+        <v>0.1732</v>
       </c>
       <c r="V10">
         <v>9</v>
       </c>
       <c r="W10">
-        <v>0.2573</v>
+        <v>0.189</v>
       </c>
       <c r="X10">
-        <v>0.2203</v>
+        <v>0.2204</v>
       </c>
       <c r="Y10">
-        <v>1.0201</v>
+        <v>0.9097</v>
       </c>
       <c r="AA10" t="s">
         <v>44</v>
@@ -1515,22 +1671,22 @@
         <v>44</v>
       </c>
       <c r="AD10">
-        <v>5.01</v>
+        <v>3.26</v>
       </c>
       <c r="AE10" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="AF10">
-        <v>0.2111</v>
+        <v>0.1889</v>
       </c>
       <c r="AG10">
-        <v>1.1549</v>
+        <v>0.7869</v>
       </c>
       <c r="AH10">
         <v>0</v>
       </c>
       <c r="AM10">
-        <v>5.01</v>
+        <v>3.26</v>
       </c>
     </row>
     <row r="11" spans="1:39" x14ac:dyDescent="0.25">
@@ -1538,28 +1694,28 @@
         <v>39</v>
       </c>
       <c r="B11" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C11">
         <v>3.5</v>
       </c>
       <c r="D11">
-        <v>-125</v>
+        <v>-143</v>
       </c>
       <c r="E11">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="F11" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="G11">
-        <v>824798</v>
+        <v>822858</v>
       </c>
       <c r="H11" t="s">
         <v>42</v>
       </c>
       <c r="I11">
-        <v>5.6</v>
+        <v>4.6</v>
       </c>
       <c r="J11" t="b">
         <v>0</v>
@@ -1571,43 +1727,43 @@
         <v>5</v>
       </c>
       <c r="M11">
-        <v>0.1893</v>
+        <v>0.1734</v>
       </c>
       <c r="N11">
         <v>5</v>
       </c>
       <c r="O11">
-        <v>117</v>
+        <v>102</v>
       </c>
       <c r="P11">
-        <v>4.31</v>
+        <v>4.49</v>
       </c>
       <c r="Q11">
-        <v>0.188</v>
+        <v>0.1667</v>
       </c>
       <c r="R11">
-        <v>0.369</v>
+        <v>0.338</v>
       </c>
       <c r="S11" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="T11">
-        <v>0.1734</v>
+        <v>0.2425</v>
       </c>
       <c r="U11">
-        <v>0.1732</v>
+        <v>0.2431</v>
       </c>
       <c r="V11">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W11">
-        <v>0.189</v>
+        <v>0.2245</v>
       </c>
       <c r="X11">
-        <v>0.2203</v>
+        <v>0.2204</v>
       </c>
       <c r="Y11">
-        <v>0.9097</v>
+        <v>1.0122</v>
       </c>
       <c r="AA11" t="s">
         <v>44</v>
@@ -1616,22 +1772,22 @@
         <v>44</v>
       </c>
       <c r="AD11">
-        <v>3.27</v>
+        <v>3.95</v>
       </c>
       <c r="AE11" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="AF11">
-        <v>0.1889</v>
+        <v>0.1711</v>
       </c>
       <c r="AG11">
-        <v>0.7871</v>
+        <v>1.1003</v>
       </c>
       <c r="AH11">
         <v>0</v>
       </c>
       <c r="AM11">
-        <v>3.27</v>
+        <v>3.95</v>
       </c>
     </row>
     <row r="12" spans="1:39" x14ac:dyDescent="0.25">
@@ -1639,7 +1795,7 @@
         <v>39</v>
       </c>
       <c r="B12" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C12">
         <v>4.5</v>
@@ -1690,7 +1846,7 @@
         <v>0.245</v>
       </c>
       <c r="S12" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="T12">
         <v>0.2715</v>
@@ -1705,7 +1861,7 @@
         <v>0.2562</v>
       </c>
       <c r="X12">
-        <v>0.2203</v>
+        <v>0.2204</v>
       </c>
       <c r="Y12">
         <v>1.0326</v>
@@ -1720,13 +1876,13 @@
         <v>4.24</v>
       </c>
       <c r="AE12" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="AF12">
         <v>0.1538</v>
       </c>
       <c r="AG12">
-        <v>1.2321</v>
+        <v>1.2318</v>
       </c>
       <c r="AH12">
         <v>0</v>
@@ -1740,28 +1896,28 @@
         <v>39</v>
       </c>
       <c r="B13" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C13">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="D13">
-        <v>-143</v>
+        <v>-113</v>
       </c>
       <c r="E13">
-        <v>120</v>
+        <v>-102</v>
       </c>
       <c r="F13" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="G13">
-        <v>822858</v>
+        <v>824151</v>
       </c>
       <c r="H13" t="s">
         <v>42</v>
       </c>
       <c r="I13">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="J13" t="b">
         <v>0</v>
@@ -1773,43 +1929,43 @@
         <v>5</v>
       </c>
       <c r="M13">
-        <v>0.1734</v>
+        <v>0.2045</v>
       </c>
       <c r="N13">
         <v>5</v>
       </c>
       <c r="O13">
-        <v>102</v>
+        <v>115</v>
       </c>
       <c r="P13">
-        <v>4.49</v>
+        <v>4.5</v>
       </c>
       <c r="Q13">
-        <v>0.1667</v>
+        <v>0.2783</v>
       </c>
       <c r="R13">
-        <v>0.338</v>
+        <v>0.365</v>
       </c>
       <c r="S13" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="T13">
-        <v>0.2425</v>
+        <v>0.2099</v>
       </c>
       <c r="U13">
-        <v>0.2431</v>
+        <v>0.2034</v>
       </c>
       <c r="V13">
         <v>8</v>
       </c>
       <c r="W13">
-        <v>0.2245</v>
+        <v>0.2052</v>
       </c>
       <c r="X13">
-        <v>0.2203</v>
+        <v>0.2204</v>
       </c>
       <c r="Y13">
-        <v>1.0122</v>
+        <v>0.9727</v>
       </c>
       <c r="AA13" t="s">
         <v>44</v>
@@ -1818,22 +1974,22 @@
         <v>44</v>
       </c>
       <c r="AD13">
-        <v>3.95</v>
+        <v>4.5</v>
       </c>
       <c r="AE13" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="AF13">
-        <v>0.1711</v>
+        <v>0.2315</v>
       </c>
       <c r="AG13">
-        <v>1.1006</v>
+        <v>0.9526</v>
       </c>
       <c r="AH13">
         <v>0</v>
       </c>
       <c r="AM13">
-        <v>3.95</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="14" spans="1:39" x14ac:dyDescent="0.25">
@@ -1841,28 +1997,28 @@
         <v>39</v>
       </c>
       <c r="B14" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C14">
         <v>6.5</v>
       </c>
       <c r="D14">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="E14">
-        <v>-154</v>
+        <v>-130</v>
       </c>
       <c r="F14" t="s">
         <v>65</v>
       </c>
       <c r="G14">
-        <v>824560</v>
+        <v>824151</v>
       </c>
       <c r="H14" t="s">
         <v>42</v>
       </c>
       <c r="I14">
-        <v>4.7</v>
+        <v>5.3</v>
       </c>
       <c r="J14" t="b">
         <v>0</v>
@@ -1874,7 +2030,7 @@
         <v>5</v>
       </c>
       <c r="M14">
-        <v>0.2861</v>
+        <v>0.2474</v>
       </c>
       <c r="N14">
         <v>5</v>
@@ -1883,34 +2039,34 @@
         <v>114</v>
       </c>
       <c r="P14">
-        <v>4.33</v>
+        <v>4.24</v>
       </c>
       <c r="Q14">
-        <v>0.2895</v>
+        <v>0.2544</v>
       </c>
       <c r="R14">
         <v>0.363</v>
       </c>
       <c r="S14" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="T14">
-        <v>0.2196</v>
+        <v>0.2489</v>
       </c>
       <c r="U14">
-        <v>0.2376</v>
+        <v>0.2157</v>
       </c>
       <c r="V14">
         <v>9</v>
       </c>
       <c r="W14">
-        <v>0.2358</v>
+        <v>0.2118</v>
       </c>
       <c r="X14">
-        <v>0.2203</v>
+        <v>0.2204</v>
       </c>
       <c r="Y14">
-        <v>1.04</v>
+        <v>1.0462</v>
       </c>
       <c r="AA14" t="s">
         <v>44</v>
@@ -1919,22 +2075,22 @@
         <v>44</v>
       </c>
       <c r="AD14">
-        <v>6.07</v>
+        <v>6.61</v>
       </c>
       <c r="AE14" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="AF14">
-        <v>0.2873</v>
+        <v>0.25</v>
       </c>
       <c r="AG14">
-        <v>0.9968</v>
+        <v>1.1293</v>
       </c>
       <c r="AH14">
         <v>0.17</v>
       </c>
       <c r="AM14">
-        <v>6.24</v>
+        <v>6.78</v>
       </c>
     </row>
     <row r="15" spans="1:39" x14ac:dyDescent="0.25">
@@ -1942,19 +2098,19 @@
         <v>39</v>
       </c>
       <c r="B15" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C15">
-        <v>4.5</v>
+        <v>6.5</v>
       </c>
       <c r="D15">
-        <v>-128</v>
+        <v>128</v>
       </c>
       <c r="E15">
-        <v>109</v>
+        <v>-154</v>
       </c>
       <c r="F15" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="G15">
         <v>824560</v>
@@ -1963,7 +2119,7 @@
         <v>42</v>
       </c>
       <c r="I15">
-        <v>5.2</v>
+        <v>4.7</v>
       </c>
       <c r="J15" t="b">
         <v>0</v>
@@ -1975,43 +2131,43 @@
         <v>5</v>
       </c>
       <c r="M15">
-        <v>0.2008</v>
+        <v>0.2861</v>
       </c>
       <c r="N15">
         <v>5</v>
       </c>
       <c r="O15">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="P15">
-        <v>4.4</v>
+        <v>4.33</v>
       </c>
       <c r="Q15">
-        <v>0.178</v>
+        <v>0.2895</v>
       </c>
       <c r="R15">
-        <v>0.371</v>
+        <v>0.363</v>
       </c>
       <c r="S15" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="T15">
-        <v>0.2182</v>
+        <v>0.2196</v>
       </c>
       <c r="U15">
-        <v>0.2388</v>
+        <v>0.2376</v>
       </c>
       <c r="V15">
         <v>9</v>
       </c>
       <c r="W15">
-        <v>0.2247</v>
+        <v>0.2358</v>
       </c>
       <c r="X15">
-        <v>0.2203</v>
+        <v>0.2204</v>
       </c>
       <c r="Y15">
-        <v>0.9823</v>
+        <v>1.04</v>
       </c>
       <c r="AA15" t="s">
         <v>44</v>
@@ -2020,22 +2176,22 @@
         <v>44</v>
       </c>
       <c r="AD15">
-        <v>4.29</v>
+        <v>6.07</v>
       </c>
       <c r="AE15" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="AF15">
-        <v>0.1923</v>
+        <v>0.2873</v>
       </c>
       <c r="AG15">
-        <v>0.9904</v>
+        <v>0.9965</v>
       </c>
       <c r="AH15">
-        <v>0</v>
+        <v>0.17</v>
       </c>
       <c r="AM15">
-        <v>4.29</v>
+        <v>6.24</v>
       </c>
     </row>
     <row r="16" spans="1:39" x14ac:dyDescent="0.25">
@@ -2043,28 +2199,28 @@
         <v>39</v>
       </c>
       <c r="B16" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C16">
-        <v>6.5</v>
+        <v>4.5</v>
       </c>
       <c r="D16">
-        <v>118</v>
+        <v>-128</v>
       </c>
       <c r="E16">
-        <v>-130</v>
+        <v>109</v>
       </c>
       <c r="F16" t="s">
         <v>68</v>
       </c>
       <c r="G16">
-        <v>824151</v>
+        <v>824560</v>
       </c>
       <c r="H16" t="s">
         <v>42</v>
       </c>
       <c r="I16">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J16" t="b">
         <v>0</v>
@@ -2076,43 +2232,43 @@
         <v>5</v>
       </c>
       <c r="M16">
-        <v>0.2474</v>
+        <v>0.2008</v>
       </c>
       <c r="N16">
         <v>5</v>
       </c>
       <c r="O16">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="P16">
-        <v>4.24</v>
+        <v>4.4</v>
       </c>
       <c r="Q16">
-        <v>0.2544</v>
+        <v>0.178</v>
       </c>
       <c r="R16">
-        <v>0.363</v>
+        <v>0.371</v>
       </c>
       <c r="S16" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="T16">
-        <v>0.2489</v>
+        <v>0.2182</v>
       </c>
       <c r="U16">
-        <v>0.2157</v>
+        <v>0.2388</v>
       </c>
       <c r="V16">
         <v>9</v>
       </c>
       <c r="W16">
-        <v>0.2118</v>
+        <v>0.2247</v>
       </c>
       <c r="X16">
-        <v>0.2203</v>
+        <v>0.2204</v>
       </c>
       <c r="Y16">
-        <v>1.0462</v>
+        <v>0.9823</v>
       </c>
       <c r="AA16" t="s">
         <v>44</v>
@@ -2121,22 +2277,22 @@
         <v>44</v>
       </c>
       <c r="AD16">
-        <v>6.61</v>
+        <v>4.28</v>
       </c>
       <c r="AE16" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="AF16">
-        <v>0.25</v>
+        <v>0.1923</v>
       </c>
       <c r="AG16">
-        <v>1.1297</v>
+        <v>0.9901</v>
       </c>
       <c r="AH16">
-        <v>0.17</v>
+        <v>0</v>
       </c>
       <c r="AM16">
-        <v>6.78</v>
+        <v>4.28</v>
       </c>
     </row>
     <row r="17" spans="1:39" x14ac:dyDescent="0.25">
@@ -2144,28 +2300,28 @@
         <v>39</v>
       </c>
       <c r="B17" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C17">
         <v>4.5</v>
       </c>
       <c r="D17">
-        <v>-113</v>
+        <v>130</v>
       </c>
       <c r="E17">
-        <v>-102</v>
+        <v>-150</v>
       </c>
       <c r="F17" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="G17">
-        <v>824151</v>
+        <v>824073</v>
       </c>
       <c r="H17" t="s">
-        <v>42</v>
+        <v>72</v>
       </c>
       <c r="I17">
-        <v>4.7</v>
+        <v>4</v>
       </c>
       <c r="J17" t="b">
         <v>0</v>
@@ -2174,46 +2330,46 @@
         <v>0</v>
       </c>
       <c r="L17">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M17">
-        <v>0.2045</v>
+        <v>0.2661</v>
       </c>
       <c r="N17">
         <v>5</v>
       </c>
       <c r="O17">
-        <v>115</v>
+        <v>81</v>
       </c>
       <c r="P17">
-        <v>4.5</v>
+        <v>4.28</v>
       </c>
       <c r="Q17">
-        <v>0.2783</v>
+        <v>0.2593</v>
       </c>
       <c r="R17">
-        <v>0.365</v>
+        <v>0.288</v>
       </c>
       <c r="S17" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="T17">
-        <v>0.2099</v>
+        <v>0.1781</v>
       </c>
       <c r="U17">
-        <v>0.2034</v>
+        <v>0.1894</v>
       </c>
       <c r="V17">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W17">
-        <v>0.2052</v>
+        <v>0.2081</v>
       </c>
       <c r="X17">
-        <v>0.2203</v>
+        <v>0.2204</v>
       </c>
       <c r="Y17">
-        <v>0.9727</v>
+        <v>0.9478</v>
       </c>
       <c r="AA17" t="s">
         <v>44</v>
@@ -2222,22 +2378,22 @@
         <v>44</v>
       </c>
       <c r="AD17">
-        <v>4.5</v>
+        <v>3.47</v>
       </c>
       <c r="AE17" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="AF17">
-        <v>0.2315</v>
+        <v>0.2641</v>
       </c>
       <c r="AG17">
-        <v>0.9528</v>
+        <v>0.8081</v>
       </c>
       <c r="AH17">
         <v>0</v>
       </c>
       <c r="AM17">
-        <v>4.5</v>
+        <v>3.47</v>
       </c>
     </row>
     <row r="18" spans="1:39" x14ac:dyDescent="0.25">
@@ -2245,28 +2401,28 @@
         <v>39</v>
       </c>
       <c r="B18" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="C18">
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
       <c r="D18">
-        <v>-128</v>
+        <v>122</v>
       </c>
       <c r="E18">
-        <v>118</v>
+        <v>-140</v>
       </c>
       <c r="F18" t="s">
         <v>71</v>
       </c>
       <c r="G18">
-        <v>824718</v>
+        <v>824073</v>
       </c>
       <c r="H18" t="s">
         <v>42</v>
       </c>
       <c r="I18">
-        <v>4.9</v>
+        <v>6.2</v>
       </c>
       <c r="J18" t="b">
         <v>0</v>
@@ -2278,43 +2434,43 @@
         <v>6</v>
       </c>
       <c r="M18">
-        <v>0.2188</v>
+        <v>0.1899</v>
       </c>
       <c r="N18">
         <v>5</v>
       </c>
       <c r="O18">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="P18">
-        <v>4.71</v>
+        <v>4.06</v>
       </c>
       <c r="Q18">
-        <v>0.2119</v>
+        <v>0.1557</v>
       </c>
       <c r="R18">
-        <v>0.371</v>
+        <v>0.379</v>
       </c>
       <c r="S18" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="T18">
-        <v>0.2149</v>
+        <v>0.1901</v>
       </c>
       <c r="U18">
-        <v>0.2004</v>
+        <v>0.1925</v>
       </c>
       <c r="V18">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="W18">
-        <v>0.2353</v>
+        <v>0.2227</v>
       </c>
       <c r="X18">
-        <v>0.2203</v>
+        <v>0.2204</v>
       </c>
       <c r="Y18">
-        <v>0.9898</v>
+        <v>0.9792</v>
       </c>
       <c r="AA18" t="s">
         <v>44</v>
@@ -2323,22 +2479,22 @@
         <v>44</v>
       </c>
       <c r="AD18">
-        <v>4.77</v>
+        <v>3.78</v>
       </c>
       <c r="AE18" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="AF18">
-        <v>0.2162</v>
+        <v>0.1769</v>
       </c>
       <c r="AG18">
-        <v>0.9753</v>
+        <v>0.8627</v>
       </c>
       <c r="AH18">
         <v>0</v>
       </c>
       <c r="AM18">
-        <v>4.77</v>
+        <v>3.78</v>
       </c>
     </row>
     <row r="19" spans="1:39" x14ac:dyDescent="0.25">
@@ -2346,28 +2502,28 @@
         <v>39</v>
       </c>
       <c r="B19" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C19">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="D19">
-        <v>-120</v>
+        <v>-114</v>
       </c>
       <c r="E19">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="F19" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="G19">
-        <v>824718</v>
+        <v>823910</v>
       </c>
       <c r="H19" t="s">
         <v>42</v>
       </c>
       <c r="I19">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="J19" t="b">
         <v>0</v>
@@ -2376,46 +2532,46 @@
         <v>0</v>
       </c>
       <c r="L19">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M19">
-        <v>0.1818</v>
+        <v>0.2677</v>
       </c>
       <c r="N19">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O19">
-        <v>63</v>
+        <v>106</v>
       </c>
       <c r="P19">
-        <v>4.07</v>
+        <v>4.2</v>
       </c>
       <c r="Q19">
-        <v>0.1587</v>
+        <v>0.2264</v>
       </c>
       <c r="R19">
-        <v>0.24</v>
+        <v>0.346</v>
       </c>
       <c r="S19" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="T19">
-        <v>0.1806</v>
+        <v>0.302</v>
       </c>
       <c r="U19">
-        <v>0.1852</v>
+        <v>0.2</v>
       </c>
       <c r="V19">
         <v>9</v>
       </c>
       <c r="W19">
-        <v>0.2142</v>
+        <v>0.2068</v>
       </c>
       <c r="X19">
-        <v>0.2203</v>
+        <v>0.2204</v>
       </c>
       <c r="Y19">
-        <v>0.9828</v>
+        <v>1.0015</v>
       </c>
       <c r="AA19" t="s">
         <v>44</v>
@@ -2424,22 +2580,22 @@
         <v>44</v>
       </c>
       <c r="AD19">
-        <v>2.89</v>
+        <v>6.68</v>
       </c>
       <c r="AE19" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="AF19">
-        <v>0.1763</v>
+        <v>0.2534</v>
       </c>
       <c r="AG19">
-        <v>0.8197</v>
+        <v>1.3702</v>
       </c>
       <c r="AH19">
-        <v>0</v>
+        <v>0.17</v>
       </c>
       <c r="AM19">
-        <v>2.89</v>
+        <v>6.85</v>
       </c>
     </row>
     <row r="20" spans="1:39" x14ac:dyDescent="0.25">
@@ -2447,28 +2603,28 @@
         <v>39</v>
       </c>
       <c r="B20" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="C20">
-        <v>4.5</v>
+        <v>8.5</v>
       </c>
       <c r="D20">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="E20">
-        <v>-130</v>
+        <v>-114</v>
       </c>
       <c r="F20" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G20">
-        <v>823100</v>
+        <v>823910</v>
       </c>
       <c r="H20" t="s">
         <v>42</v>
       </c>
       <c r="I20">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J20" t="b">
         <v>0</v>
@@ -2480,43 +2636,43 @@
         <v>5</v>
       </c>
       <c r="M20">
-        <v>0.1874</v>
+        <v>0.3027</v>
       </c>
       <c r="N20">
         <v>5</v>
       </c>
       <c r="O20">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="P20">
-        <v>4.51</v>
+        <v>3.92</v>
       </c>
       <c r="Q20">
-        <v>0.1983</v>
+        <v>0.296</v>
       </c>
       <c r="R20">
-        <v>0.377</v>
+        <v>0.385</v>
       </c>
       <c r="S20" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="T20">
-        <v>0.2274</v>
+        <v>0.2012</v>
       </c>
       <c r="U20">
-        <v>0.2111</v>
+        <v>0.2211</v>
       </c>
       <c r="V20">
         <v>9</v>
       </c>
       <c r="W20">
-        <v>0.2401</v>
+        <v>0.2559</v>
       </c>
       <c r="X20">
-        <v>0.2203</v>
+        <v>0.2204</v>
       </c>
       <c r="Y20">
-        <v>0.9856</v>
+        <v>1.0139</v>
       </c>
       <c r="AA20" t="s">
         <v>44</v>
@@ -2525,22 +2681,22 @@
         <v>44</v>
       </c>
       <c r="AD20">
-        <v>4.41</v>
+        <v>6.52</v>
       </c>
       <c r="AE20" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="AF20">
-        <v>0.1915</v>
+        <v>0.3001</v>
       </c>
       <c r="AG20">
-        <v>1.032</v>
+        <v>0.9132</v>
       </c>
       <c r="AH20">
-        <v>0</v>
+        <v>0.17</v>
       </c>
       <c r="AM20">
-        <v>4.41</v>
+        <v>6.69</v>
       </c>
     </row>
     <row r="21" spans="1:39" x14ac:dyDescent="0.25">
@@ -2548,28 +2704,28 @@
         <v>39</v>
       </c>
       <c r="B21" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C21">
         <v>4.5</v>
       </c>
       <c r="D21">
-        <v>130</v>
+        <v>108</v>
       </c>
       <c r="E21">
-        <v>-150</v>
+        <v>-130</v>
       </c>
       <c r="F21" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="G21">
-        <v>824073</v>
+        <v>823100</v>
       </c>
       <c r="H21" t="s">
-        <v>77</v>
+        <v>42</v>
       </c>
       <c r="I21">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J21" t="b">
         <v>0</v>
@@ -2578,46 +2734,46 @@
         <v>0</v>
       </c>
       <c r="L21">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M21">
-        <v>0.2661</v>
+        <v>0.1874</v>
       </c>
       <c r="N21">
         <v>5</v>
       </c>
       <c r="O21">
-        <v>81</v>
+        <v>121</v>
       </c>
       <c r="P21">
-        <v>4.28</v>
+        <v>4.51</v>
       </c>
       <c r="Q21">
-        <v>0.2593</v>
+        <v>0.1983</v>
       </c>
       <c r="R21">
-        <v>0.288</v>
+        <v>0.377</v>
       </c>
       <c r="S21" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="T21">
-        <v>0.1781</v>
+        <v>0.2274</v>
       </c>
       <c r="U21">
-        <v>0.1894</v>
+        <v>0.2111</v>
       </c>
       <c r="V21">
         <v>9</v>
       </c>
       <c r="W21">
-        <v>0.2081</v>
+        <v>0.2401</v>
       </c>
       <c r="X21">
-        <v>0.2203</v>
+        <v>0.2204</v>
       </c>
       <c r="Y21">
-        <v>0.9478</v>
+        <v>0.9856</v>
       </c>
       <c r="AA21" t="s">
         <v>44</v>
@@ -2626,22 +2782,22 @@
         <v>44</v>
       </c>
       <c r="AD21">
-        <v>3.47</v>
+        <v>4.41</v>
       </c>
       <c r="AE21" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="AF21">
-        <v>0.2641</v>
+        <v>0.1915</v>
       </c>
       <c r="AG21">
-        <v>0.8084</v>
+        <v>1.0317</v>
       </c>
       <c r="AH21">
         <v>0</v>
       </c>
       <c r="AM21">
-        <v>3.47</v>
+        <v>4.41</v>
       </c>
     </row>
     <row r="22" spans="1:39" x14ac:dyDescent="0.25">
@@ -2649,28 +2805,28 @@
         <v>39</v>
       </c>
       <c r="B22" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C22">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="D22">
-        <v>122</v>
+        <v>-120</v>
       </c>
       <c r="E22">
-        <v>-140</v>
+        <v>105</v>
       </c>
       <c r="F22" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="G22">
-        <v>824073</v>
+        <v>824718</v>
       </c>
       <c r="H22" t="s">
         <v>42</v>
       </c>
       <c r="I22">
-        <v>6.2</v>
+        <v>5</v>
       </c>
       <c r="J22" t="b">
         <v>0</v>
@@ -2682,43 +2838,43 @@
         <v>6</v>
       </c>
       <c r="M22">
-        <v>0.1899</v>
+        <v>0.1818</v>
       </c>
       <c r="N22">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O22">
-        <v>122</v>
+        <v>63</v>
       </c>
       <c r="P22">
-        <v>4.06</v>
+        <v>4.07</v>
       </c>
       <c r="Q22">
-        <v>0.1557</v>
+        <v>0.1587</v>
       </c>
       <c r="R22">
-        <v>0.379</v>
+        <v>0.24</v>
       </c>
       <c r="S22" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="T22">
-        <v>0.1901</v>
+        <v>0.1806</v>
       </c>
       <c r="U22">
-        <v>0.1925</v>
+        <v>0.1852</v>
       </c>
       <c r="V22">
         <v>9</v>
       </c>
       <c r="W22">
-        <v>0.2227</v>
+        <v>0.2142</v>
       </c>
       <c r="X22">
-        <v>0.2203</v>
+        <v>0.2204</v>
       </c>
       <c r="Y22">
-        <v>0.9792</v>
+        <v>0.9828</v>
       </c>
       <c r="AA22" t="s">
         <v>44</v>
@@ -2727,22 +2883,22 @@
         <v>44</v>
       </c>
       <c r="AD22">
-        <v>3.78</v>
+        <v>2.89</v>
       </c>
       <c r="AE22" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="AF22">
-        <v>0.1769</v>
+        <v>0.1763</v>
       </c>
       <c r="AG22">
-        <v>0.8629</v>
+        <v>0.8195</v>
       </c>
       <c r="AH22">
         <v>0</v>
       </c>
       <c r="AM22">
-        <v>3.78</v>
+        <v>2.89</v>
       </c>
     </row>
     <row r="23" spans="1:39" x14ac:dyDescent="0.25">
@@ -2750,28 +2906,28 @@
         <v>39</v>
       </c>
       <c r="B23" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C23">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="D23">
-        <v>-114</v>
+        <v>-128</v>
       </c>
       <c r="E23">
-        <v>100</v>
+        <v>118</v>
       </c>
       <c r="F23" t="s">
         <v>80</v>
       </c>
       <c r="G23">
-        <v>823910</v>
+        <v>824718</v>
       </c>
       <c r="H23" t="s">
         <v>42</v>
       </c>
       <c r="I23">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="J23" t="b">
         <v>0</v>
@@ -2780,46 +2936,46 @@
         <v>0</v>
       </c>
       <c r="L23">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M23">
-        <v>0.2677</v>
+        <v>0.2188</v>
       </c>
       <c r="N23">
         <v>5</v>
       </c>
       <c r="O23">
-        <v>106</v>
+        <v>118</v>
       </c>
       <c r="P23">
-        <v>4.2</v>
+        <v>4.71</v>
       </c>
       <c r="Q23">
-        <v>0.2264</v>
+        <v>0.2119</v>
       </c>
       <c r="R23">
-        <v>0.346</v>
+        <v>0.371</v>
       </c>
       <c r="S23" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="T23">
-        <v>0.302</v>
+        <v>0.2149</v>
       </c>
       <c r="U23">
-        <v>0.2</v>
+        <v>0.2004</v>
       </c>
       <c r="V23">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="W23">
-        <v>0.2068</v>
+        <v>0.2353</v>
       </c>
       <c r="X23">
-        <v>0.2203</v>
+        <v>0.2204</v>
       </c>
       <c r="Y23">
-        <v>1.0015</v>
+        <v>0.9898</v>
       </c>
       <c r="AA23" t="s">
         <v>44</v>
@@ -2828,22 +2984,22 @@
         <v>44</v>
       </c>
       <c r="AD23">
-        <v>6.68</v>
+        <v>4.77</v>
       </c>
       <c r="AE23" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="AF23">
-        <v>0.2534</v>
+        <v>0.2162</v>
       </c>
       <c r="AG23">
-        <v>1.3706</v>
+        <v>0.975</v>
       </c>
       <c r="AH23">
-        <v>0.17</v>
+        <v>0</v>
       </c>
       <c r="AM23">
-        <v>6.85</v>
+        <v>4.77</v>
       </c>
     </row>
     <row r="24" spans="1:39" x14ac:dyDescent="0.25">
@@ -2851,76 +3007,76 @@
         <v>39</v>
       </c>
       <c r="B24" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C24">
-        <v>8.5</v>
+        <v>3.5</v>
       </c>
       <c r="D24">
-        <v>105</v>
+        <v>-110</v>
       </c>
       <c r="E24">
-        <v>-114</v>
+        <v>-104</v>
       </c>
       <c r="F24" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="G24">
-        <v>823910</v>
+        <v>825044</v>
       </c>
       <c r="H24" t="s">
         <v>42</v>
       </c>
       <c r="I24">
+        <v>4.9</v>
+      </c>
+      <c r="J24" t="b">
+        <v>0</v>
+      </c>
+      <c r="K24" t="b">
+        <v>0</v>
+      </c>
+      <c r="L24">
         <v>6</v>
       </c>
-      <c r="J24" t="b">
-        <v>0</v>
-      </c>
-      <c r="K24" t="b">
-        <v>0</v>
-      </c>
-      <c r="L24">
-        <v>5</v>
-      </c>
       <c r="M24">
-        <v>0.3027</v>
+        <v>0.1814</v>
       </c>
       <c r="N24">
         <v>5</v>
       </c>
       <c r="O24">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="P24">
-        <v>3.92</v>
+        <v>4.48</v>
       </c>
       <c r="Q24">
-        <v>0.296</v>
+        <v>0.1795</v>
       </c>
       <c r="R24">
-        <v>0.385</v>
+        <v>0.369</v>
       </c>
       <c r="S24" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="T24">
-        <v>0.2012</v>
+        <v>0.1657</v>
       </c>
       <c r="U24">
-        <v>0.2211</v>
+        <v>0.1668</v>
       </c>
       <c r="V24">
         <v>9</v>
       </c>
       <c r="W24">
-        <v>0.2559</v>
+        <v>0.1988</v>
       </c>
       <c r="X24">
-        <v>0.2203</v>
+        <v>0.2204</v>
       </c>
       <c r="Y24">
-        <v>1.0139</v>
+        <v>0.9037</v>
       </c>
       <c r="AA24" t="s">
         <v>44</v>
@@ -2929,22 +3085,22 @@
         <v>44</v>
       </c>
       <c r="AD24">
-        <v>6.52</v>
+        <v>2.72</v>
       </c>
       <c r="AE24" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="AF24">
-        <v>0.3001</v>
+        <v>0.1807</v>
       </c>
       <c r="AG24">
-        <v>0.9135</v>
+        <v>0.7517</v>
       </c>
       <c r="AH24">
-        <v>0.17</v>
+        <v>0</v>
       </c>
       <c r="AM24">
-        <v>6.69</v>
+        <v>2.72</v>
       </c>
     </row>
     <row r="25" spans="1:39" x14ac:dyDescent="0.25">
@@ -2952,7 +3108,7 @@
         <v>39</v>
       </c>
       <c r="B25" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C25">
         <v>5.5</v>
@@ -3003,7 +3159,7 @@
         <v>0.322</v>
       </c>
       <c r="S25" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="T25">
         <v>0.2819</v>
@@ -3018,7 +3174,7 @@
         <v>0.2557</v>
       </c>
       <c r="X25">
-        <v>0.2203</v>
+        <v>0.2204</v>
       </c>
       <c r="Y25">
         <v>1.0246</v>
@@ -3033,13 +3189,13 @@
         <v>6.76</v>
       </c>
       <c r="AE25" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="AF25">
         <v>0.2337</v>
       </c>
       <c r="AG25">
-        <v>1.2795</v>
+        <v>1.2791</v>
       </c>
       <c r="AH25">
         <v>0.17</v>
@@ -3053,28 +3209,28 @@
         <v>39</v>
       </c>
       <c r="B26" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C26">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="D26">
-        <v>-110</v>
+        <v>-113</v>
       </c>
       <c r="E26">
-        <v>-104</v>
+        <v>-108</v>
       </c>
       <c r="F26" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="G26">
-        <v>825044</v>
+        <v>824316</v>
       </c>
       <c r="H26" t="s">
         <v>42</v>
       </c>
       <c r="I26">
-        <v>4.9</v>
+        <v>5.8</v>
       </c>
       <c r="J26" t="b">
         <v>0</v>
@@ -3086,43 +3242,43 @@
         <v>6</v>
       </c>
       <c r="M26">
-        <v>0.1814</v>
+        <v>0.1909</v>
       </c>
       <c r="N26">
         <v>5</v>
       </c>
       <c r="O26">
-        <v>117</v>
+        <v>131</v>
       </c>
       <c r="P26">
-        <v>4.48</v>
+        <v>4.08</v>
       </c>
       <c r="Q26">
-        <v>0.1795</v>
+        <v>0.1908</v>
       </c>
       <c r="R26">
-        <v>0.369</v>
+        <v>0.396</v>
       </c>
       <c r="S26" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="T26">
-        <v>0.1657</v>
+        <v>0.2347</v>
       </c>
       <c r="U26">
-        <v>0.1668</v>
+        <v>0.2264</v>
       </c>
       <c r="V26">
         <v>9</v>
       </c>
       <c r="W26">
-        <v>0.1988</v>
+        <v>0.2178</v>
       </c>
       <c r="X26">
-        <v>0.2203</v>
+        <v>0.2204</v>
       </c>
       <c r="Y26">
-        <v>0.9037</v>
+        <v>0.9978</v>
       </c>
       <c r="AA26" t="s">
         <v>44</v>
@@ -3131,22 +3287,22 @@
         <v>44</v>
       </c>
       <c r="AD26">
-        <v>2.72</v>
+        <v>4.78</v>
       </c>
       <c r="AE26" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="AF26">
-        <v>0.1807</v>
+        <v>0.1909</v>
       </c>
       <c r="AG26">
-        <v>0.752</v>
+        <v>1.0652</v>
       </c>
       <c r="AH26">
         <v>0</v>
       </c>
       <c r="AM26">
-        <v>2.72</v>
+        <v>4.78</v>
       </c>
     </row>
     <row r="27" spans="1:39" x14ac:dyDescent="0.25">
@@ -3154,7 +3310,7 @@
         <v>39</v>
       </c>
       <c r="B27" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C27">
         <v>3.5</v>
@@ -3205,7 +3361,7 @@
         <v>0.351</v>
       </c>
       <c r="S27" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="T27">
         <v>0.217</v>
@@ -3220,7 +3376,7 @@
         <v>0.2137</v>
       </c>
       <c r="X27">
-        <v>0.2203</v>
+        <v>0.2204</v>
       </c>
       <c r="Y27">
         <v>0.9237</v>
@@ -3235,13 +3391,13 @@
         <v>3.77</v>
       </c>
       <c r="AE27" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="AF27">
         <v>0.1924</v>
       </c>
       <c r="AG27">
-        <v>0.9849</v>
+        <v>0.9846</v>
       </c>
       <c r="AH27">
         <v>0</v>
@@ -3255,28 +3411,28 @@
         <v>39</v>
       </c>
       <c r="B28" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C28">
         <v>4.5</v>
       </c>
       <c r="D28">
-        <v>-113</v>
+        <v>102</v>
       </c>
       <c r="E28">
-        <v>-108</v>
+        <v>-115</v>
       </c>
       <c r="F28" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="G28">
-        <v>824316</v>
+        <v>823261</v>
       </c>
       <c r="H28" t="s">
         <v>42</v>
       </c>
       <c r="I28">
-        <v>5.8</v>
+        <v>5.3</v>
       </c>
       <c r="J28" t="b">
         <v>0</v>
@@ -3285,46 +3441,46 @@
         <v>0</v>
       </c>
       <c r="L28">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M28">
-        <v>0.1909</v>
+        <v>0.2442</v>
       </c>
       <c r="N28">
         <v>5</v>
       </c>
       <c r="O28">
-        <v>131</v>
+        <v>114</v>
       </c>
       <c r="P28">
-        <v>4.08</v>
+        <v>4.07</v>
       </c>
       <c r="Q28">
-        <v>0.1908</v>
+        <v>0.2105</v>
       </c>
       <c r="R28">
-        <v>0.396</v>
+        <v>0.363</v>
       </c>
       <c r="S28" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="T28">
-        <v>0.2347</v>
+        <v>0.1876</v>
       </c>
       <c r="U28">
-        <v>0.2264</v>
+        <v>0.1898</v>
       </c>
       <c r="V28">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W28">
-        <v>0.2178</v>
+        <v>0.2166</v>
       </c>
       <c r="X28">
-        <v>0.2203</v>
+        <v>0.2204</v>
       </c>
       <c r="Y28">
-        <v>0.9978</v>
+        <v>0.9947</v>
       </c>
       <c r="AA28" t="s">
         <v>44</v>
@@ -3333,22 +3489,22 @@
         <v>44</v>
       </c>
       <c r="AD28">
-        <v>4.78</v>
+        <v>4.26</v>
       </c>
       <c r="AE28" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="AF28">
-        <v>0.1909</v>
+        <v>0.232</v>
       </c>
       <c r="AG28">
-        <v>1.0655</v>
+        <v>0.8511</v>
       </c>
       <c r="AH28">
         <v>0</v>
       </c>
       <c r="AM28">
-        <v>4.78</v>
+        <v>4.26</v>
       </c>
     </row>
     <row r="29" spans="1:39" x14ac:dyDescent="0.25">
@@ -3356,7 +3512,7 @@
         <v>39</v>
       </c>
       <c r="B29" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C29">
         <v>4.5</v>
@@ -3407,7 +3563,7 @@
         <v>0.342</v>
       </c>
       <c r="S29" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="T29">
         <v>0.1983</v>
@@ -3422,7 +3578,7 @@
         <v>0.2101</v>
       </c>
       <c r="X29">
-        <v>0.2203</v>
+        <v>0.2204</v>
       </c>
       <c r="Y29">
         <v>0.9967</v>
@@ -3437,13 +3593,13 @@
         <v>4.09</v>
       </c>
       <c r="AE29" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="AF29">
         <v>0.2124</v>
       </c>
       <c r="AG29">
-        <v>0.9002</v>
+        <v>0.8999</v>
       </c>
       <c r="AH29">
         <v>0</v>
@@ -3457,76 +3613,34 @@
         <v>39</v>
       </c>
       <c r="B30" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C30">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="D30">
-        <v>102</v>
+        <v>-111</v>
       </c>
       <c r="E30">
-        <v>-115</v>
+        <v>-110</v>
       </c>
       <c r="F30" t="s">
-        <v>89</v>
-      </c>
-      <c r="G30">
-        <v>823261</v>
+        <v>50</v>
+      </c>
+      <c r="G30" t="s">
+        <v>44</v>
       </c>
       <c r="H30" t="s">
-        <v>42</v>
-      </c>
-      <c r="I30">
-        <v>5.3</v>
-      </c>
-      <c r="J30" t="b">
-        <v>0</v>
-      </c>
-      <c r="K30" t="b">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="L30">
-        <v>4</v>
-      </c>
-      <c r="M30">
-        <v>0.2442</v>
-      </c>
-      <c r="N30">
-        <v>5</v>
-      </c>
-      <c r="O30">
-        <v>114</v>
-      </c>
-      <c r="P30">
-        <v>4.07</v>
-      </c>
-      <c r="Q30">
-        <v>0.2105</v>
-      </c>
-      <c r="R30">
-        <v>0.363</v>
+        <v>6</v>
       </c>
       <c r="S30" t="s">
-        <v>43</v>
-      </c>
-      <c r="T30">
-        <v>0.1876</v>
-      </c>
-      <c r="U30">
-        <v>0.1898</v>
-      </c>
-      <c r="V30">
-        <v>8</v>
-      </c>
-      <c r="W30">
-        <v>0.2166</v>
-      </c>
-      <c r="X30">
-        <v>0.2203</v>
-      </c>
-      <c r="Y30">
-        <v>0.9947</v>
+        <v>44</v>
+      </c>
+      <c r="V30" t="s">
+        <v>44</v>
       </c>
       <c r="AA30" t="s">
         <v>44</v>
@@ -3534,23 +3648,8 @@
       <c r="AC30" t="s">
         <v>44</v>
       </c>
-      <c r="AD30">
-        <v>4.26</v>
-      </c>
       <c r="AE30" t="s">
-        <v>47</v>
-      </c>
-      <c r="AF30">
-        <v>0.232</v>
-      </c>
-      <c r="AG30">
-        <v>0.8514</v>
-      </c>
-      <c r="AH30">
-        <v>0</v>
-      </c>
-      <c r="AM30">
-        <v>4.26</v>
+        <v>44</v>
       </c>
     </row>
     <row r="31" spans="1:39" x14ac:dyDescent="0.25">
@@ -3558,67 +3657,34 @@
         <v>39</v>
       </c>
       <c r="B31" t="s">
-        <v>91</v>
+        <v>92</v>
+      </c>
+      <c r="C31">
+        <v>6.5</v>
+      </c>
+      <c r="D31">
+        <v>110</v>
+      </c>
+      <c r="E31">
+        <v>-132</v>
       </c>
       <c r="F31" t="s">
-        <v>49</v>
-      </c>
-      <c r="G31">
-        <v>823743</v>
+        <v>54</v>
+      </c>
+      <c r="G31" t="s">
+        <v>44</v>
       </c>
       <c r="H31" t="s">
-        <v>42</v>
-      </c>
-      <c r="I31">
-        <v>5.1</v>
-      </c>
-      <c r="J31" t="b">
-        <v>0</v>
-      </c>
-      <c r="K31" t="b">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="L31">
-        <v>0</v>
-      </c>
-      <c r="M31">
-        <v>0.1824</v>
-      </c>
-      <c r="N31">
-        <v>5</v>
-      </c>
-      <c r="O31">
-        <v>106</v>
-      </c>
-      <c r="P31">
-        <v>4.09</v>
-      </c>
-      <c r="Q31">
-        <v>0.1698</v>
-      </c>
-      <c r="R31">
-        <v>0.346</v>
+        <v>6</v>
       </c>
       <c r="S31" t="s">
-        <v>43</v>
-      </c>
-      <c r="T31">
-        <v>0.2293</v>
-      </c>
-      <c r="U31">
-        <v>0.2269</v>
-      </c>
-      <c r="V31">
-        <v>8</v>
-      </c>
-      <c r="W31">
-        <v>0.2223</v>
-      </c>
-      <c r="X31">
-        <v>0.2203</v>
-      </c>
-      <c r="Y31">
-        <v>1.0155</v>
+        <v>44</v>
+      </c>
+      <c r="V31" t="s">
+        <v>44</v>
       </c>
       <c r="AA31" t="s">
         <v>44</v>
@@ -3626,23 +3692,8 @@
       <c r="AC31" t="s">
         <v>44</v>
       </c>
-      <c r="AD31">
-        <v>3.92</v>
-      </c>
       <c r="AE31" t="s">
-        <v>47</v>
-      </c>
-      <c r="AF31">
-        <v>0.1781</v>
-      </c>
-      <c r="AG31">
-        <v>1.0409</v>
-      </c>
-      <c r="AH31">
-        <v>0</v>
-      </c>
-      <c r="AM31">
-        <v>3.92</v>
+        <v>44</v>
       </c>
     </row>
     <row r="32" spans="1:39" x14ac:dyDescent="0.25">
@@ -3650,67 +3701,34 @@
         <v>39</v>
       </c>
       <c r="B32" t="s">
-        <v>92</v>
+        <v>93</v>
+      </c>
+      <c r="C32">
+        <v>4.5</v>
+      </c>
+      <c r="D32">
+        <v>105</v>
+      </c>
+      <c r="E32">
+        <v>108</v>
       </c>
       <c r="F32" t="s">
-        <v>53</v>
-      </c>
-      <c r="G32">
-        <v>823831</v>
+        <v>57</v>
+      </c>
+      <c r="G32" t="s">
+        <v>44</v>
       </c>
       <c r="H32" t="s">
-        <v>42</v>
-      </c>
-      <c r="I32">
-        <v>5.6</v>
-      </c>
-      <c r="J32" t="b">
-        <v>0</v>
-      </c>
-      <c r="K32" t="b">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="L32">
-        <v>0</v>
-      </c>
-      <c r="M32">
-        <v>0.2692</v>
-      </c>
-      <c r="N32">
-        <v>5</v>
-      </c>
-      <c r="O32">
-        <v>123</v>
-      </c>
-      <c r="P32">
-        <v>4.03</v>
-      </c>
-      <c r="Q32">
-        <v>0.2358</v>
-      </c>
-      <c r="R32">
-        <v>0.381</v>
+        <v>6</v>
       </c>
       <c r="S32" t="s">
-        <v>43</v>
-      </c>
-      <c r="T32">
-        <v>0.2359</v>
-      </c>
-      <c r="U32">
-        <v>0.2361</v>
-      </c>
-      <c r="V32">
-        <v>9</v>
-      </c>
-      <c r="W32">
-        <v>0.2076</v>
-      </c>
-      <c r="X32">
-        <v>0.2203</v>
-      </c>
-      <c r="Y32">
-        <v>1.017</v>
+        <v>44</v>
+      </c>
+      <c r="V32" t="s">
+        <v>44</v>
       </c>
       <c r="AA32" t="s">
         <v>44</v>
@@ -3718,23 +3736,8 @@
       <c r="AC32" t="s">
         <v>44</v>
       </c>
-      <c r="AD32">
-        <v>6.27</v>
-      </c>
       <c r="AE32" t="s">
-        <v>51</v>
-      </c>
-      <c r="AF32">
-        <v>0.2565</v>
-      </c>
-      <c r="AG32">
-        <v>1.0708</v>
-      </c>
-      <c r="AH32">
-        <v>0.17</v>
-      </c>
-      <c r="AM32">
-        <v>6.44</v>
+        <v>44</v>
       </c>
     </row>
   </sheetData>

--- a/data/k-props/2026-08-22.xlsx
+++ b/data/k-props/2026-08-22.xlsx
@@ -869,7 +869,7 @@
         <v>0.2473</v>
       </c>
       <c r="X2">
-        <v>0.2204</v>
+        <v>0.2198</v>
       </c>
       <c r="Y2">
         <v>1.0348</v>
@@ -881,7 +881,7 @@
         <v>44</v>
       </c>
       <c r="AD2">
-        <v>11.28</v>
+        <v>11.31</v>
       </c>
       <c r="AE2" t="s">
         <v>45</v>
@@ -890,13 +890,13 @@
         <v>0.3641</v>
       </c>
       <c r="AG2">
-        <v>1.2453</v>
+        <v>1.2484</v>
       </c>
       <c r="AH2">
         <v>0</v>
       </c>
       <c r="AM2">
-        <v>11.28</v>
+        <v>11.31</v>
       </c>
     </row>
     <row r="3" spans="1:39" x14ac:dyDescent="0.25">
@@ -970,7 +970,7 @@
         <v>0.2108</v>
       </c>
       <c r="X3">
-        <v>0.2204</v>
+        <v>0.2198</v>
       </c>
       <c r="Y3">
         <v>0.9765</v>
@@ -982,7 +982,7 @@
         <v>44</v>
       </c>
       <c r="AD3">
-        <v>4.93</v>
+        <v>4.95</v>
       </c>
       <c r="AE3" t="s">
         <v>48</v>
@@ -991,13 +991,13 @@
         <v>0.2377</v>
       </c>
       <c r="AG3">
-        <v>0.9259</v>
+        <v>0.9282</v>
       </c>
       <c r="AH3">
         <v>0</v>
       </c>
       <c r="AM3">
-        <v>4.93</v>
+        <v>4.95</v>
       </c>
     </row>
     <row r="4" spans="1:39" x14ac:dyDescent="0.25">
@@ -1047,25 +1047,25 @@
         <v>0.346</v>
       </c>
       <c r="S4" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="T4">
-        <v>0.2293</v>
+        <v>0.2262</v>
       </c>
       <c r="U4">
-        <v>0.2269</v>
+        <v>0.222</v>
       </c>
       <c r="V4">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W4">
         <v>0.2223</v>
       </c>
       <c r="X4">
-        <v>0.2204</v>
+        <v>0.2198</v>
       </c>
       <c r="Y4">
-        <v>1.0155</v>
+        <v>0.9813</v>
       </c>
       <c r="AA4" t="s">
         <v>44</v>
@@ -1074,7 +1074,7 @@
         <v>44</v>
       </c>
       <c r="AD4">
-        <v>3.92</v>
+        <v>3.75</v>
       </c>
       <c r="AE4" t="s">
         <v>48</v>
@@ -1083,13 +1083,13 @@
         <v>0.1781</v>
       </c>
       <c r="AG4">
-        <v>1.0406</v>
+        <v>1.0291</v>
       </c>
       <c r="AH4">
         <v>0</v>
       </c>
       <c r="AM4">
-        <v>3.92</v>
+        <v>3.75</v>
       </c>
     </row>
     <row r="5" spans="1:39" x14ac:dyDescent="0.25">
@@ -1148,13 +1148,13 @@
         <v>0.359</v>
       </c>
       <c r="S5" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="T5">
-        <v>0.2437</v>
+        <v>0.2236</v>
       </c>
       <c r="U5">
-        <v>0.2371</v>
+        <v>0.2244</v>
       </c>
       <c r="V5">
         <v>9</v>
@@ -1163,10 +1163,10 @@
         <v>0.2201</v>
       </c>
       <c r="X5">
-        <v>0.2204</v>
+        <v>0.2198</v>
       </c>
       <c r="Y5">
-        <v>0.9913</v>
+        <v>0.9745</v>
       </c>
       <c r="AA5" t="s">
         <v>44</v>
@@ -1175,7 +1175,7 @@
         <v>44</v>
       </c>
       <c r="AD5">
-        <v>6.99</v>
+        <v>6.32</v>
       </c>
       <c r="AE5" t="s">
         <v>52</v>
@@ -1184,13 +1184,13 @@
         <v>0.3189</v>
       </c>
       <c r="AG5">
-        <v>1.1059</v>
+        <v>1.0172</v>
       </c>
       <c r="AH5">
         <v>0.17</v>
       </c>
       <c r="AM5">
-        <v>7.16</v>
+        <v>6.49</v>
       </c>
     </row>
     <row r="6" spans="1:39" x14ac:dyDescent="0.25">
@@ -1249,13 +1249,13 @@
         <v>0.336</v>
       </c>
       <c r="S6" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="T6">
-        <v>0.2194</v>
+        <v>0.2262</v>
       </c>
       <c r="U6">
-        <v>0.2079</v>
+        <v>0.2109</v>
       </c>
       <c r="V6">
         <v>9</v>
@@ -1264,10 +1264,10 @@
         <v>0.2121</v>
       </c>
       <c r="X6">
-        <v>0.2204</v>
+        <v>0.2198</v>
       </c>
       <c r="Y6">
-        <v>0.9726</v>
+        <v>0.9201</v>
       </c>
       <c r="AA6" t="s">
         <v>44</v>
@@ -1276,7 +1276,7 @@
         <v>44</v>
       </c>
       <c r="AD6">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="AE6" t="s">
         <v>48</v>
@@ -1285,13 +1285,13 @@
         <v>0.2226</v>
       </c>
       <c r="AG6">
-        <v>0.9955</v>
+        <v>1.0291</v>
       </c>
       <c r="AH6">
         <v>0</v>
       </c>
       <c r="AM6">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
     </row>
     <row r="7" spans="1:39" x14ac:dyDescent="0.25">
@@ -1356,7 +1356,7 @@
         <v>0.2076</v>
       </c>
       <c r="X7">
-        <v>0.2204</v>
+        <v>0.2198</v>
       </c>
       <c r="Y7">
         <v>1.017</v>
@@ -1368,7 +1368,7 @@
         <v>44</v>
       </c>
       <c r="AD7">
-        <v>6.27</v>
+        <v>6.29</v>
       </c>
       <c r="AE7" t="s">
         <v>52</v>
@@ -1377,13 +1377,13 @@
         <v>0.2565</v>
       </c>
       <c r="AG7">
-        <v>1.0705</v>
+        <v>1.0731</v>
       </c>
       <c r="AH7">
         <v>0.17</v>
       </c>
       <c r="AM7">
-        <v>6.44</v>
+        <v>6.46</v>
       </c>
     </row>
     <row r="8" spans="1:39" x14ac:dyDescent="0.25">
@@ -1457,7 +1457,7 @@
         <v>0.2137</v>
       </c>
       <c r="X8">
-        <v>0.2204</v>
+        <v>0.2198</v>
       </c>
       <c r="Y8">
         <v>0.9561</v>
@@ -1469,7 +1469,7 @@
         <v>44</v>
       </c>
       <c r="AD8">
-        <v>3.52</v>
+        <v>3.53</v>
       </c>
       <c r="AE8" t="s">
         <v>48</v>
@@ -1478,13 +1478,13 @@
         <v>0.1949</v>
       </c>
       <c r="AG8">
-        <v>0.8944</v>
+        <v>0.8966</v>
       </c>
       <c r="AH8">
         <v>0</v>
       </c>
       <c r="AM8">
-        <v>3.52</v>
+        <v>3.53</v>
       </c>
     </row>
     <row r="9" spans="1:39" x14ac:dyDescent="0.25">
@@ -1558,7 +1558,7 @@
         <v>0.2573</v>
       </c>
       <c r="X9">
-        <v>0.2204</v>
+        <v>0.2198</v>
       </c>
       <c r="Y9">
         <v>1.0201</v>
@@ -1570,7 +1570,7 @@
         <v>44</v>
       </c>
       <c r="AD9">
-        <v>5.01</v>
+        <v>5.02</v>
       </c>
       <c r="AE9" t="s">
         <v>48</v>
@@ -1579,13 +1579,13 @@
         <v>0.2111</v>
       </c>
       <c r="AG9">
-        <v>1.1546</v>
+        <v>1.1574</v>
       </c>
       <c r="AH9">
         <v>0</v>
       </c>
       <c r="AM9">
-        <v>5.01</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="10" spans="1:39" x14ac:dyDescent="0.25">
@@ -1659,7 +1659,7 @@
         <v>0.189</v>
       </c>
       <c r="X10">
-        <v>0.2204</v>
+        <v>0.2198</v>
       </c>
       <c r="Y10">
         <v>0.9097</v>
@@ -1671,7 +1671,7 @@
         <v>44</v>
       </c>
       <c r="AD10">
-        <v>3.26</v>
+        <v>3.27</v>
       </c>
       <c r="AE10" t="s">
         <v>48</v>
@@ -1680,13 +1680,13 @@
         <v>0.1889</v>
       </c>
       <c r="AG10">
-        <v>0.7869</v>
+        <v>0.7889</v>
       </c>
       <c r="AH10">
         <v>0</v>
       </c>
       <c r="AM10">
-        <v>3.26</v>
+        <v>3.27</v>
       </c>
     </row>
     <row r="11" spans="1:39" x14ac:dyDescent="0.25">
@@ -1760,7 +1760,7 @@
         <v>0.2245</v>
       </c>
       <c r="X11">
-        <v>0.2204</v>
+        <v>0.2198</v>
       </c>
       <c r="Y11">
         <v>1.0122</v>
@@ -1772,7 +1772,7 @@
         <v>44</v>
       </c>
       <c r="AD11">
-        <v>3.95</v>
+        <v>3.96</v>
       </c>
       <c r="AE11" t="s">
         <v>48</v>
@@ -1781,13 +1781,13 @@
         <v>0.1711</v>
       </c>
       <c r="AG11">
-        <v>1.1003</v>
+        <v>1.103</v>
       </c>
       <c r="AH11">
         <v>0</v>
       </c>
       <c r="AM11">
-        <v>3.95</v>
+        <v>3.96</v>
       </c>
     </row>
     <row r="12" spans="1:39" x14ac:dyDescent="0.25">
@@ -1861,7 +1861,7 @@
         <v>0.2562</v>
       </c>
       <c r="X12">
-        <v>0.2204</v>
+        <v>0.2198</v>
       </c>
       <c r="Y12">
         <v>1.0326</v>
@@ -1873,7 +1873,7 @@
         <v>44</v>
       </c>
       <c r="AD12">
-        <v>4.24</v>
+        <v>4.25</v>
       </c>
       <c r="AE12" t="s">
         <v>48</v>
@@ -1882,13 +1882,13 @@
         <v>0.1538</v>
       </c>
       <c r="AG12">
-        <v>1.2318</v>
+        <v>1.2348</v>
       </c>
       <c r="AH12">
         <v>0</v>
       </c>
       <c r="AM12">
-        <v>4.24</v>
+        <v>4.25</v>
       </c>
     </row>
     <row r="13" spans="1:39" x14ac:dyDescent="0.25">
@@ -1962,7 +1962,7 @@
         <v>0.2052</v>
       </c>
       <c r="X13">
-        <v>0.2204</v>
+        <v>0.2198</v>
       </c>
       <c r="Y13">
         <v>0.9727</v>
@@ -1974,7 +1974,7 @@
         <v>44</v>
       </c>
       <c r="AD13">
-        <v>4.5</v>
+        <v>4.51</v>
       </c>
       <c r="AE13" t="s">
         <v>48</v>
@@ -1983,13 +1983,13 @@
         <v>0.2315</v>
       </c>
       <c r="AG13">
-        <v>0.9526</v>
+        <v>0.9549</v>
       </c>
       <c r="AH13">
         <v>0</v>
       </c>
       <c r="AM13">
-        <v>4.5</v>
+        <v>4.51</v>
       </c>
     </row>
     <row r="14" spans="1:39" x14ac:dyDescent="0.25">
@@ -2063,7 +2063,7 @@
         <v>0.2118</v>
       </c>
       <c r="X14">
-        <v>0.2204</v>
+        <v>0.2198</v>
       </c>
       <c r="Y14">
         <v>1.0462</v>
@@ -2075,7 +2075,7 @@
         <v>44</v>
       </c>
       <c r="AD14">
-        <v>6.61</v>
+        <v>6.63</v>
       </c>
       <c r="AE14" t="s">
         <v>52</v>
@@ -2084,13 +2084,13 @@
         <v>0.25</v>
       </c>
       <c r="AG14">
-        <v>1.1293</v>
+        <v>1.1321</v>
       </c>
       <c r="AH14">
         <v>0.17</v>
       </c>
       <c r="AM14">
-        <v>6.78</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="15" spans="1:39" x14ac:dyDescent="0.25">
@@ -2164,7 +2164,7 @@
         <v>0.2358</v>
       </c>
       <c r="X15">
-        <v>0.2204</v>
+        <v>0.2198</v>
       </c>
       <c r="Y15">
         <v>1.04</v>
@@ -2176,7 +2176,7 @@
         <v>44</v>
       </c>
       <c r="AD15">
-        <v>6.07</v>
+        <v>6.09</v>
       </c>
       <c r="AE15" t="s">
         <v>52</v>
@@ -2185,13 +2185,13 @@
         <v>0.2873</v>
       </c>
       <c r="AG15">
-        <v>0.9965</v>
+        <v>0.999</v>
       </c>
       <c r="AH15">
         <v>0.17</v>
       </c>
       <c r="AM15">
-        <v>6.24</v>
+        <v>6.26</v>
       </c>
     </row>
     <row r="16" spans="1:39" x14ac:dyDescent="0.25">
@@ -2265,7 +2265,7 @@
         <v>0.2247</v>
       </c>
       <c r="X16">
-        <v>0.2204</v>
+        <v>0.2198</v>
       </c>
       <c r="Y16">
         <v>0.9823</v>
@@ -2277,7 +2277,7 @@
         <v>44</v>
       </c>
       <c r="AD16">
-        <v>4.28</v>
+        <v>4.29</v>
       </c>
       <c r="AE16" t="s">
         <v>48</v>
@@ -2286,13 +2286,13 @@
         <v>0.1923</v>
       </c>
       <c r="AG16">
-        <v>0.9901</v>
+        <v>0.9926</v>
       </c>
       <c r="AH16">
         <v>0</v>
       </c>
       <c r="AM16">
-        <v>4.28</v>
+        <v>4.29</v>
       </c>
     </row>
     <row r="17" spans="1:39" x14ac:dyDescent="0.25">
@@ -2366,7 +2366,7 @@
         <v>0.2081</v>
       </c>
       <c r="X17">
-        <v>0.2204</v>
+        <v>0.2198</v>
       </c>
       <c r="Y17">
         <v>0.9478</v>
@@ -2387,7 +2387,7 @@
         <v>0.2641</v>
       </c>
       <c r="AG17">
-        <v>0.8081</v>
+        <v>0.8101</v>
       </c>
       <c r="AH17">
         <v>0</v>
@@ -2467,7 +2467,7 @@
         <v>0.2227</v>
       </c>
       <c r="X18">
-        <v>0.2204</v>
+        <v>0.2198</v>
       </c>
       <c r="Y18">
         <v>0.9792</v>
@@ -2479,7 +2479,7 @@
         <v>44</v>
       </c>
       <c r="AD18">
-        <v>3.78</v>
+        <v>3.79</v>
       </c>
       <c r="AE18" t="s">
         <v>48</v>
@@ -2488,13 +2488,13 @@
         <v>0.1769</v>
       </c>
       <c r="AG18">
-        <v>0.8627</v>
+        <v>0.8648</v>
       </c>
       <c r="AH18">
         <v>0</v>
       </c>
       <c r="AM18">
-        <v>3.78</v>
+        <v>3.79</v>
       </c>
     </row>
     <row r="19" spans="1:39" x14ac:dyDescent="0.25">
@@ -2568,7 +2568,7 @@
         <v>0.2068</v>
       </c>
       <c r="X19">
-        <v>0.2204</v>
+        <v>0.2198</v>
       </c>
       <c r="Y19">
         <v>1.0015</v>
@@ -2580,7 +2580,7 @@
         <v>44</v>
       </c>
       <c r="AD19">
-        <v>6.68</v>
+        <v>6.7</v>
       </c>
       <c r="AE19" t="s">
         <v>52</v>
@@ -2589,13 +2589,13 @@
         <v>0.2534</v>
       </c>
       <c r="AG19">
-        <v>1.3702</v>
+        <v>1.3736</v>
       </c>
       <c r="AH19">
         <v>0.17</v>
       </c>
       <c r="AM19">
-        <v>6.85</v>
+        <v>6.87</v>
       </c>
     </row>
     <row r="20" spans="1:39" x14ac:dyDescent="0.25">
@@ -2669,7 +2669,7 @@
         <v>0.2559</v>
       </c>
       <c r="X20">
-        <v>0.2204</v>
+        <v>0.2198</v>
       </c>
       <c r="Y20">
         <v>1.0139</v>
@@ -2681,7 +2681,7 @@
         <v>44</v>
       </c>
       <c r="AD20">
-        <v>6.52</v>
+        <v>6.54</v>
       </c>
       <c r="AE20" t="s">
         <v>52</v>
@@ -2690,13 +2690,13 @@
         <v>0.3001</v>
       </c>
       <c r="AG20">
-        <v>0.9132</v>
+        <v>0.9154</v>
       </c>
       <c r="AH20">
         <v>0.17</v>
       </c>
       <c r="AM20">
-        <v>6.69</v>
+        <v>6.71</v>
       </c>
     </row>
     <row r="21" spans="1:39" x14ac:dyDescent="0.25">
@@ -2770,7 +2770,7 @@
         <v>0.2401</v>
       </c>
       <c r="X21">
-        <v>0.2204</v>
+        <v>0.2198</v>
       </c>
       <c r="Y21">
         <v>0.9856</v>
@@ -2782,7 +2782,7 @@
         <v>44</v>
       </c>
       <c r="AD21">
-        <v>4.41</v>
+        <v>4.42</v>
       </c>
       <c r="AE21" t="s">
         <v>48</v>
@@ -2791,13 +2791,13 @@
         <v>0.1915</v>
       </c>
       <c r="AG21">
-        <v>1.0317</v>
+        <v>1.0343</v>
       </c>
       <c r="AH21">
         <v>0</v>
       </c>
       <c r="AM21">
-        <v>4.41</v>
+        <v>4.42</v>
       </c>
     </row>
     <row r="22" spans="1:39" x14ac:dyDescent="0.25">
@@ -2871,7 +2871,7 @@
         <v>0.2142</v>
       </c>
       <c r="X22">
-        <v>0.2204</v>
+        <v>0.2198</v>
       </c>
       <c r="Y22">
         <v>0.9828</v>
@@ -2883,7 +2883,7 @@
         <v>44</v>
       </c>
       <c r="AD22">
-        <v>2.89</v>
+        <v>2.9</v>
       </c>
       <c r="AE22" t="s">
         <v>48</v>
@@ -2892,13 +2892,13 @@
         <v>0.1763</v>
       </c>
       <c r="AG22">
-        <v>0.8195</v>
+        <v>0.8215</v>
       </c>
       <c r="AH22">
         <v>0</v>
       </c>
       <c r="AM22">
-        <v>2.89</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="23" spans="1:39" x14ac:dyDescent="0.25">
@@ -2972,7 +2972,7 @@
         <v>0.2353</v>
       </c>
       <c r="X23">
-        <v>0.2204</v>
+        <v>0.2198</v>
       </c>
       <c r="Y23">
         <v>0.9898</v>
@@ -2984,7 +2984,7 @@
         <v>44</v>
       </c>
       <c r="AD23">
-        <v>4.77</v>
+        <v>4.78</v>
       </c>
       <c r="AE23" t="s">
         <v>48</v>
@@ -2993,13 +2993,13 @@
         <v>0.2162</v>
       </c>
       <c r="AG23">
-        <v>0.975</v>
+        <v>0.9774</v>
       </c>
       <c r="AH23">
         <v>0</v>
       </c>
       <c r="AM23">
-        <v>4.77</v>
+        <v>4.78</v>
       </c>
     </row>
     <row r="24" spans="1:39" x14ac:dyDescent="0.25">
@@ -3073,7 +3073,7 @@
         <v>0.1988</v>
       </c>
       <c r="X24">
-        <v>0.2204</v>
+        <v>0.2198</v>
       </c>
       <c r="Y24">
         <v>0.9037</v>
@@ -3094,7 +3094,7 @@
         <v>0.1807</v>
       </c>
       <c r="AG24">
-        <v>0.7517</v>
+        <v>0.7536</v>
       </c>
       <c r="AH24">
         <v>0</v>
@@ -3174,7 +3174,7 @@
         <v>0.2557</v>
       </c>
       <c r="X25">
-        <v>0.2204</v>
+        <v>0.2198</v>
       </c>
       <c r="Y25">
         <v>1.0246</v>
@@ -3186,7 +3186,7 @@
         <v>44</v>
       </c>
       <c r="AD25">
-        <v>6.76</v>
+        <v>6.77</v>
       </c>
       <c r="AE25" t="s">
         <v>52</v>
@@ -3195,13 +3195,13 @@
         <v>0.2337</v>
       </c>
       <c r="AG25">
-        <v>1.2791</v>
+        <v>1.2823</v>
       </c>
       <c r="AH25">
         <v>0.17</v>
       </c>
       <c r="AM25">
-        <v>6.93</v>
+        <v>6.94</v>
       </c>
     </row>
     <row r="26" spans="1:39" x14ac:dyDescent="0.25">
@@ -3275,7 +3275,7 @@
         <v>0.2178</v>
       </c>
       <c r="X26">
-        <v>0.2204</v>
+        <v>0.2198</v>
       </c>
       <c r="Y26">
         <v>0.9978</v>
@@ -3287,7 +3287,7 @@
         <v>44</v>
       </c>
       <c r="AD26">
-        <v>4.78</v>
+        <v>4.79</v>
       </c>
       <c r="AE26" t="s">
         <v>48</v>
@@ -3296,13 +3296,13 @@
         <v>0.1909</v>
       </c>
       <c r="AG26">
-        <v>1.0652</v>
+        <v>1.0678</v>
       </c>
       <c r="AH26">
         <v>0</v>
       </c>
       <c r="AM26">
-        <v>4.78</v>
+        <v>4.79</v>
       </c>
     </row>
     <row r="27" spans="1:39" x14ac:dyDescent="0.25">
@@ -3376,7 +3376,7 @@
         <v>0.2137</v>
       </c>
       <c r="X27">
-        <v>0.2204</v>
+        <v>0.2198</v>
       </c>
       <c r="Y27">
         <v>0.9237</v>
@@ -3388,7 +3388,7 @@
         <v>44</v>
       </c>
       <c r="AD27">
-        <v>3.77</v>
+        <v>3.78</v>
       </c>
       <c r="AE27" t="s">
         <v>48</v>
@@ -3397,13 +3397,13 @@
         <v>0.1924</v>
       </c>
       <c r="AG27">
-        <v>0.9846</v>
+        <v>0.9871</v>
       </c>
       <c r="AH27">
         <v>0</v>
       </c>
       <c r="AM27">
-        <v>3.77</v>
+        <v>3.78</v>
       </c>
     </row>
     <row r="28" spans="1:39" x14ac:dyDescent="0.25">
@@ -3477,7 +3477,7 @@
         <v>0.2166</v>
       </c>
       <c r="X28">
-        <v>0.2204</v>
+        <v>0.2198</v>
       </c>
       <c r="Y28">
         <v>0.9947</v>
@@ -3489,7 +3489,7 @@
         <v>44</v>
       </c>
       <c r="AD28">
-        <v>4.26</v>
+        <v>4.27</v>
       </c>
       <c r="AE28" t="s">
         <v>48</v>
@@ -3498,13 +3498,13 @@
         <v>0.232</v>
       </c>
       <c r="AG28">
-        <v>0.8511</v>
+        <v>0.8532</v>
       </c>
       <c r="AH28">
         <v>0</v>
       </c>
       <c r="AM28">
-        <v>4.26</v>
+        <v>4.27</v>
       </c>
     </row>
     <row r="29" spans="1:39" x14ac:dyDescent="0.25">
@@ -3578,7 +3578,7 @@
         <v>0.2101</v>
       </c>
       <c r="X29">
-        <v>0.2204</v>
+        <v>0.2198</v>
       </c>
       <c r="Y29">
         <v>0.9967</v>
@@ -3590,7 +3590,7 @@
         <v>44</v>
       </c>
       <c r="AD29">
-        <v>4.09</v>
+        <v>4.1</v>
       </c>
       <c r="AE29" t="s">
         <v>48</v>
@@ -3599,13 +3599,13 @@
         <v>0.2124</v>
       </c>
       <c r="AG29">
-        <v>0.8999</v>
+        <v>0.9022</v>
       </c>
       <c r="AH29">
         <v>0</v>
       </c>
       <c r="AM29">
-        <v>4.09</v>
+        <v>4.1</v>
       </c>
     </row>
     <row r="30" spans="1:39" x14ac:dyDescent="0.25">

--- a/data/k-props/2026-08-22.xlsx
+++ b/data/k-props/2026-08-22.xlsx
@@ -154,37 +154,37 @@
     <t>Ryan Weathers</t>
   </si>
   <si>
+    <t>&lt;6</t>
+  </si>
+  <si>
+    <t>Martín Pérez</t>
+  </si>
+  <si>
+    <t>Atlanta Braves @ Milwaukee Brewers</t>
+  </si>
+  <si>
+    <t>Logan Henderson</t>
+  </si>
+  <si>
+    <t>Jake Irvin</t>
+  </si>
+  <si>
+    <t>Washington Nationals @ Miami Marlins</t>
+  </si>
+  <si>
+    <t>Eury Pérez</t>
+  </si>
+  <si>
+    <t>6-7</t>
+  </si>
+  <si>
+    <t>Andrew Painter</t>
+  </si>
+  <si>
+    <t>St. Louis Cardinals @ Philadelphia Phillies</t>
+  </si>
+  <si>
     <t>lineup_unweighted_30d_projected_regulars</t>
-  </si>
-  <si>
-    <t>&lt;6</t>
-  </si>
-  <si>
-    <t>Martín Pérez</t>
-  </si>
-  <si>
-    <t>Atlanta Braves @ Milwaukee Brewers</t>
-  </si>
-  <si>
-    <t>Logan Henderson</t>
-  </si>
-  <si>
-    <t>6-7</t>
-  </si>
-  <si>
-    <t>Jake Irvin</t>
-  </si>
-  <si>
-    <t>Washington Nationals @ Miami Marlins</t>
-  </si>
-  <si>
-    <t>Eury Pérez</t>
-  </si>
-  <si>
-    <t>Andrew Painter</t>
-  </si>
-  <si>
-    <t>St. Louis Cardinals @ Philadelphia Phillies</t>
   </si>
   <si>
     <t>Shane McClanahan</t>
@@ -824,7 +824,7 @@
         <v>42</v>
       </c>
       <c r="I2">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="J2" t="b">
         <v>0</v>
@@ -836,22 +836,22 @@
         <v>6</v>
       </c>
       <c r="M2">
-        <v>0.3635</v>
+        <v>0.3652</v>
       </c>
       <c r="N2">
         <v>5</v>
       </c>
       <c r="O2">
-        <v>126</v>
+        <v>107</v>
       </c>
       <c r="P2">
-        <v>4.02</v>
+        <v>4.01</v>
       </c>
       <c r="Q2">
-        <v>0.3651</v>
+        <v>0.3645</v>
       </c>
       <c r="R2">
-        <v>0.387</v>
+        <v>0.349</v>
       </c>
       <c r="S2" t="s">
         <v>43</v>
@@ -869,7 +869,7 @@
         <v>0.2473</v>
       </c>
       <c r="X2">
-        <v>0.2198</v>
+        <v>0.2211</v>
       </c>
       <c r="Y2">
         <v>1.0348</v>
@@ -881,22 +881,22 @@
         <v>44</v>
       </c>
       <c r="AD2">
-        <v>11.31</v>
+        <v>11.02</v>
       </c>
       <c r="AE2" t="s">
         <v>45</v>
       </c>
       <c r="AF2">
-        <v>0.3641</v>
+        <v>0.365</v>
       </c>
       <c r="AG2">
-        <v>1.2484</v>
+        <v>1.2412</v>
       </c>
       <c r="AH2">
         <v>0</v>
       </c>
       <c r="AM2">
-        <v>11.31</v>
+        <v>11.02</v>
       </c>
     </row>
     <row r="3" spans="1:39" x14ac:dyDescent="0.25">
@@ -925,7 +925,7 @@
         <v>42</v>
       </c>
       <c r="I3">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="J3" t="b">
         <v>0</v>
@@ -937,31 +937,31 @@
         <v>6</v>
       </c>
       <c r="M3">
-        <v>0.2541</v>
+        <v>0.2518</v>
       </c>
       <c r="N3">
         <v>5</v>
       </c>
       <c r="O3">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="P3">
-        <v>4.11</v>
+        <v>4.14</v>
       </c>
       <c r="Q3">
-        <v>0.2101</v>
+        <v>0.1875</v>
       </c>
       <c r="R3">
-        <v>0.373</v>
+        <v>0.359</v>
       </c>
       <c r="S3" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="T3">
-        <v>0.2041</v>
+        <v>0.1953</v>
       </c>
       <c r="U3">
-        <v>0.191</v>
+        <v>0.177</v>
       </c>
       <c r="V3">
         <v>9</v>
@@ -970,10 +970,10 @@
         <v>0.2108</v>
       </c>
       <c r="X3">
-        <v>0.2198</v>
+        <v>0.2211</v>
       </c>
       <c r="Y3">
-        <v>0.9765</v>
+        <v>0.943</v>
       </c>
       <c r="AA3" t="s">
         <v>44</v>
@@ -982,22 +982,22 @@
         <v>44</v>
       </c>
       <c r="AD3">
-        <v>4.95</v>
+        <v>4.33</v>
       </c>
       <c r="AE3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="AF3">
-        <v>0.2377</v>
+        <v>0.2287</v>
       </c>
       <c r="AG3">
-        <v>0.9282</v>
+        <v>0.8833</v>
       </c>
       <c r="AH3">
         <v>0</v>
       </c>
       <c r="AM3">
-        <v>4.95</v>
+        <v>4.33</v>
       </c>
     </row>
     <row r="4" spans="1:39" x14ac:dyDescent="0.25">
@@ -1005,10 +1005,10 @@
         <v>39</v>
       </c>
       <c r="B4" t="s">
+        <v>48</v>
+      </c>
+      <c r="F4" t="s">
         <v>49</v>
-      </c>
-      <c r="F4" t="s">
-        <v>50</v>
       </c>
       <c r="G4">
         <v>823743</v>
@@ -1017,7 +1017,7 @@
         <v>42</v>
       </c>
       <c r="I4">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="J4" t="b">
         <v>0</v>
@@ -1029,22 +1029,22 @@
         <v>0</v>
       </c>
       <c r="M4">
-        <v>0.1824</v>
+        <v>0.1814</v>
       </c>
       <c r="N4">
         <v>5</v>
       </c>
       <c r="O4">
-        <v>106</v>
+        <v>90</v>
       </c>
       <c r="P4">
         <v>4.09</v>
       </c>
       <c r="Q4">
-        <v>0.1698</v>
+        <v>0.1667</v>
       </c>
       <c r="R4">
-        <v>0.346</v>
+        <v>0.31</v>
       </c>
       <c r="S4" t="s">
         <v>43</v>
@@ -1059,10 +1059,10 @@
         <v>9</v>
       </c>
       <c r="W4">
-        <v>0.2223</v>
+        <v>0.2218</v>
       </c>
       <c r="X4">
-        <v>0.2198</v>
+        <v>0.2211</v>
       </c>
       <c r="Y4">
         <v>0.9813</v>
@@ -1074,22 +1074,22 @@
         <v>44</v>
       </c>
       <c r="AD4">
-        <v>3.75</v>
+        <v>3.59</v>
       </c>
       <c r="AE4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="AF4">
-        <v>0.1781</v>
+        <v>0.1768</v>
       </c>
       <c r="AG4">
-        <v>1.0291</v>
+        <v>1.0232</v>
       </c>
       <c r="AH4">
         <v>0</v>
       </c>
       <c r="AM4">
-        <v>3.75</v>
+        <v>3.59</v>
       </c>
     </row>
     <row r="5" spans="1:39" x14ac:dyDescent="0.25">
@@ -1097,7 +1097,7 @@
         <v>39</v>
       </c>
       <c r="B5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C5">
         <v>6.5</v>
@@ -1109,7 +1109,7 @@
         <v>-112</v>
       </c>
       <c r="F5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G5">
         <v>823743</v>
@@ -1118,7 +1118,7 @@
         <v>42</v>
       </c>
       <c r="I5">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="J5" t="b">
         <v>0</v>
@@ -1130,22 +1130,22 @@
         <v>6</v>
       </c>
       <c r="M5">
-        <v>0.3125</v>
+        <v>0.3068</v>
       </c>
       <c r="N5">
         <v>5</v>
       </c>
       <c r="O5">
-        <v>112</v>
+        <v>102</v>
       </c>
       <c r="P5">
-        <v>3.79</v>
+        <v>3.82</v>
       </c>
       <c r="Q5">
-        <v>0.3304</v>
+        <v>0.2941</v>
       </c>
       <c r="R5">
-        <v>0.359</v>
+        <v>0.338</v>
       </c>
       <c r="S5" t="s">
         <v>43</v>
@@ -1163,7 +1163,7 @@
         <v>0.2201</v>
       </c>
       <c r="X5">
-        <v>0.2198</v>
+        <v>0.2211</v>
       </c>
       <c r="Y5">
         <v>0.9745</v>
@@ -1175,22 +1175,22 @@
         <v>44</v>
       </c>
       <c r="AD5">
-        <v>6.32</v>
+        <v>5.76</v>
       </c>
       <c r="AE5" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="AF5">
-        <v>0.3189</v>
+        <v>0.3025</v>
       </c>
       <c r="AG5">
-        <v>1.0172</v>
+        <v>1.0113</v>
       </c>
       <c r="AH5">
-        <v>0.17</v>
+        <v>0</v>
       </c>
       <c r="AM5">
-        <v>6.49</v>
+        <v>5.76</v>
       </c>
     </row>
     <row r="6" spans="1:39" x14ac:dyDescent="0.25">
@@ -1198,7 +1198,7 @@
         <v>39</v>
       </c>
       <c r="B6" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C6">
         <v>4.5</v>
@@ -1210,7 +1210,7 @@
         <v>-110</v>
       </c>
       <c r="F6" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="G6">
         <v>823831</v>
@@ -1264,7 +1264,7 @@
         <v>0.2121</v>
       </c>
       <c r="X6">
-        <v>0.2198</v>
+        <v>0.2211</v>
       </c>
       <c r="Y6">
         <v>0.9201</v>
@@ -1276,22 +1276,22 @@
         <v>44</v>
       </c>
       <c r="AD6">
-        <v>4.4</v>
+        <v>4.37</v>
       </c>
       <c r="AE6" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="AF6">
         <v>0.2226</v>
       </c>
       <c r="AG6">
-        <v>1.0291</v>
+        <v>1.0231</v>
       </c>
       <c r="AH6">
         <v>0</v>
       </c>
       <c r="AM6">
-        <v>4.4</v>
+        <v>4.37</v>
       </c>
     </row>
     <row r="7" spans="1:39" x14ac:dyDescent="0.25">
@@ -1299,10 +1299,10 @@
         <v>39</v>
       </c>
       <c r="B7" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="F7" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="G7">
         <v>823831</v>
@@ -1341,13 +1341,13 @@
         <v>0.381</v>
       </c>
       <c r="S7" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="T7">
-        <v>0.2359</v>
+        <v>0.2447</v>
       </c>
       <c r="U7">
-        <v>0.2361</v>
+        <v>0.2368</v>
       </c>
       <c r="V7">
         <v>9</v>
@@ -1356,10 +1356,10 @@
         <v>0.2076</v>
       </c>
       <c r="X7">
-        <v>0.2198</v>
+        <v>0.2211</v>
       </c>
       <c r="Y7">
-        <v>1.017</v>
+        <v>1.0251</v>
       </c>
       <c r="AA7" t="s">
         <v>44</v>
@@ -1368,22 +1368,22 @@
         <v>44</v>
       </c>
       <c r="AD7">
-        <v>6.29</v>
+        <v>6.53</v>
       </c>
       <c r="AE7" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="AF7">
         <v>0.2565</v>
       </c>
       <c r="AG7">
-        <v>1.0731</v>
+        <v>1.1066</v>
       </c>
       <c r="AH7">
         <v>0.17</v>
       </c>
       <c r="AM7">
-        <v>6.46</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="8" spans="1:39" x14ac:dyDescent="0.25">
@@ -1391,7 +1391,7 @@
         <v>39</v>
       </c>
       <c r="B8" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C8">
         <v>3.5</v>
@@ -1403,7 +1403,7 @@
         <v>125</v>
       </c>
       <c r="F8" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G8">
         <v>823422</v>
@@ -1442,7 +1442,7 @@
         <v>0.329</v>
       </c>
       <c r="S8" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="T8">
         <v>0.1971</v>
@@ -1457,7 +1457,7 @@
         <v>0.2137</v>
       </c>
       <c r="X8">
-        <v>0.2198</v>
+        <v>0.2211</v>
       </c>
       <c r="Y8">
         <v>0.9561</v>
@@ -1469,22 +1469,22 @@
         <v>44</v>
       </c>
       <c r="AD8">
-        <v>3.53</v>
+        <v>3.51</v>
       </c>
       <c r="AE8" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="AF8">
         <v>0.1949</v>
       </c>
       <c r="AG8">
-        <v>0.8966</v>
+        <v>0.8914</v>
       </c>
       <c r="AH8">
         <v>0</v>
       </c>
       <c r="AM8">
-        <v>3.53</v>
+        <v>3.51</v>
       </c>
     </row>
     <row r="9" spans="1:39" x14ac:dyDescent="0.25">
@@ -1543,7 +1543,7 @@
         <v>0.313</v>
       </c>
       <c r="S9" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="T9">
         <v>0.2544</v>
@@ -1558,7 +1558,7 @@
         <v>0.2573</v>
       </c>
       <c r="X9">
-        <v>0.2198</v>
+        <v>0.2211</v>
       </c>
       <c r="Y9">
         <v>1.0201</v>
@@ -1570,22 +1570,22 @@
         <v>44</v>
       </c>
       <c r="AD9">
-        <v>5.02</v>
+        <v>4.99</v>
       </c>
       <c r="AE9" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="AF9">
         <v>0.2111</v>
       </c>
       <c r="AG9">
-        <v>1.1574</v>
+        <v>1.1507</v>
       </c>
       <c r="AH9">
         <v>0</v>
       </c>
       <c r="AM9">
-        <v>5.02</v>
+        <v>4.99</v>
       </c>
     </row>
     <row r="10" spans="1:39" x14ac:dyDescent="0.25">
@@ -1644,7 +1644,7 @@
         <v>0.369</v>
       </c>
       <c r="S10" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="T10">
         <v>0.1734</v>
@@ -1659,7 +1659,7 @@
         <v>0.189</v>
       </c>
       <c r="X10">
-        <v>0.2198</v>
+        <v>0.2211</v>
       </c>
       <c r="Y10">
         <v>0.9097</v>
@@ -1671,22 +1671,22 @@
         <v>44</v>
       </c>
       <c r="AD10">
-        <v>3.27</v>
+        <v>3.25</v>
       </c>
       <c r="AE10" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="AF10">
         <v>0.1889</v>
       </c>
       <c r="AG10">
-        <v>0.7889</v>
+        <v>0.7843</v>
       </c>
       <c r="AH10">
         <v>0</v>
       </c>
       <c r="AM10">
-        <v>3.27</v>
+        <v>3.25</v>
       </c>
     </row>
     <row r="11" spans="1:39" x14ac:dyDescent="0.25">
@@ -1745,7 +1745,7 @@
         <v>0.338</v>
       </c>
       <c r="S11" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="T11">
         <v>0.2425</v>
@@ -1760,7 +1760,7 @@
         <v>0.2245</v>
       </c>
       <c r="X11">
-        <v>0.2198</v>
+        <v>0.2211</v>
       </c>
       <c r="Y11">
         <v>1.0122</v>
@@ -1772,22 +1772,22 @@
         <v>44</v>
       </c>
       <c r="AD11">
-        <v>3.96</v>
+        <v>3.93</v>
       </c>
       <c r="AE11" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="AF11">
         <v>0.1711</v>
       </c>
       <c r="AG11">
-        <v>1.103</v>
+        <v>1.0966</v>
       </c>
       <c r="AH11">
         <v>0</v>
       </c>
       <c r="AM11">
-        <v>3.96</v>
+        <v>3.93</v>
       </c>
     </row>
     <row r="12" spans="1:39" x14ac:dyDescent="0.25">
@@ -1846,7 +1846,7 @@
         <v>0.245</v>
       </c>
       <c r="S12" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="T12">
         <v>0.2715</v>
@@ -1861,7 +1861,7 @@
         <v>0.2562</v>
       </c>
       <c r="X12">
-        <v>0.2198</v>
+        <v>0.2211</v>
       </c>
       <c r="Y12">
         <v>1.0326</v>
@@ -1873,22 +1873,22 @@
         <v>44</v>
       </c>
       <c r="AD12">
-        <v>4.25</v>
+        <v>4.23</v>
       </c>
       <c r="AE12" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="AF12">
         <v>0.1538</v>
       </c>
       <c r="AG12">
-        <v>1.2348</v>
+        <v>1.2276</v>
       </c>
       <c r="AH12">
         <v>0</v>
       </c>
       <c r="AM12">
-        <v>4.25</v>
+        <v>4.23</v>
       </c>
     </row>
     <row r="13" spans="1:39" x14ac:dyDescent="0.25">
@@ -1947,7 +1947,7 @@
         <v>0.365</v>
       </c>
       <c r="S13" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="T13">
         <v>0.2099</v>
@@ -1962,7 +1962,7 @@
         <v>0.2052</v>
       </c>
       <c r="X13">
-        <v>0.2198</v>
+        <v>0.2211</v>
       </c>
       <c r="Y13">
         <v>0.9727</v>
@@ -1974,22 +1974,22 @@
         <v>44</v>
       </c>
       <c r="AD13">
-        <v>4.51</v>
+        <v>4.49</v>
       </c>
       <c r="AE13" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="AF13">
         <v>0.2315</v>
       </c>
       <c r="AG13">
-        <v>0.9549</v>
+        <v>0.9494</v>
       </c>
       <c r="AH13">
         <v>0</v>
       </c>
       <c r="AM13">
-        <v>4.51</v>
+        <v>4.49</v>
       </c>
     </row>
     <row r="14" spans="1:39" x14ac:dyDescent="0.25">
@@ -2048,7 +2048,7 @@
         <v>0.363</v>
       </c>
       <c r="S14" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="T14">
         <v>0.2489</v>
@@ -2063,7 +2063,7 @@
         <v>0.2118</v>
       </c>
       <c r="X14">
-        <v>0.2198</v>
+        <v>0.2211</v>
       </c>
       <c r="Y14">
         <v>1.0462</v>
@@ -2075,22 +2075,22 @@
         <v>44</v>
       </c>
       <c r="AD14">
-        <v>6.63</v>
+        <v>6.59</v>
       </c>
       <c r="AE14" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="AF14">
         <v>0.25</v>
       </c>
       <c r="AG14">
-        <v>1.1321</v>
+        <v>1.1255</v>
       </c>
       <c r="AH14">
         <v>0.17</v>
       </c>
       <c r="AM14">
-        <v>6.8</v>
+        <v>6.76</v>
       </c>
     </row>
     <row r="15" spans="1:39" x14ac:dyDescent="0.25">
@@ -2149,7 +2149,7 @@
         <v>0.363</v>
       </c>
       <c r="S15" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="T15">
         <v>0.2196</v>
@@ -2164,7 +2164,7 @@
         <v>0.2358</v>
       </c>
       <c r="X15">
-        <v>0.2198</v>
+        <v>0.2211</v>
       </c>
       <c r="Y15">
         <v>1.04</v>
@@ -2176,22 +2176,22 @@
         <v>44</v>
       </c>
       <c r="AD15">
-        <v>6.09</v>
+        <v>6.05</v>
       </c>
       <c r="AE15" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="AF15">
         <v>0.2873</v>
       </c>
       <c r="AG15">
-        <v>0.999</v>
+        <v>0.9931</v>
       </c>
       <c r="AH15">
         <v>0.17</v>
       </c>
       <c r="AM15">
-        <v>6.26</v>
+        <v>6.22</v>
       </c>
     </row>
     <row r="16" spans="1:39" x14ac:dyDescent="0.25">
@@ -2250,7 +2250,7 @@
         <v>0.371</v>
       </c>
       <c r="S16" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="T16">
         <v>0.2182</v>
@@ -2265,7 +2265,7 @@
         <v>0.2247</v>
       </c>
       <c r="X16">
-        <v>0.2198</v>
+        <v>0.2211</v>
       </c>
       <c r="Y16">
         <v>0.9823</v>
@@ -2277,22 +2277,22 @@
         <v>44</v>
       </c>
       <c r="AD16">
-        <v>4.29</v>
+        <v>4.27</v>
       </c>
       <c r="AE16" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="AF16">
         <v>0.1923</v>
       </c>
       <c r="AG16">
-        <v>0.9926</v>
+        <v>0.9868</v>
       </c>
       <c r="AH16">
         <v>0</v>
       </c>
       <c r="AM16">
-        <v>4.29</v>
+        <v>4.27</v>
       </c>
     </row>
     <row r="17" spans="1:39" x14ac:dyDescent="0.25">
@@ -2351,13 +2351,13 @@
         <v>0.288</v>
       </c>
       <c r="S17" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="T17">
-        <v>0.1781</v>
+        <v>0.1852</v>
       </c>
       <c r="U17">
-        <v>0.1894</v>
+        <v>0.1917</v>
       </c>
       <c r="V17">
         <v>9</v>
@@ -2366,10 +2366,10 @@
         <v>0.2081</v>
       </c>
       <c r="X17">
-        <v>0.2198</v>
+        <v>0.2211</v>
       </c>
       <c r="Y17">
-        <v>0.9478</v>
+        <v>0.8912</v>
       </c>
       <c r="AA17" t="s">
         <v>44</v>
@@ -2378,22 +2378,22 @@
         <v>44</v>
       </c>
       <c r="AD17">
-        <v>3.47</v>
+        <v>3.38</v>
       </c>
       <c r="AE17" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="AF17">
         <v>0.2641</v>
       </c>
       <c r="AG17">
-        <v>0.8101</v>
+        <v>0.8375</v>
       </c>
       <c r="AH17">
         <v>0</v>
       </c>
       <c r="AM17">
-        <v>3.47</v>
+        <v>3.38</v>
       </c>
     </row>
     <row r="18" spans="1:39" x14ac:dyDescent="0.25">
@@ -2452,7 +2452,7 @@
         <v>0.379</v>
       </c>
       <c r="S18" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="T18">
         <v>0.1901</v>
@@ -2467,7 +2467,7 @@
         <v>0.2227</v>
       </c>
       <c r="X18">
-        <v>0.2198</v>
+        <v>0.2211</v>
       </c>
       <c r="Y18">
         <v>0.9792</v>
@@ -2479,22 +2479,22 @@
         <v>44</v>
       </c>
       <c r="AD18">
-        <v>3.79</v>
+        <v>3.77</v>
       </c>
       <c r="AE18" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="AF18">
         <v>0.1769</v>
       </c>
       <c r="AG18">
-        <v>0.8648</v>
+        <v>0.8598</v>
       </c>
       <c r="AH18">
         <v>0</v>
       </c>
       <c r="AM18">
-        <v>3.79</v>
+        <v>3.77</v>
       </c>
     </row>
     <row r="19" spans="1:39" x14ac:dyDescent="0.25">
@@ -2553,7 +2553,7 @@
         <v>0.346</v>
       </c>
       <c r="S19" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="T19">
         <v>0.302</v>
@@ -2568,7 +2568,7 @@
         <v>0.2068</v>
       </c>
       <c r="X19">
-        <v>0.2198</v>
+        <v>0.2211</v>
       </c>
       <c r="Y19">
         <v>1.0015</v>
@@ -2580,22 +2580,22 @@
         <v>44</v>
       </c>
       <c r="AD19">
-        <v>6.7</v>
+        <v>6.66</v>
       </c>
       <c r="AE19" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="AF19">
         <v>0.2534</v>
       </c>
       <c r="AG19">
-        <v>1.3736</v>
+        <v>1.3656</v>
       </c>
       <c r="AH19">
         <v>0.17</v>
       </c>
       <c r="AM19">
-        <v>6.87</v>
+        <v>6.83</v>
       </c>
     </row>
     <row r="20" spans="1:39" x14ac:dyDescent="0.25">
@@ -2654,7 +2654,7 @@
         <v>0.385</v>
       </c>
       <c r="S20" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="T20">
         <v>0.2012</v>
@@ -2669,7 +2669,7 @@
         <v>0.2559</v>
       </c>
       <c r="X20">
-        <v>0.2198</v>
+        <v>0.2211</v>
       </c>
       <c r="Y20">
         <v>1.0139</v>
@@ -2681,22 +2681,22 @@
         <v>44</v>
       </c>
       <c r="AD20">
-        <v>6.54</v>
+        <v>6.5</v>
       </c>
       <c r="AE20" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="AF20">
         <v>0.3001</v>
       </c>
       <c r="AG20">
-        <v>0.9154</v>
+        <v>0.9101</v>
       </c>
       <c r="AH20">
         <v>0.17</v>
       </c>
       <c r="AM20">
-        <v>6.71</v>
+        <v>6.67</v>
       </c>
     </row>
     <row r="21" spans="1:39" x14ac:dyDescent="0.25">
@@ -2755,7 +2755,7 @@
         <v>0.377</v>
       </c>
       <c r="S21" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="T21">
         <v>0.2274</v>
@@ -2770,7 +2770,7 @@
         <v>0.2401</v>
       </c>
       <c r="X21">
-        <v>0.2198</v>
+        <v>0.2211</v>
       </c>
       <c r="Y21">
         <v>0.9856</v>
@@ -2782,22 +2782,22 @@
         <v>44</v>
       </c>
       <c r="AD21">
-        <v>4.42</v>
+        <v>4.4</v>
       </c>
       <c r="AE21" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="AF21">
         <v>0.1915</v>
       </c>
       <c r="AG21">
-        <v>1.0343</v>
+        <v>1.0282</v>
       </c>
       <c r="AH21">
         <v>0</v>
       </c>
       <c r="AM21">
-        <v>4.42</v>
+        <v>4.4</v>
       </c>
     </row>
     <row r="22" spans="1:39" x14ac:dyDescent="0.25">
@@ -2856,7 +2856,7 @@
         <v>0.24</v>
       </c>
       <c r="S22" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="T22">
         <v>0.1806</v>
@@ -2871,7 +2871,7 @@
         <v>0.2142</v>
       </c>
       <c r="X22">
-        <v>0.2198</v>
+        <v>0.2211</v>
       </c>
       <c r="Y22">
         <v>0.9828</v>
@@ -2883,22 +2883,22 @@
         <v>44</v>
       </c>
       <c r="AD22">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="AE22" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="AF22">
         <v>0.1763</v>
       </c>
       <c r="AG22">
-        <v>0.8215</v>
+        <v>0.8167</v>
       </c>
       <c r="AH22">
         <v>0</v>
       </c>
       <c r="AM22">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
     </row>
     <row r="23" spans="1:39" x14ac:dyDescent="0.25">
@@ -2957,7 +2957,7 @@
         <v>0.371</v>
       </c>
       <c r="S23" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="T23">
         <v>0.2149</v>
@@ -2972,7 +2972,7 @@
         <v>0.2353</v>
       </c>
       <c r="X23">
-        <v>0.2198</v>
+        <v>0.2211</v>
       </c>
       <c r="Y23">
         <v>0.9898</v>
@@ -2984,22 +2984,22 @@
         <v>44</v>
       </c>
       <c r="AD23">
-        <v>4.78</v>
+        <v>4.75</v>
       </c>
       <c r="AE23" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="AF23">
         <v>0.2162</v>
       </c>
       <c r="AG23">
-        <v>0.9774</v>
+        <v>0.9717</v>
       </c>
       <c r="AH23">
         <v>0</v>
       </c>
       <c r="AM23">
-        <v>4.78</v>
+        <v>4.75</v>
       </c>
     </row>
     <row r="24" spans="1:39" x14ac:dyDescent="0.25">
@@ -3058,7 +3058,7 @@
         <v>0.369</v>
       </c>
       <c r="S24" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="T24">
         <v>0.1657</v>
@@ -3073,7 +3073,7 @@
         <v>0.1988</v>
       </c>
       <c r="X24">
-        <v>0.2198</v>
+        <v>0.2211</v>
       </c>
       <c r="Y24">
         <v>0.9037</v>
@@ -3085,22 +3085,22 @@
         <v>44</v>
       </c>
       <c r="AD24">
-        <v>2.72</v>
+        <v>2.71</v>
       </c>
       <c r="AE24" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="AF24">
         <v>0.1807</v>
       </c>
       <c r="AG24">
-        <v>0.7536</v>
+        <v>0.7492</v>
       </c>
       <c r="AH24">
         <v>0</v>
       </c>
       <c r="AM24">
-        <v>2.72</v>
+        <v>2.71</v>
       </c>
     </row>
     <row r="25" spans="1:39" x14ac:dyDescent="0.25">
@@ -3159,7 +3159,7 @@
         <v>0.322</v>
       </c>
       <c r="S25" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="T25">
         <v>0.2819</v>
@@ -3174,7 +3174,7 @@
         <v>0.2557</v>
       </c>
       <c r="X25">
-        <v>0.2198</v>
+        <v>0.2211</v>
       </c>
       <c r="Y25">
         <v>1.0246</v>
@@ -3186,22 +3186,22 @@
         <v>44</v>
       </c>
       <c r="AD25">
-        <v>6.77</v>
+        <v>6.73</v>
       </c>
       <c r="AE25" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="AF25">
         <v>0.2337</v>
       </c>
       <c r="AG25">
-        <v>1.2823</v>
+        <v>1.2748</v>
       </c>
       <c r="AH25">
         <v>0.17</v>
       </c>
       <c r="AM25">
-        <v>6.94</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="26" spans="1:39" x14ac:dyDescent="0.25">
@@ -3260,7 +3260,7 @@
         <v>0.396</v>
       </c>
       <c r="S26" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="T26">
         <v>0.2347</v>
@@ -3275,7 +3275,7 @@
         <v>0.2178</v>
       </c>
       <c r="X26">
-        <v>0.2198</v>
+        <v>0.2211</v>
       </c>
       <c r="Y26">
         <v>0.9978</v>
@@ -3287,22 +3287,22 @@
         <v>44</v>
       </c>
       <c r="AD26">
-        <v>4.79</v>
+        <v>4.77</v>
       </c>
       <c r="AE26" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="AF26">
         <v>0.1909</v>
       </c>
       <c r="AG26">
-        <v>1.0678</v>
+        <v>1.0616</v>
       </c>
       <c r="AH26">
         <v>0</v>
       </c>
       <c r="AM26">
-        <v>4.79</v>
+        <v>4.77</v>
       </c>
     </row>
     <row r="27" spans="1:39" x14ac:dyDescent="0.25">
@@ -3361,7 +3361,7 @@
         <v>0.351</v>
       </c>
       <c r="S27" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="T27">
         <v>0.217</v>
@@ -3376,7 +3376,7 @@
         <v>0.2137</v>
       </c>
       <c r="X27">
-        <v>0.2198</v>
+        <v>0.2211</v>
       </c>
       <c r="Y27">
         <v>0.9237</v>
@@ -3388,22 +3388,22 @@
         <v>44</v>
       </c>
       <c r="AD27">
-        <v>3.78</v>
+        <v>3.76</v>
       </c>
       <c r="AE27" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="AF27">
         <v>0.1924</v>
       </c>
       <c r="AG27">
-        <v>0.9871</v>
+        <v>0.9813</v>
       </c>
       <c r="AH27">
         <v>0</v>
       </c>
       <c r="AM27">
-        <v>3.78</v>
+        <v>3.76</v>
       </c>
     </row>
     <row r="28" spans="1:39" x14ac:dyDescent="0.25">
@@ -3462,7 +3462,7 @@
         <v>0.363</v>
       </c>
       <c r="S28" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="T28">
         <v>0.1876</v>
@@ -3477,7 +3477,7 @@
         <v>0.2166</v>
       </c>
       <c r="X28">
-        <v>0.2198</v>
+        <v>0.2211</v>
       </c>
       <c r="Y28">
         <v>0.9947</v>
@@ -3489,22 +3489,22 @@
         <v>44</v>
       </c>
       <c r="AD28">
-        <v>4.27</v>
+        <v>4.25</v>
       </c>
       <c r="AE28" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="AF28">
         <v>0.232</v>
       </c>
       <c r="AG28">
-        <v>0.8532</v>
+        <v>0.8483</v>
       </c>
       <c r="AH28">
         <v>0</v>
       </c>
       <c r="AM28">
-        <v>4.27</v>
+        <v>4.25</v>
       </c>
     </row>
     <row r="29" spans="1:39" x14ac:dyDescent="0.25">
@@ -3563,7 +3563,7 @@
         <v>0.342</v>
       </c>
       <c r="S29" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="T29">
         <v>0.1983</v>
@@ -3578,7 +3578,7 @@
         <v>0.2101</v>
       </c>
       <c r="X29">
-        <v>0.2198</v>
+        <v>0.2211</v>
       </c>
       <c r="Y29">
         <v>0.9967</v>
@@ -3590,22 +3590,22 @@
         <v>44</v>
       </c>
       <c r="AD29">
-        <v>4.1</v>
+        <v>4.08</v>
       </c>
       <c r="AE29" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="AF29">
         <v>0.2124</v>
       </c>
       <c r="AG29">
-        <v>0.9022</v>
+        <v>0.8969</v>
       </c>
       <c r="AH29">
         <v>0</v>
       </c>
       <c r="AM29">
-        <v>4.1</v>
+        <v>4.08</v>
       </c>
     </row>
     <row r="30" spans="1:39" x14ac:dyDescent="0.25">
@@ -3625,7 +3625,7 @@
         <v>-110</v>
       </c>
       <c r="F30" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G30" t="s">
         <v>44</v>
@@ -3669,7 +3669,7 @@
         <v>-132</v>
       </c>
       <c r="F31" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="G31" t="s">
         <v>44</v>
@@ -3713,7 +3713,7 @@
         <v>108</v>
       </c>
       <c r="F32" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G32" t="s">
         <v>44</v>

--- a/data/k-props/2026-08-22.xlsx
+++ b/data/k-props/2026-08-22.xlsx
@@ -133,30 +133,153 @@
     <t>08/22/2026</t>
   </si>
   <si>
+    <t>Eury Perez</t>
+  </si>
+  <si>
+    <t>Washington Nationals @ Miami Marlins</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Jake Irvin</t>
+  </si>
+  <si>
+    <t>Traditional starter</t>
+  </si>
+  <si>
+    <t>lineup_unweighted_30d_posted</t>
+  </si>
+  <si>
+    <t>&lt;6</t>
+  </si>
+  <si>
+    <t>Quinn Mathews</t>
+  </si>
+  <si>
+    <t>St. Louis Cardinals @ Philadelphia Phillies</t>
+  </si>
+  <si>
+    <t>Andrew Painter</t>
+  </si>
+  <si>
+    <t>Shane McClanahan</t>
+  </si>
+  <si>
+    <t>Tampa Bay Rays @ Baltimore Orioles</t>
+  </si>
+  <si>
+    <t>Brandon Young</t>
+  </si>
+  <si>
+    <t>Cody Bradford</t>
+  </si>
+  <si>
+    <t>Los Angeles Angels @ Texas Rangers</t>
+  </si>
+  <si>
+    <t>lineup_unweighted_30d_projected_regulars</t>
+  </si>
+  <si>
+    <t>Ryan Johnson</t>
+  </si>
+  <si>
+    <t>Christian Scott</t>
+  </si>
+  <si>
+    <t>New York Mets @ Chicago White Sox</t>
+  </si>
+  <si>
+    <t>6-7</t>
+  </si>
+  <si>
+    <t>Luis Castillo</t>
+  </si>
+  <si>
+    <t>Hunter Brown</t>
+  </si>
+  <si>
+    <t>Athletics @ Houston Astros</t>
+  </si>
+  <si>
+    <t>Jacob Lopez</t>
+  </si>
+  <si>
+    <t>Patrick Sandoval</t>
+  </si>
+  <si>
+    <t>San Francisco Giants @ Boston Red Sox</t>
+  </si>
+  <si>
+    <t>Blade Tidwell</t>
+  </si>
+  <si>
+    <t>David Peterson</t>
+  </si>
+  <si>
+    <t>Chicago Cubs @ Seattle Mariners</t>
+  </si>
+  <si>
+    <t>Drew Anderson</t>
+  </si>
+  <si>
+    <t>Detroit Tigers @ Kansas City Royals</t>
+  </si>
+  <si>
+    <t>Limited starter</t>
+  </si>
+  <si>
+    <t>Michael Wacha</t>
+  </si>
+  <si>
+    <t>Jared Jones</t>
+  </si>
+  <si>
+    <t>Pittsburgh Pirates @ Los Angeles Dodgers</t>
+  </si>
+  <si>
+    <t>Tarik Skubal</t>
+  </si>
+  <si>
+    <t>&gt;=7</t>
+  </si>
+  <si>
+    <t>Michael Soroka</t>
+  </si>
+  <si>
+    <t>Cincinnati Reds @ Arizona Diamondbacks</t>
+  </si>
+  <si>
+    <t>Rhett Lowder</t>
+  </si>
+  <si>
+    <t>Gabriel Hughes</t>
+  </si>
+  <si>
+    <t>Cleveland Guardians @ Colorado Rockies</t>
+  </si>
+  <si>
+    <t>Tanner Bibee</t>
+  </si>
+  <si>
+    <t>Casey Mize</t>
+  </si>
+  <si>
+    <t>Minnesota Twins @ San Diego Padres</t>
+  </si>
+  <si>
+    <t>Dean Kremer</t>
+  </si>
+  <si>
     <t>Dylan Cease</t>
   </si>
   <si>
     <t>Toronto Blue Jays @ New York Yankees</t>
   </si>
   <si>
-    <t>Traditional starter</t>
-  </si>
-  <si>
-    <t>lineup_unweighted_30d_posted</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>&gt;=7</t>
-  </si>
-  <si>
     <t>Ryan Weathers</t>
   </si>
   <si>
-    <t>&lt;6</t>
-  </si>
-  <si>
     <t>Martín Pérez</t>
   </si>
   <si>
@@ -166,133 +289,10 @@
     <t>Logan Henderson</t>
   </si>
   <si>
-    <t>Jake Irvin</t>
-  </si>
-  <si>
-    <t>Washington Nationals @ Miami Marlins</t>
-  </si>
-  <si>
     <t>Eury Pérez</t>
   </si>
   <si>
-    <t>6-7</t>
-  </si>
-  <si>
-    <t>Andrew Painter</t>
-  </si>
-  <si>
-    <t>St. Louis Cardinals @ Philadelphia Phillies</t>
-  </si>
-  <si>
-    <t>lineup_unweighted_30d_projected_regulars</t>
-  </si>
-  <si>
-    <t>Shane McClanahan</t>
-  </si>
-  <si>
-    <t>Tampa Bay Rays @ Baltimore Orioles</t>
-  </si>
-  <si>
-    <t>Brandon Young</t>
-  </si>
-  <si>
-    <t>Ryan Johnson</t>
-  </si>
-  <si>
-    <t>Los Angeles Angels @ Texas Rangers</t>
-  </si>
-  <si>
-    <t>Cody Bradford</t>
-  </si>
-  <si>
-    <t>Jacob Lopez</t>
-  </si>
-  <si>
-    <t>Athletics @ Houston Astros</t>
-  </si>
-  <si>
-    <t>Hunter Brown</t>
-  </si>
-  <si>
-    <t>Christian Scott</t>
-  </si>
-  <si>
-    <t>New York Mets @ Chicago White Sox</t>
-  </si>
-  <si>
-    <t>Luis Castillo</t>
-  </si>
-  <si>
-    <t>Drew Anderson</t>
-  </si>
-  <si>
-    <t>Detroit Tigers @ Kansas City Royals</t>
-  </si>
-  <si>
-    <t>Limited starter</t>
-  </si>
-  <si>
-    <t>Michael Wacha</t>
-  </si>
-  <si>
-    <t>Jared Jones</t>
-  </si>
-  <si>
-    <t>Pittsburgh Pirates @ Los Angeles Dodgers</t>
-  </si>
-  <si>
-    <t>Tarik Skubal</t>
-  </si>
-  <si>
-    <t>David Peterson</t>
-  </si>
-  <si>
-    <t>Chicago Cubs @ Seattle Mariners</t>
-  </si>
-  <si>
-    <t>Blade Tidwell</t>
-  </si>
-  <si>
-    <t>San Francisco Giants @ Boston Red Sox</t>
-  </si>
-  <si>
-    <t>Patrick Sandoval</t>
-  </si>
-  <si>
-    <t>Rhett Lowder</t>
-  </si>
-  <si>
-    <t>Cincinnati Reds @ Arizona Diamondbacks</t>
-  </si>
-  <si>
-    <t>Michael Soroka</t>
-  </si>
-  <si>
-    <t>Tanner Bibee</t>
-  </si>
-  <si>
-    <t>Cleveland Guardians @ Colorado Rockies</t>
-  </si>
-  <si>
-    <t>Gabriel Hughes</t>
-  </si>
-  <si>
-    <t>Dean Kremer</t>
-  </si>
-  <si>
-    <t>Minnesota Twins @ San Diego Padres</t>
-  </si>
-  <si>
-    <t>Casey Mize</t>
-  </si>
-  <si>
     <t>Martin Perez</t>
-  </si>
-  <si>
-    <t>Eury Perez</t>
-  </si>
-  <si>
-    <t>Quinn Mathews</t>
   </si>
 </sst>
 </file>
@@ -806,97 +806,40 @@
         <v>40</v>
       </c>
       <c r="C2">
-        <v>8.5</v>
+        <v>5.5</v>
       </c>
       <c r="D2">
-        <v>-115</v>
+        <v>-180</v>
       </c>
       <c r="E2">
-        <v>102</v>
+        <v>130</v>
       </c>
       <c r="F2" t="s">
         <v>41</v>
       </c>
-      <c r="G2">
-        <v>823509</v>
+      <c r="G2" t="s">
+        <v>42</v>
       </c>
       <c r="H2" t="s">
         <v>42</v>
       </c>
-      <c r="I2">
-        <v>5.9</v>
-      </c>
-      <c r="J2" t="b">
-        <v>0</v>
-      </c>
-      <c r="K2" t="b">
-        <v>0</v>
-      </c>
       <c r="L2">
-        <v>6</v>
-      </c>
-      <c r="M2">
-        <v>0.3652</v>
-      </c>
-      <c r="N2">
-        <v>5</v>
-      </c>
-      <c r="O2">
-        <v>107</v>
-      </c>
-      <c r="P2">
-        <v>4.01</v>
-      </c>
-      <c r="Q2">
-        <v>0.3645</v>
-      </c>
-      <c r="R2">
-        <v>0.349</v>
+        <v>1</v>
       </c>
       <c r="S2" t="s">
-        <v>43</v>
-      </c>
-      <c r="T2">
-        <v>0.2744</v>
-      </c>
-      <c r="U2">
-        <v>0.2725</v>
-      </c>
-      <c r="V2">
-        <v>9</v>
-      </c>
-      <c r="W2">
-        <v>0.2473</v>
-      </c>
-      <c r="X2">
-        <v>0.2211</v>
-      </c>
-      <c r="Y2">
-        <v>1.0348</v>
+        <v>42</v>
+      </c>
+      <c r="V2" t="s">
+        <v>42</v>
       </c>
       <c r="AA2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AC2" t="s">
-        <v>44</v>
-      </c>
-      <c r="AD2">
-        <v>11.02</v>
+        <v>42</v>
       </c>
       <c r="AE2" t="s">
-        <v>45</v>
-      </c>
-      <c r="AF2">
-        <v>0.365</v>
-      </c>
-      <c r="AG2">
-        <v>1.2412</v>
-      </c>
-      <c r="AH2">
-        <v>0</v>
-      </c>
-      <c r="AM2">
-        <v>11.02</v>
+        <v>42</v>
       </c>
     </row>
     <row r="3" spans="1:39" x14ac:dyDescent="0.25">
@@ -904,28 +847,28 @@
         <v>39</v>
       </c>
       <c r="B3" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="C3">
-        <v>5.5</v>
+        <v>2.5</v>
       </c>
       <c r="D3">
+        <v>-105</v>
+      </c>
+      <c r="E3">
         <v>115</v>
-      </c>
-      <c r="E3">
-        <v>-128</v>
       </c>
       <c r="F3" t="s">
         <v>41</v>
       </c>
       <c r="G3">
-        <v>823509</v>
+        <v>823831</v>
       </c>
       <c r="H3" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I3">
-        <v>5.5</v>
+        <v>4.6</v>
       </c>
       <c r="J3" t="b">
         <v>0</v>
@@ -934,70 +877,70 @@
         <v>0</v>
       </c>
       <c r="L3">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M3">
-        <v>0.2518</v>
+        <v>0.2239</v>
       </c>
       <c r="N3">
         <v>5</v>
       </c>
       <c r="O3">
-        <v>112</v>
+        <v>96</v>
       </c>
       <c r="P3">
-        <v>4.14</v>
+        <v>4.39</v>
       </c>
       <c r="Q3">
-        <v>0.1875</v>
+        <v>0.1458</v>
       </c>
       <c r="R3">
-        <v>0.359</v>
+        <v>0.324</v>
       </c>
       <c r="S3" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="T3">
-        <v>0.1953</v>
+        <v>0.2262</v>
       </c>
       <c r="U3">
-        <v>0.177</v>
+        <v>0.2109</v>
       </c>
       <c r="V3">
         <v>9</v>
       </c>
       <c r="W3">
-        <v>0.2108</v>
+        <v>0.2121</v>
       </c>
       <c r="X3">
-        <v>0.2211</v>
+        <v>0.2179</v>
       </c>
       <c r="Y3">
-        <v>0.943</v>
+        <v>0.9201</v>
       </c>
       <c r="AA3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AC3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AD3">
-        <v>4.33</v>
+        <v>3.87</v>
       </c>
       <c r="AE3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="AF3">
-        <v>0.2287</v>
+        <v>0.1986</v>
       </c>
       <c r="AG3">
-        <v>0.8833</v>
+        <v>1.0382</v>
       </c>
       <c r="AH3">
         <v>0</v>
       </c>
       <c r="AM3">
-        <v>4.33</v>
+        <v>3.87</v>
       </c>
     </row>
     <row r="4" spans="1:39" x14ac:dyDescent="0.25">
@@ -1005,91 +948,43 @@
         <v>39</v>
       </c>
       <c r="B4" t="s">
+        <v>47</v>
+      </c>
+      <c r="C4">
+        <v>4.5</v>
+      </c>
+      <c r="D4">
+        <v>-115</v>
+      </c>
+      <c r="E4">
+        <v>104</v>
+      </c>
+      <c r="F4" t="s">
         <v>48</v>
       </c>
-      <c r="F4" t="s">
-        <v>49</v>
-      </c>
-      <c r="G4">
-        <v>823743</v>
+      <c r="G4" t="s">
+        <v>42</v>
       </c>
       <c r="H4" t="s">
         <v>42</v>
       </c>
-      <c r="I4">
-        <v>5</v>
-      </c>
-      <c r="J4" t="b">
-        <v>0</v>
-      </c>
-      <c r="K4" t="b">
-        <v>0</v>
-      </c>
       <c r="L4">
-        <v>0</v>
-      </c>
-      <c r="M4">
-        <v>0.1814</v>
-      </c>
-      <c r="N4">
-        <v>5</v>
-      </c>
-      <c r="O4">
-        <v>90</v>
-      </c>
-      <c r="P4">
-        <v>4.09</v>
-      </c>
-      <c r="Q4">
-        <v>0.1667</v>
-      </c>
-      <c r="R4">
-        <v>0.31</v>
+        <v>6</v>
       </c>
       <c r="S4" t="s">
-        <v>43</v>
-      </c>
-      <c r="T4">
-        <v>0.2262</v>
-      </c>
-      <c r="U4">
-        <v>0.222</v>
-      </c>
-      <c r="V4">
-        <v>9</v>
-      </c>
-      <c r="W4">
-        <v>0.2218</v>
-      </c>
-      <c r="X4">
-        <v>0.2211</v>
-      </c>
-      <c r="Y4">
-        <v>0.9813</v>
+        <v>42</v>
+      </c>
+      <c r="V4" t="s">
+        <v>42</v>
       </c>
       <c r="AA4" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AC4" t="s">
-        <v>44</v>
-      </c>
-      <c r="AD4">
-        <v>3.59</v>
+        <v>42</v>
       </c>
       <c r="AE4" t="s">
-        <v>47</v>
-      </c>
-      <c r="AF4">
-        <v>0.1768</v>
-      </c>
-      <c r="AG4">
-        <v>1.0232</v>
-      </c>
-      <c r="AH4">
-        <v>0</v>
-      </c>
-      <c r="AM4">
-        <v>3.59</v>
+        <v>42</v>
       </c>
     </row>
     <row r="5" spans="1:39" x14ac:dyDescent="0.25">
@@ -1097,28 +992,28 @@
         <v>39</v>
       </c>
       <c r="B5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C5">
-        <v>6.5</v>
+        <v>3.5</v>
       </c>
       <c r="D5">
-        <v>-106</v>
+        <v>-150</v>
       </c>
       <c r="E5">
-        <v>-112</v>
+        <v>128</v>
       </c>
       <c r="F5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G5">
-        <v>823743</v>
+        <v>823422</v>
       </c>
       <c r="H5" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I5">
-        <v>5.1</v>
+        <v>4.7</v>
       </c>
       <c r="J5" t="b">
         <v>0</v>
@@ -1130,67 +1025,67 @@
         <v>6</v>
       </c>
       <c r="M5">
-        <v>0.3068</v>
+        <v>0.1854</v>
       </c>
       <c r="N5">
         <v>5</v>
       </c>
       <c r="O5">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="P5">
-        <v>3.82</v>
+        <v>4.49</v>
       </c>
       <c r="Q5">
-        <v>0.2941</v>
+        <v>0.2143</v>
       </c>
       <c r="R5">
-        <v>0.338</v>
+        <v>0.329</v>
       </c>
       <c r="S5" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="T5">
-        <v>0.2236</v>
+        <v>0.2004</v>
       </c>
       <c r="U5">
-        <v>0.2244</v>
+        <v>0.1919</v>
       </c>
       <c r="V5">
         <v>9</v>
       </c>
       <c r="W5">
-        <v>0.2201</v>
+        <v>0.2137</v>
       </c>
       <c r="X5">
-        <v>0.2211</v>
+        <v>0.2179</v>
       </c>
       <c r="Y5">
-        <v>0.9745</v>
+        <v>0.8933</v>
       </c>
       <c r="AA5" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AC5" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AD5">
-        <v>5.76</v>
+        <v>3.38</v>
       </c>
       <c r="AE5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="AF5">
-        <v>0.3025</v>
+        <v>0.1949</v>
       </c>
       <c r="AG5">
-        <v>1.0113</v>
+        <v>0.9196</v>
       </c>
       <c r="AH5">
         <v>0</v>
       </c>
       <c r="AM5">
-        <v>5.76</v>
+        <v>3.38</v>
       </c>
     </row>
     <row r="6" spans="1:39" x14ac:dyDescent="0.25">
@@ -1198,28 +1093,28 @@
         <v>39</v>
       </c>
       <c r="B6" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C6">
         <v>4.5</v>
       </c>
       <c r="D6">
-        <v>-102</v>
+        <v>-101</v>
       </c>
       <c r="E6">
-        <v>-110</v>
+        <v>-118</v>
       </c>
       <c r="F6" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G6">
-        <v>823831</v>
+        <v>824798</v>
       </c>
       <c r="H6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I6">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="J6" t="b">
         <v>0</v>
@@ -1228,70 +1123,70 @@
         <v>0</v>
       </c>
       <c r="L6">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M6">
-        <v>0.23</v>
+        <v>0.2222</v>
       </c>
       <c r="N6">
         <v>5</v>
       </c>
       <c r="O6">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="P6">
-        <v>4.39</v>
+        <v>4.13</v>
       </c>
       <c r="Q6">
-        <v>0.2079</v>
+        <v>0.1868</v>
       </c>
       <c r="R6">
-        <v>0.336</v>
+        <v>0.313</v>
       </c>
       <c r="S6" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="T6">
-        <v>0.2262</v>
+        <v>0.2472</v>
       </c>
       <c r="U6">
-        <v>0.2109</v>
+        <v>0.2345</v>
       </c>
       <c r="V6">
         <v>9</v>
       </c>
       <c r="W6">
-        <v>0.2121</v>
+        <v>0.2573</v>
       </c>
       <c r="X6">
-        <v>0.2211</v>
+        <v>0.2179</v>
       </c>
       <c r="Y6">
-        <v>0.9201</v>
+        <v>1.0352</v>
       </c>
       <c r="AA6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AC6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AD6">
-        <v>4.37</v>
+        <v>4.99</v>
       </c>
       <c r="AE6" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="AF6">
-        <v>0.2226</v>
+        <v>0.2111</v>
       </c>
       <c r="AG6">
-        <v>1.0231</v>
+        <v>1.1343</v>
       </c>
       <c r="AH6">
         <v>0</v>
       </c>
       <c r="AM6">
-        <v>4.37</v>
+        <v>4.99</v>
       </c>
     </row>
     <row r="7" spans="1:39" x14ac:dyDescent="0.25">
@@ -1299,16 +1194,25 @@
         <v>39</v>
       </c>
       <c r="B7" t="s">
-        <v>53</v>
+        <v>52</v>
+      </c>
+      <c r="C7">
+        <v>3.5</v>
+      </c>
+      <c r="D7">
+        <v>-135</v>
+      </c>
+      <c r="E7">
+        <v>110</v>
       </c>
       <c r="F7" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G7">
-        <v>823831</v>
+        <v>824798</v>
       </c>
       <c r="H7" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I7">
         <v>5.6</v>
@@ -1320,70 +1224,70 @@
         <v>0</v>
       </c>
       <c r="L7">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M7">
-        <v>0.2692</v>
+        <v>0.1893</v>
       </c>
       <c r="N7">
         <v>5</v>
       </c>
       <c r="O7">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="P7">
-        <v>4.03</v>
+        <v>4.31</v>
       </c>
       <c r="Q7">
-        <v>0.2358</v>
+        <v>0.188</v>
       </c>
       <c r="R7">
-        <v>0.381</v>
+        <v>0.369</v>
       </c>
       <c r="S7" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="T7">
-        <v>0.2447</v>
+        <v>0.1752</v>
       </c>
       <c r="U7">
-        <v>0.2368</v>
+        <v>0.1744</v>
       </c>
       <c r="V7">
         <v>9</v>
       </c>
       <c r="W7">
-        <v>0.2076</v>
+        <v>0.189</v>
       </c>
       <c r="X7">
-        <v>0.2211</v>
+        <v>0.2179</v>
       </c>
       <c r="Y7">
-        <v>1.0251</v>
+        <v>0.88</v>
       </c>
       <c r="AA7" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AC7" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AD7">
-        <v>6.53</v>
+        <v>3.23</v>
       </c>
       <c r="AE7" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="AF7">
-        <v>0.2565</v>
+        <v>0.1889</v>
       </c>
       <c r="AG7">
-        <v>1.1066</v>
+        <v>0.804</v>
       </c>
       <c r="AH7">
-        <v>0.17</v>
+        <v>0</v>
       </c>
       <c r="AM7">
-        <v>6.7</v>
+        <v>3.23</v>
       </c>
     </row>
     <row r="8" spans="1:39" x14ac:dyDescent="0.25">
@@ -1391,28 +1295,28 @@
         <v>39</v>
       </c>
       <c r="B8" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C8">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="D8">
-        <v>-154</v>
+        <v>-142</v>
       </c>
       <c r="E8">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="F8" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="G8">
-        <v>823422</v>
+        <v>822858</v>
       </c>
       <c r="H8" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I8">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="J8" t="b">
         <v>0</v>
@@ -1424,67 +1328,67 @@
         <v>6</v>
       </c>
       <c r="M8">
-        <v>0.1854</v>
+        <v>0.1538</v>
       </c>
       <c r="N8">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O8">
-        <v>98</v>
+        <v>65</v>
       </c>
       <c r="P8">
-        <v>4.49</v>
+        <v>4.24</v>
       </c>
       <c r="Q8">
-        <v>0.2143</v>
+        <v>0.1538</v>
       </c>
       <c r="R8">
-        <v>0.329</v>
+        <v>0.245</v>
       </c>
       <c r="S8" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="T8">
-        <v>0.1971</v>
+        <v>0.2715</v>
       </c>
       <c r="U8">
-        <v>0.1985</v>
+        <v>0.2585</v>
       </c>
       <c r="V8">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W8">
-        <v>0.2137</v>
+        <v>0.2562</v>
       </c>
       <c r="X8">
-        <v>0.2211</v>
+        <v>0.2179</v>
       </c>
       <c r="Y8">
-        <v>0.9561</v>
+        <v>1.0326</v>
       </c>
       <c r="AA8" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AC8" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AD8">
-        <v>3.51</v>
+        <v>4.29</v>
       </c>
       <c r="AE8" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="AF8">
-        <v>0.1949</v>
+        <v>0.1538</v>
       </c>
       <c r="AG8">
-        <v>0.8914</v>
+        <v>1.2458</v>
       </c>
       <c r="AH8">
         <v>0</v>
       </c>
       <c r="AM8">
-        <v>3.51</v>
+        <v>4.29</v>
       </c>
     </row>
     <row r="9" spans="1:39" x14ac:dyDescent="0.25">
@@ -1492,28 +1396,28 @@
         <v>39</v>
       </c>
       <c r="B9" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C9">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="D9">
-        <v>103</v>
+        <v>-149</v>
       </c>
       <c r="E9">
-        <v>-125</v>
+        <v>129</v>
       </c>
       <c r="F9" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="G9">
-        <v>824798</v>
+        <v>822858</v>
       </c>
       <c r="H9" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I9">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
       <c r="J9" t="b">
         <v>0</v>
@@ -1522,70 +1426,70 @@
         <v>0</v>
       </c>
       <c r="L9">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M9">
-        <v>0.2222</v>
+        <v>0.1734</v>
       </c>
       <c r="N9">
         <v>5</v>
       </c>
       <c r="O9">
-        <v>91</v>
+        <v>102</v>
       </c>
       <c r="P9">
-        <v>4.13</v>
+        <v>4.49</v>
       </c>
       <c r="Q9">
-        <v>0.1868</v>
+        <v>0.1667</v>
       </c>
       <c r="R9">
-        <v>0.313</v>
+        <v>0.338</v>
       </c>
       <c r="S9" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="T9">
-        <v>0.2544</v>
+        <v>0.2663</v>
       </c>
       <c r="U9">
-        <v>0.2401</v>
+        <v>0.2461</v>
       </c>
       <c r="V9">
         <v>9</v>
       </c>
       <c r="W9">
-        <v>0.2573</v>
+        <v>0.2245</v>
       </c>
       <c r="X9">
-        <v>0.2211</v>
+        <v>0.2179</v>
       </c>
       <c r="Y9">
-        <v>1.0201</v>
+        <v>1.0657</v>
       </c>
       <c r="AA9" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AC9" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AD9">
-        <v>4.99</v>
+        <v>4.62</v>
       </c>
       <c r="AE9" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="AF9">
-        <v>0.2111</v>
+        <v>0.1711</v>
       </c>
       <c r="AG9">
-        <v>1.1507</v>
+        <v>1.222</v>
       </c>
       <c r="AH9">
         <v>0</v>
       </c>
       <c r="AM9">
-        <v>4.99</v>
+        <v>4.62</v>
       </c>
     </row>
     <row r="10" spans="1:39" x14ac:dyDescent="0.25">
@@ -1593,28 +1497,28 @@
         <v>39</v>
       </c>
       <c r="B10" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="C10">
-        <v>3.5</v>
+        <v>5.5</v>
       </c>
       <c r="D10">
-        <v>-125</v>
+        <v>-145</v>
       </c>
       <c r="E10">
-        <v>110</v>
+        <v>126</v>
       </c>
       <c r="F10" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G10">
-        <v>824798</v>
+        <v>824560</v>
       </c>
       <c r="H10" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I10">
-        <v>5.6</v>
+        <v>4.7</v>
       </c>
       <c r="J10" t="b">
         <v>0</v>
@@ -1626,67 +1530,67 @@
         <v>5</v>
       </c>
       <c r="M10">
-        <v>0.1893</v>
+        <v>0.2861</v>
       </c>
       <c r="N10">
         <v>5</v>
       </c>
       <c r="O10">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="P10">
-        <v>4.31</v>
+        <v>4.33</v>
       </c>
       <c r="Q10">
-        <v>0.188</v>
+        <v>0.2895</v>
       </c>
       <c r="R10">
-        <v>0.369</v>
+        <v>0.363</v>
       </c>
       <c r="S10" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="T10">
-        <v>0.1734</v>
+        <v>0.2375</v>
       </c>
       <c r="U10">
-        <v>0.1732</v>
+        <v>0.2438</v>
       </c>
       <c r="V10">
         <v>9</v>
       </c>
       <c r="W10">
-        <v>0.189</v>
+        <v>0.2358</v>
       </c>
       <c r="X10">
-        <v>0.2211</v>
+        <v>0.2179</v>
       </c>
       <c r="Y10">
-        <v>0.9097</v>
+        <v>1.0743</v>
       </c>
       <c r="AA10" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AC10" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AD10">
-        <v>3.25</v>
+        <v>6.86</v>
       </c>
       <c r="AE10" t="s">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="AF10">
-        <v>0.1889</v>
+        <v>0.2873</v>
       </c>
       <c r="AG10">
-        <v>0.7843</v>
+        <v>1.09</v>
       </c>
       <c r="AH10">
-        <v>0</v>
+        <v>0.17</v>
       </c>
       <c r="AM10">
-        <v>3.25</v>
+        <v>7.03</v>
       </c>
     </row>
     <row r="11" spans="1:39" x14ac:dyDescent="0.25">
@@ -1694,28 +1598,28 @@
         <v>39</v>
       </c>
       <c r="B11" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C11">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="D11">
-        <v>-143</v>
+        <v>-113</v>
       </c>
       <c r="E11">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="F11" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="G11">
-        <v>822858</v>
+        <v>824560</v>
       </c>
       <c r="H11" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I11">
-        <v>4.6</v>
+        <v>5.2</v>
       </c>
       <c r="J11" t="b">
         <v>0</v>
@@ -1727,67 +1631,67 @@
         <v>5</v>
       </c>
       <c r="M11">
-        <v>0.1734</v>
+        <v>0.2008</v>
       </c>
       <c r="N11">
         <v>5</v>
       </c>
       <c r="O11">
-        <v>102</v>
+        <v>118</v>
       </c>
       <c r="P11">
-        <v>4.49</v>
+        <v>4.4</v>
       </c>
       <c r="Q11">
-        <v>0.1667</v>
+        <v>0.178</v>
       </c>
       <c r="R11">
-        <v>0.338</v>
+        <v>0.371</v>
       </c>
       <c r="S11" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="T11">
-        <v>0.2425</v>
+        <v>0.2529</v>
       </c>
       <c r="U11">
-        <v>0.2431</v>
+        <v>0.2462</v>
       </c>
       <c r="V11">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W11">
-        <v>0.2245</v>
+        <v>0.2247</v>
       </c>
       <c r="X11">
-        <v>0.2211</v>
+        <v>0.2179</v>
       </c>
       <c r="Y11">
-        <v>1.0122</v>
+        <v>0.9809</v>
       </c>
       <c r="AA11" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AC11" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AD11">
-        <v>3.93</v>
+        <v>5.02</v>
       </c>
       <c r="AE11" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="AF11">
-        <v>0.1711</v>
+        <v>0.1923</v>
       </c>
       <c r="AG11">
-        <v>1.0966</v>
+        <v>1.1607</v>
       </c>
       <c r="AH11">
         <v>0</v>
       </c>
       <c r="AM11">
-        <v>3.93</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="12" spans="1:39" x14ac:dyDescent="0.25">
@@ -1795,28 +1699,28 @@
         <v>39</v>
       </c>
       <c r="B12" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C12">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="D12">
-        <v>-122</v>
+        <v>-128</v>
       </c>
       <c r="E12">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="F12" t="s">
         <v>62</v>
       </c>
       <c r="G12">
-        <v>822858</v>
+        <v>824151</v>
       </c>
       <c r="H12" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I12">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="J12" t="b">
         <v>0</v>
@@ -1828,67 +1732,67 @@
         <v>5</v>
       </c>
       <c r="M12">
-        <v>0.1538</v>
+        <v>0.2474</v>
       </c>
       <c r="N12">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O12">
-        <v>65</v>
+        <v>114</v>
       </c>
       <c r="P12">
         <v>4.24</v>
       </c>
       <c r="Q12">
-        <v>0.1538</v>
+        <v>0.2544</v>
       </c>
       <c r="R12">
-        <v>0.245</v>
+        <v>0.363</v>
       </c>
       <c r="S12" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="T12">
-        <v>0.2715</v>
+        <v>0.1952</v>
       </c>
       <c r="U12">
-        <v>0.2585</v>
+        <v>0.1898</v>
       </c>
       <c r="V12">
         <v>9</v>
       </c>
       <c r="W12">
-        <v>0.2562</v>
+        <v>0.2118</v>
       </c>
       <c r="X12">
-        <v>0.2211</v>
+        <v>0.2179</v>
       </c>
       <c r="Y12">
-        <v>1.0326</v>
+        <v>1.0455</v>
       </c>
       <c r="AA12" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AC12" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AD12">
-        <v>4.23</v>
+        <v>5.24</v>
       </c>
       <c r="AE12" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="AF12">
-        <v>0.1538</v>
+        <v>0.25</v>
       </c>
       <c r="AG12">
-        <v>1.2276</v>
+        <v>0.8957</v>
       </c>
       <c r="AH12">
         <v>0</v>
       </c>
       <c r="AM12">
-        <v>4.23</v>
+        <v>5.24</v>
       </c>
     </row>
     <row r="13" spans="1:39" x14ac:dyDescent="0.25">
@@ -1896,25 +1800,25 @@
         <v>39</v>
       </c>
       <c r="B13" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C13">
         <v>4.5</v>
       </c>
       <c r="D13">
-        <v>-113</v>
+        <v>-110</v>
       </c>
       <c r="E13">
-        <v>-102</v>
+        <v>105</v>
       </c>
       <c r="F13" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="G13">
         <v>824151</v>
       </c>
       <c r="H13" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I13">
         <v>4.7</v>
@@ -1947,49 +1851,49 @@
         <v>0.365</v>
       </c>
       <c r="S13" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="T13">
-        <v>0.2099</v>
+        <v>0.1981</v>
       </c>
       <c r="U13">
-        <v>0.2034</v>
+        <v>0.1966</v>
       </c>
       <c r="V13">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W13">
         <v>0.2052</v>
       </c>
       <c r="X13">
-        <v>0.2211</v>
+        <v>0.2179</v>
       </c>
       <c r="Y13">
-        <v>0.9727</v>
+        <v>0.9272</v>
       </c>
       <c r="AA13" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AC13" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AD13">
-        <v>4.49</v>
+        <v>4.1</v>
       </c>
       <c r="AE13" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="AF13">
         <v>0.2315</v>
       </c>
       <c r="AG13">
-        <v>0.9494</v>
+        <v>0.9093</v>
       </c>
       <c r="AH13">
         <v>0</v>
       </c>
       <c r="AM13">
-        <v>4.49</v>
+        <v>4.1</v>
       </c>
     </row>
     <row r="14" spans="1:39" x14ac:dyDescent="0.25">
@@ -1997,28 +1901,28 @@
         <v>39</v>
       </c>
       <c r="B14" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C14">
-        <v>6.5</v>
+        <v>5.5</v>
       </c>
       <c r="D14">
-        <v>118</v>
+        <v>-110</v>
       </c>
       <c r="E14">
-        <v>-130</v>
+        <v>-110</v>
       </c>
       <c r="F14" t="s">
         <v>65</v>
       </c>
       <c r="G14">
-        <v>824151</v>
+        <v>824718</v>
       </c>
       <c r="H14" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I14">
-        <v>5.3</v>
+        <v>4.9</v>
       </c>
       <c r="J14" t="b">
         <v>0</v>
@@ -2027,70 +1931,70 @@
         <v>0</v>
       </c>
       <c r="L14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M14">
-        <v>0.2474</v>
+        <v>0.2188</v>
       </c>
       <c r="N14">
         <v>5</v>
       </c>
       <c r="O14">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="P14">
-        <v>4.24</v>
+        <v>4.71</v>
       </c>
       <c r="Q14">
-        <v>0.2544</v>
+        <v>0.2119</v>
       </c>
       <c r="R14">
-        <v>0.363</v>
+        <v>0.371</v>
       </c>
       <c r="S14" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="T14">
-        <v>0.2489</v>
+        <v>0.23</v>
       </c>
       <c r="U14">
-        <v>0.2157</v>
+        <v>0.2146</v>
       </c>
       <c r="V14">
         <v>9</v>
       </c>
       <c r="W14">
-        <v>0.2118</v>
+        <v>0.2353</v>
       </c>
       <c r="X14">
-        <v>0.2211</v>
+        <v>0.2179</v>
       </c>
       <c r="Y14">
-        <v>1.0462</v>
+        <v>0.985</v>
       </c>
       <c r="AA14" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AC14" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AD14">
-        <v>6.59</v>
+        <v>5.14</v>
       </c>
       <c r="AE14" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="AF14">
-        <v>0.25</v>
+        <v>0.2162</v>
       </c>
       <c r="AG14">
-        <v>1.1255</v>
+        <v>1.0557</v>
       </c>
       <c r="AH14">
-        <v>0.17</v>
+        <v>0</v>
       </c>
       <c r="AM14">
-        <v>6.76</v>
+        <v>5.14</v>
       </c>
     </row>
     <row r="15" spans="1:39" x14ac:dyDescent="0.25">
@@ -2098,28 +2002,28 @@
         <v>39</v>
       </c>
       <c r="B15" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C15">
-        <v>6.5</v>
+        <v>3.5</v>
       </c>
       <c r="D15">
-        <v>128</v>
+        <v>-113</v>
       </c>
       <c r="E15">
-        <v>-154</v>
+        <v>-105</v>
       </c>
       <c r="F15" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="G15">
-        <v>824560</v>
+        <v>824718</v>
       </c>
       <c r="H15" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I15">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="J15" t="b">
         <v>0</v>
@@ -2128,70 +2032,70 @@
         <v>0</v>
       </c>
       <c r="L15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M15">
-        <v>0.2861</v>
+        <v>0.1818</v>
       </c>
       <c r="N15">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O15">
-        <v>114</v>
+        <v>63</v>
       </c>
       <c r="P15">
-        <v>4.33</v>
+        <v>4.07</v>
       </c>
       <c r="Q15">
-        <v>0.2895</v>
+        <v>0.1587</v>
       </c>
       <c r="R15">
-        <v>0.363</v>
+        <v>0.24</v>
       </c>
       <c r="S15" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="T15">
-        <v>0.2196</v>
+        <v>0.1867</v>
       </c>
       <c r="U15">
-        <v>0.2376</v>
+        <v>0.1921</v>
       </c>
       <c r="V15">
         <v>9</v>
       </c>
       <c r="W15">
-        <v>0.2358</v>
+        <v>0.2142</v>
       </c>
       <c r="X15">
-        <v>0.2211</v>
+        <v>0.2179</v>
       </c>
       <c r="Y15">
-        <v>1.04</v>
+        <v>0.9673</v>
       </c>
       <c r="AA15" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AC15" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AD15">
-        <v>6.05</v>
+        <v>2.98</v>
       </c>
       <c r="AE15" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="AF15">
-        <v>0.2873</v>
+        <v>0.1763</v>
       </c>
       <c r="AG15">
-        <v>0.9931</v>
+        <v>0.857</v>
       </c>
       <c r="AH15">
-        <v>0.17</v>
+        <v>0</v>
       </c>
       <c r="AM15">
-        <v>6.22</v>
+        <v>2.98</v>
       </c>
     </row>
     <row r="16" spans="1:39" x14ac:dyDescent="0.25">
@@ -2199,28 +2103,28 @@
         <v>39</v>
       </c>
       <c r="B16" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C16">
         <v>4.5</v>
       </c>
       <c r="D16">
-        <v>-128</v>
+        <v>115</v>
       </c>
       <c r="E16">
-        <v>109</v>
+        <v>-133</v>
       </c>
       <c r="F16" t="s">
         <v>68</v>
       </c>
       <c r="G16">
-        <v>824560</v>
+        <v>823100</v>
       </c>
       <c r="H16" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I16">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="J16" t="b">
         <v>0</v>
@@ -2229,70 +2133,70 @@
         <v>0</v>
       </c>
       <c r="L16">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M16">
-        <v>0.2008</v>
+        <v>0.1874</v>
       </c>
       <c r="N16">
         <v>5</v>
       </c>
       <c r="O16">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="P16">
-        <v>4.4</v>
+        <v>4.51</v>
       </c>
       <c r="Q16">
-        <v>0.178</v>
+        <v>0.1983</v>
       </c>
       <c r="R16">
-        <v>0.371</v>
+        <v>0.377</v>
       </c>
       <c r="S16" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="T16">
-        <v>0.2182</v>
+        <v>0.1985</v>
       </c>
       <c r="U16">
-        <v>0.2388</v>
+        <v>0.2026</v>
       </c>
       <c r="V16">
         <v>9</v>
       </c>
       <c r="W16">
-        <v>0.2247</v>
+        <v>0.2401</v>
       </c>
       <c r="X16">
-        <v>0.2211</v>
+        <v>0.2179</v>
       </c>
       <c r="Y16">
-        <v>0.9823</v>
+        <v>0.9578</v>
       </c>
       <c r="AA16" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AC16" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AD16">
-        <v>4.27</v>
+        <v>3.79</v>
       </c>
       <c r="AE16" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="AF16">
-        <v>0.1923</v>
+        <v>0.1915</v>
       </c>
       <c r="AG16">
-        <v>0.9868</v>
+        <v>0.9111</v>
       </c>
       <c r="AH16">
         <v>0</v>
       </c>
       <c r="AM16">
-        <v>4.27</v>
+        <v>3.79</v>
       </c>
     </row>
     <row r="17" spans="1:39" x14ac:dyDescent="0.25">
@@ -2300,25 +2204,25 @@
         <v>39</v>
       </c>
       <c r="B17" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C17">
         <v>4.5</v>
       </c>
       <c r="D17">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="E17">
-        <v>-150</v>
+        <v>-160</v>
       </c>
       <c r="F17" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G17">
         <v>824073</v>
       </c>
       <c r="H17" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="I17">
         <v>4</v>
@@ -2351,7 +2255,7 @@
         <v>0.288</v>
       </c>
       <c r="S17" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="T17">
         <v>0.1852</v>
@@ -2366,34 +2270,34 @@
         <v>0.2081</v>
       </c>
       <c r="X17">
-        <v>0.2211</v>
+        <v>0.2179</v>
       </c>
       <c r="Y17">
         <v>0.8912</v>
       </c>
       <c r="AA17" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AC17" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AD17">
-        <v>3.38</v>
+        <v>3.43</v>
       </c>
       <c r="AE17" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="AF17">
         <v>0.2641</v>
       </c>
       <c r="AG17">
-        <v>0.8375</v>
+        <v>0.8498</v>
       </c>
       <c r="AH17">
         <v>0</v>
       </c>
       <c r="AM17">
-        <v>3.38</v>
+        <v>3.43</v>
       </c>
     </row>
     <row r="18" spans="1:39" x14ac:dyDescent="0.25">
@@ -2401,25 +2305,25 @@
         <v>39</v>
       </c>
       <c r="B18" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C18">
         <v>4.5</v>
       </c>
       <c r="D18">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="E18">
-        <v>-140</v>
+        <v>-151</v>
       </c>
       <c r="F18" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G18">
         <v>824073</v>
       </c>
       <c r="H18" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I18">
         <v>6.2</v>
@@ -2452,13 +2356,13 @@
         <v>0.379</v>
       </c>
       <c r="S18" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="T18">
-        <v>0.1901</v>
+        <v>0.1867</v>
       </c>
       <c r="U18">
-        <v>0.1925</v>
+        <v>0.1864</v>
       </c>
       <c r="V18">
         <v>9</v>
@@ -2467,34 +2371,34 @@
         <v>0.2227</v>
       </c>
       <c r="X18">
-        <v>0.2211</v>
+        <v>0.2179</v>
       </c>
       <c r="Y18">
-        <v>0.9792</v>
+        <v>0.9419</v>
       </c>
       <c r="AA18" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AC18" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AD18">
-        <v>3.77</v>
+        <v>3.61</v>
       </c>
       <c r="AE18" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="AF18">
         <v>0.1769</v>
       </c>
       <c r="AG18">
-        <v>0.8598</v>
+        <v>0.8567</v>
       </c>
       <c r="AH18">
         <v>0</v>
       </c>
       <c r="AM18">
-        <v>3.77</v>
+        <v>3.61</v>
       </c>
     </row>
     <row r="19" spans="1:39" x14ac:dyDescent="0.25">
@@ -2502,25 +2406,25 @@
         <v>39</v>
       </c>
       <c r="B19" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C19">
         <v>4.5</v>
       </c>
       <c r="D19">
-        <v>-114</v>
+        <v>-143</v>
       </c>
       <c r="E19">
-        <v>100</v>
+        <v>118</v>
       </c>
       <c r="F19" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G19">
         <v>823910</v>
       </c>
       <c r="H19" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I19">
         <v>4.6</v>
@@ -2532,7 +2436,7 @@
         <v>0</v>
       </c>
       <c r="L19">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M19">
         <v>0.2677</v>
@@ -2553,49 +2457,49 @@
         <v>0.346</v>
       </c>
       <c r="S19" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="T19">
-        <v>0.302</v>
+        <v>0.2208</v>
       </c>
       <c r="U19">
-        <v>0.2</v>
+        <v>0.2068</v>
       </c>
       <c r="V19">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W19">
         <v>0.2068</v>
       </c>
       <c r="X19">
-        <v>0.2211</v>
+        <v>0.2179</v>
       </c>
       <c r="Y19">
-        <v>1.0015</v>
+        <v>0.994</v>
       </c>
       <c r="AA19" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AC19" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AD19">
-        <v>6.66</v>
+        <v>4.9</v>
       </c>
       <c r="AE19" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="AF19">
         <v>0.2534</v>
       </c>
       <c r="AG19">
-        <v>1.3656</v>
+        <v>1.0135</v>
       </c>
       <c r="AH19">
-        <v>0.17</v>
+        <v>0</v>
       </c>
       <c r="AM19">
-        <v>6.83</v>
+        <v>4.9</v>
       </c>
     </row>
     <row r="20" spans="1:39" x14ac:dyDescent="0.25">
@@ -2603,25 +2507,25 @@
         <v>39</v>
       </c>
       <c r="B20" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C20">
         <v>8.5</v>
       </c>
       <c r="D20">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="E20">
-        <v>-114</v>
+        <v>-126</v>
       </c>
       <c r="F20" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G20">
         <v>823910</v>
       </c>
       <c r="H20" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I20">
         <v>6</v>
@@ -2633,7 +2537,7 @@
         <v>0</v>
       </c>
       <c r="L20">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M20">
         <v>0.3027</v>
@@ -2654,13 +2558,13 @@
         <v>0.385</v>
       </c>
       <c r="S20" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="T20">
-        <v>0.2012</v>
+        <v>0.2485</v>
       </c>
       <c r="U20">
-        <v>0.2211</v>
+        <v>0.2409</v>
       </c>
       <c r="V20">
         <v>9</v>
@@ -2669,34 +2573,34 @@
         <v>0.2559</v>
       </c>
       <c r="X20">
-        <v>0.2211</v>
+        <v>0.2179</v>
       </c>
       <c r="Y20">
-        <v>1.0139</v>
+        <v>1.1003</v>
       </c>
       <c r="AA20" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AC20" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AD20">
-        <v>6.5</v>
+        <v>8.84</v>
       </c>
       <c r="AE20" t="s">
-        <v>54</v>
+        <v>76</v>
       </c>
       <c r="AF20">
         <v>0.3001</v>
       </c>
       <c r="AG20">
-        <v>0.9101</v>
+        <v>1.1404</v>
       </c>
       <c r="AH20">
-        <v>0.17</v>
+        <v>0</v>
       </c>
       <c r="AM20">
-        <v>6.67</v>
+        <v>8.84</v>
       </c>
     </row>
     <row r="21" spans="1:39" x14ac:dyDescent="0.25">
@@ -2707,25 +2611,25 @@
         <v>77</v>
       </c>
       <c r="C21">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="D21">
-        <v>108</v>
+        <v>-150</v>
       </c>
       <c r="E21">
-        <v>-130</v>
+        <v>124</v>
       </c>
       <c r="F21" t="s">
         <v>78</v>
       </c>
       <c r="G21">
-        <v>823100</v>
+        <v>825044</v>
       </c>
       <c r="H21" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I21">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="J21" t="b">
         <v>0</v>
@@ -2734,70 +2638,70 @@
         <v>0</v>
       </c>
       <c r="L21">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M21">
-        <v>0.1874</v>
+        <v>0.2347</v>
       </c>
       <c r="N21">
         <v>5</v>
       </c>
       <c r="O21">
-        <v>121</v>
+        <v>95</v>
       </c>
       <c r="P21">
-        <v>4.51</v>
+        <v>4.08</v>
       </c>
       <c r="Q21">
-        <v>0.1983</v>
+        <v>0.2316</v>
       </c>
       <c r="R21">
-        <v>0.377</v>
+        <v>0.322</v>
       </c>
       <c r="S21" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="T21">
-        <v>0.2274</v>
+        <v>0.2819</v>
       </c>
       <c r="U21">
-        <v>0.2111</v>
+        <v>0.2818</v>
       </c>
       <c r="V21">
         <v>9</v>
       </c>
       <c r="W21">
-        <v>0.2401</v>
+        <v>0.2557</v>
       </c>
       <c r="X21">
-        <v>0.2211</v>
+        <v>0.2179</v>
       </c>
       <c r="Y21">
-        <v>0.9856</v>
+        <v>1.0246</v>
       </c>
       <c r="AA21" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AC21" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AD21">
-        <v>4.4</v>
+        <v>6.83</v>
       </c>
       <c r="AE21" t="s">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="AF21">
-        <v>0.1915</v>
+        <v>0.2337</v>
       </c>
       <c r="AG21">
-        <v>1.0282</v>
+        <v>1.2936</v>
       </c>
       <c r="AH21">
-        <v>0</v>
+        <v>0.17</v>
       </c>
       <c r="AM21">
-        <v>4.4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="22" spans="1:39" x14ac:dyDescent="0.25">
@@ -2811,22 +2715,22 @@
         <v>3.5</v>
       </c>
       <c r="D22">
-        <v>-120</v>
+        <v>102</v>
       </c>
       <c r="E22">
-        <v>105</v>
+        <v>-115</v>
       </c>
       <c r="F22" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="G22">
-        <v>824718</v>
+        <v>825044</v>
       </c>
       <c r="H22" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I22">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="J22" t="b">
         <v>0</v>
@@ -2838,67 +2742,67 @@
         <v>6</v>
       </c>
       <c r="M22">
-        <v>0.1818</v>
+        <v>0.1814</v>
       </c>
       <c r="N22">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O22">
-        <v>63</v>
+        <v>117</v>
       </c>
       <c r="P22">
-        <v>4.07</v>
+        <v>4.48</v>
       </c>
       <c r="Q22">
-        <v>0.1587</v>
+        <v>0.1795</v>
       </c>
       <c r="R22">
-        <v>0.24</v>
+        <v>0.369</v>
       </c>
       <c r="S22" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="T22">
-        <v>0.1806</v>
+        <v>0.167</v>
       </c>
       <c r="U22">
-        <v>0.1852</v>
+        <v>0.1663</v>
       </c>
       <c r="V22">
         <v>9</v>
       </c>
       <c r="W22">
-        <v>0.2142</v>
+        <v>0.1988</v>
       </c>
       <c r="X22">
-        <v>0.2211</v>
+        <v>0.2179</v>
       </c>
       <c r="Y22">
-        <v>0.9828</v>
+        <v>0.88</v>
       </c>
       <c r="AA22" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AC22" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AD22">
-        <v>2.88</v>
+        <v>2.7</v>
       </c>
       <c r="AE22" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="AF22">
-        <v>0.1763</v>
+        <v>0.1807</v>
       </c>
       <c r="AG22">
-        <v>0.8167</v>
+        <v>0.7662</v>
       </c>
       <c r="AH22">
         <v>0</v>
       </c>
       <c r="AM22">
-        <v>2.88</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="23" spans="1:39" x14ac:dyDescent="0.25">
@@ -2906,28 +2810,28 @@
         <v>39</v>
       </c>
       <c r="B23" t="s">
+        <v>80</v>
+      </c>
+      <c r="C23">
+        <v>3.5</v>
+      </c>
+      <c r="D23">
+        <v>145</v>
+      </c>
+      <c r="E23">
+        <v>-167</v>
+      </c>
+      <c r="F23" t="s">
         <v>81</v>
       </c>
-      <c r="C23">
-        <v>5.5</v>
-      </c>
-      <c r="D23">
-        <v>-128</v>
-      </c>
-      <c r="E23">
-        <v>118</v>
-      </c>
-      <c r="F23" t="s">
-        <v>80</v>
-      </c>
       <c r="G23">
-        <v>824718</v>
+        <v>824316</v>
       </c>
       <c r="H23" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I23">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="J23" t="b">
         <v>0</v>
@@ -2939,67 +2843,67 @@
         <v>6</v>
       </c>
       <c r="M23">
-        <v>0.2188</v>
+        <v>0.2012</v>
       </c>
       <c r="N23">
         <v>5</v>
       </c>
       <c r="O23">
-        <v>118</v>
+        <v>108</v>
       </c>
       <c r="P23">
-        <v>4.71</v>
+        <v>4.35</v>
       </c>
       <c r="Q23">
-        <v>0.2119</v>
+        <v>0.1759</v>
       </c>
       <c r="R23">
-        <v>0.371</v>
+        <v>0.351</v>
       </c>
       <c r="S23" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="T23">
-        <v>0.2149</v>
+        <v>0.1724</v>
       </c>
       <c r="U23">
-        <v>0.2004</v>
+        <v>0.1742</v>
       </c>
       <c r="V23">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="W23">
-        <v>0.2353</v>
+        <v>0.2137</v>
       </c>
       <c r="X23">
-        <v>0.2211</v>
+        <v>0.2179</v>
       </c>
       <c r="Y23">
-        <v>0.9898</v>
+        <v>0.88</v>
       </c>
       <c r="AA23" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AC23" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AD23">
-        <v>4.75</v>
+        <v>2.89</v>
       </c>
       <c r="AE23" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="AF23">
-        <v>0.2162</v>
+        <v>0.1924</v>
       </c>
       <c r="AG23">
-        <v>0.9717</v>
+        <v>0.791</v>
       </c>
       <c r="AH23">
         <v>0</v>
       </c>
       <c r="AM23">
-        <v>4.75</v>
+        <v>2.89</v>
       </c>
     </row>
     <row r="24" spans="1:39" x14ac:dyDescent="0.25">
@@ -3010,25 +2914,25 @@
         <v>82</v>
       </c>
       <c r="C24">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="D24">
-        <v>-110</v>
+        <v>-102</v>
       </c>
       <c r="E24">
-        <v>-104</v>
+        <v>-113</v>
       </c>
       <c r="F24" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="G24">
-        <v>825044</v>
+        <v>824316</v>
       </c>
       <c r="H24" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I24">
-        <v>4.9</v>
+        <v>5.8</v>
       </c>
       <c r="J24" t="b">
         <v>0</v>
@@ -3040,67 +2944,67 @@
         <v>6</v>
       </c>
       <c r="M24">
-        <v>0.1814</v>
+        <v>0.1909</v>
       </c>
       <c r="N24">
         <v>5</v>
       </c>
       <c r="O24">
-        <v>117</v>
+        <v>131</v>
       </c>
       <c r="P24">
-        <v>4.48</v>
+        <v>4.08</v>
       </c>
       <c r="Q24">
-        <v>0.1795</v>
+        <v>0.1908</v>
       </c>
       <c r="R24">
-        <v>0.369</v>
+        <v>0.396</v>
       </c>
       <c r="S24" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="T24">
-        <v>0.1657</v>
+        <v>0.2188</v>
       </c>
       <c r="U24">
-        <v>0.1668</v>
+        <v>0.2075</v>
       </c>
       <c r="V24">
         <v>9</v>
       </c>
       <c r="W24">
-        <v>0.1988</v>
+        <v>0.2178</v>
       </c>
       <c r="X24">
-        <v>0.2211</v>
+        <v>0.2179</v>
       </c>
       <c r="Y24">
-        <v>0.9037</v>
+        <v>0.9455</v>
       </c>
       <c r="AA24" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AC24" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AD24">
-        <v>2.71</v>
+        <v>4.27</v>
       </c>
       <c r="AE24" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="AF24">
-        <v>0.1807</v>
+        <v>0.1909</v>
       </c>
       <c r="AG24">
-        <v>0.7492</v>
+        <v>1.0043</v>
       </c>
       <c r="AH24">
         <v>0</v>
       </c>
       <c r="AM24">
-        <v>2.71</v>
+        <v>4.27</v>
       </c>
     </row>
     <row r="25" spans="1:39" x14ac:dyDescent="0.25">
@@ -3108,25 +3012,25 @@
         <v>39</v>
       </c>
       <c r="B25" t="s">
+        <v>83</v>
+      </c>
+      <c r="C25">
+        <v>4.5</v>
+      </c>
+      <c r="D25">
+        <v>-108</v>
+      </c>
+      <c r="E25">
+        <v>-102</v>
+      </c>
+      <c r="F25" t="s">
         <v>84</v>
       </c>
-      <c r="C25">
-        <v>5.5</v>
-      </c>
-      <c r="D25">
-        <v>-150</v>
-      </c>
-      <c r="E25">
-        <v>126</v>
-      </c>
-      <c r="F25" t="s">
-        <v>83</v>
-      </c>
       <c r="G25">
-        <v>825044</v>
+        <v>823261</v>
       </c>
       <c r="H25" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I25">
         <v>5.4</v>
@@ -3141,67 +3045,67 @@
         <v>6</v>
       </c>
       <c r="M25">
-        <v>0.2347</v>
+        <v>0.2328</v>
       </c>
       <c r="N25">
         <v>5</v>
       </c>
       <c r="O25">
-        <v>95</v>
+        <v>104</v>
       </c>
       <c r="P25">
-        <v>4.08</v>
+        <v>4</v>
       </c>
       <c r="Q25">
-        <v>0.2316</v>
+        <v>0.1731</v>
       </c>
       <c r="R25">
-        <v>0.322</v>
+        <v>0.342</v>
       </c>
       <c r="S25" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="T25">
-        <v>0.2819</v>
+        <v>0.1983</v>
       </c>
       <c r="U25">
-        <v>0.2818</v>
+        <v>0.1939</v>
       </c>
       <c r="V25">
         <v>9</v>
       </c>
       <c r="W25">
-        <v>0.2557</v>
+        <v>0.2101</v>
       </c>
       <c r="X25">
-        <v>0.2211</v>
+        <v>0.2179</v>
       </c>
       <c r="Y25">
-        <v>1.0246</v>
+        <v>0.9967</v>
       </c>
       <c r="AA25" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AC25" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AD25">
-        <v>6.73</v>
+        <v>4.14</v>
       </c>
       <c r="AE25" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="AF25">
-        <v>0.2337</v>
+        <v>0.2124</v>
       </c>
       <c r="AG25">
-        <v>1.2748</v>
+        <v>0.9102</v>
       </c>
       <c r="AH25">
-        <v>0.17</v>
+        <v>0</v>
       </c>
       <c r="AM25">
-        <v>6.9</v>
+        <v>4.14</v>
       </c>
     </row>
     <row r="26" spans="1:39" x14ac:dyDescent="0.25">
@@ -3215,22 +3119,22 @@
         <v>4.5</v>
       </c>
       <c r="D26">
-        <v>-113</v>
+        <v>107</v>
       </c>
       <c r="E26">
-        <v>-108</v>
+        <v>-128</v>
       </c>
       <c r="F26" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="G26">
-        <v>824316</v>
+        <v>823261</v>
       </c>
       <c r="H26" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I26">
-        <v>5.8</v>
+        <v>5.3</v>
       </c>
       <c r="J26" t="b">
         <v>0</v>
@@ -3242,67 +3146,67 @@
         <v>6</v>
       </c>
       <c r="M26">
-        <v>0.1909</v>
+        <v>0.2442</v>
       </c>
       <c r="N26">
         <v>5</v>
       </c>
       <c r="O26">
-        <v>131</v>
+        <v>114</v>
       </c>
       <c r="P26">
-        <v>4.08</v>
+        <v>4.07</v>
       </c>
       <c r="Q26">
-        <v>0.1908</v>
+        <v>0.2105</v>
       </c>
       <c r="R26">
-        <v>0.396</v>
+        <v>0.363</v>
       </c>
       <c r="S26" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="T26">
-        <v>0.2347</v>
+        <v>0.1876</v>
       </c>
       <c r="U26">
-        <v>0.2264</v>
+        <v>0.1898</v>
       </c>
       <c r="V26">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W26">
-        <v>0.2178</v>
+        <v>0.2166</v>
       </c>
       <c r="X26">
-        <v>0.2211</v>
+        <v>0.2179</v>
       </c>
       <c r="Y26">
-        <v>0.9978</v>
+        <v>0.9947</v>
       </c>
       <c r="AA26" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AC26" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AD26">
-        <v>4.77</v>
+        <v>4.31</v>
       </c>
       <c r="AE26" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="AF26">
-        <v>0.1909</v>
+        <v>0.232</v>
       </c>
       <c r="AG26">
-        <v>1.0616</v>
+        <v>0.8608</v>
       </c>
       <c r="AH26">
         <v>0</v>
       </c>
       <c r="AM26">
-        <v>4.77</v>
+        <v>4.31</v>
       </c>
     </row>
     <row r="27" spans="1:39" x14ac:dyDescent="0.25">
@@ -3310,28 +3214,28 @@
         <v>39</v>
       </c>
       <c r="B27" t="s">
+        <v>86</v>
+      </c>
+      <c r="C27">
+        <v>8.5</v>
+      </c>
+      <c r="D27">
+        <v>-115</v>
+      </c>
+      <c r="E27">
+        <v>102</v>
+      </c>
+      <c r="F27" t="s">
         <v>87</v>
       </c>
-      <c r="C27">
-        <v>3.5</v>
-      </c>
-      <c r="D27">
-        <v>145</v>
-      </c>
-      <c r="E27">
-        <v>-163</v>
-      </c>
-      <c r="F27" t="s">
-        <v>86</v>
-      </c>
       <c r="G27">
-        <v>824316</v>
+        <v>823509</v>
       </c>
       <c r="H27" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I27">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J27" t="b">
         <v>0</v>
@@ -3343,67 +3247,67 @@
         <v>6</v>
       </c>
       <c r="M27">
-        <v>0.2012</v>
+        <v>0.361</v>
       </c>
       <c r="N27">
         <v>5</v>
       </c>
       <c r="O27">
-        <v>108</v>
+        <v>122</v>
       </c>
       <c r="P27">
-        <v>4.35</v>
+        <v>4.01</v>
       </c>
       <c r="Q27">
-        <v>0.1759</v>
+        <v>0.3443</v>
       </c>
       <c r="R27">
-        <v>0.351</v>
+        <v>0.379</v>
       </c>
       <c r="S27" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="T27">
-        <v>0.217</v>
+        <v>0.2744</v>
       </c>
       <c r="U27">
-        <v>0.1926</v>
+        <v>0.2725</v>
       </c>
       <c r="V27">
         <v>9</v>
       </c>
       <c r="W27">
-        <v>0.2137</v>
+        <v>0.2482</v>
       </c>
       <c r="X27">
-        <v>0.2211</v>
+        <v>0.2179</v>
       </c>
       <c r="Y27">
-        <v>0.9237</v>
+        <v>1.0348</v>
       </c>
       <c r="AA27" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AC27" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AD27">
-        <v>3.76</v>
+        <v>11.15</v>
       </c>
       <c r="AE27" t="s">
-        <v>47</v>
+        <v>76</v>
       </c>
       <c r="AF27">
-        <v>0.1924</v>
+        <v>0.3546</v>
       </c>
       <c r="AG27">
-        <v>0.9813</v>
+        <v>1.2595</v>
       </c>
       <c r="AH27">
         <v>0</v>
       </c>
       <c r="AM27">
-        <v>3.76</v>
+        <v>11.15</v>
       </c>
     </row>
     <row r="28" spans="1:39" x14ac:dyDescent="0.25">
@@ -3414,25 +3318,25 @@
         <v>88</v>
       </c>
       <c r="C28">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="D28">
-        <v>102</v>
+        <v>115</v>
       </c>
       <c r="E28">
-        <v>-115</v>
+        <v>-128</v>
       </c>
       <c r="F28" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="G28">
-        <v>823261</v>
+        <v>823509</v>
       </c>
       <c r="H28" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I28">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="J28" t="b">
         <v>0</v>
@@ -3441,70 +3345,70 @@
         <v>0</v>
       </c>
       <c r="L28">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M28">
-        <v>0.2442</v>
+        <v>0.2518</v>
       </c>
       <c r="N28">
         <v>5</v>
       </c>
       <c r="O28">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="P28">
-        <v>4.07</v>
+        <v>4.14</v>
       </c>
       <c r="Q28">
-        <v>0.2105</v>
+        <v>0.1875</v>
       </c>
       <c r="R28">
-        <v>0.363</v>
+        <v>0.359</v>
       </c>
       <c r="S28" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="T28">
-        <v>0.1876</v>
+        <v>0.1953</v>
       </c>
       <c r="U28">
-        <v>0.1898</v>
+        <v>0.177</v>
       </c>
       <c r="V28">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W28">
-        <v>0.2166</v>
+        <v>0.2104</v>
       </c>
       <c r="X28">
-        <v>0.2211</v>
+        <v>0.2179</v>
       </c>
       <c r="Y28">
-        <v>0.9947</v>
+        <v>0.943</v>
       </c>
       <c r="AA28" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AC28" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AD28">
-        <v>4.25</v>
+        <v>4.39</v>
       </c>
       <c r="AE28" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="AF28">
-        <v>0.232</v>
+        <v>0.2287</v>
       </c>
       <c r="AG28">
-        <v>0.8483</v>
+        <v>0.8963</v>
       </c>
       <c r="AH28">
         <v>0</v>
       </c>
       <c r="AM28">
-        <v>4.25</v>
+        <v>4.39</v>
       </c>
     </row>
     <row r="29" spans="1:39" x14ac:dyDescent="0.25">
@@ -3512,28 +3416,19 @@
         <v>39</v>
       </c>
       <c r="B29" t="s">
+        <v>89</v>
+      </c>
+      <c r="F29" t="s">
         <v>90</v>
       </c>
-      <c r="C29">
-        <v>4.5</v>
-      </c>
-      <c r="D29">
-        <v>-122</v>
-      </c>
-      <c r="E29">
-        <v>104</v>
-      </c>
-      <c r="F29" t="s">
-        <v>89</v>
-      </c>
       <c r="G29">
-        <v>823261</v>
+        <v>823743</v>
       </c>
       <c r="H29" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I29">
-        <v>5.4</v>
+        <v>5</v>
       </c>
       <c r="J29" t="b">
         <v>0</v>
@@ -3542,70 +3437,70 @@
         <v>0</v>
       </c>
       <c r="L29">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M29">
-        <v>0.2328</v>
+        <v>0.1789</v>
       </c>
       <c r="N29">
         <v>5</v>
       </c>
       <c r="O29">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="P29">
-        <v>4</v>
+        <v>4.12</v>
       </c>
       <c r="Q29">
-        <v>0.1731</v>
+        <v>0.1569</v>
       </c>
       <c r="R29">
-        <v>0.342</v>
+        <v>0.338</v>
       </c>
       <c r="S29" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="T29">
-        <v>0.1983</v>
+        <v>0.2262</v>
       </c>
       <c r="U29">
-        <v>0.1939</v>
+        <v>0.222</v>
       </c>
       <c r="V29">
         <v>9</v>
       </c>
       <c r="W29">
-        <v>0.2101</v>
+        <v>0.2197</v>
       </c>
       <c r="X29">
-        <v>0.2211</v>
+        <v>0.2179</v>
       </c>
       <c r="Y29">
-        <v>0.9967</v>
+        <v>0.9813</v>
       </c>
       <c r="AA29" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AC29" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AD29">
-        <v>4.08</v>
+        <v>3.63</v>
       </c>
       <c r="AE29" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="AF29">
-        <v>0.2124</v>
+        <v>0.1715</v>
       </c>
       <c r="AG29">
-        <v>0.8969</v>
+        <v>1.0383</v>
       </c>
       <c r="AH29">
         <v>0</v>
       </c>
       <c r="AM29">
-        <v>4.08</v>
+        <v>3.63</v>
       </c>
     </row>
     <row r="30" spans="1:39" x14ac:dyDescent="0.25">
@@ -3616,40 +3511,97 @@
         <v>91</v>
       </c>
       <c r="C30">
-        <v>3.5</v>
+        <v>6.5</v>
       </c>
       <c r="D30">
-        <v>-111</v>
+        <v>-106</v>
       </c>
       <c r="E30">
-        <v>-110</v>
+        <v>-112</v>
       </c>
       <c r="F30" t="s">
-        <v>49</v>
-      </c>
-      <c r="G30" t="s">
-        <v>44</v>
+        <v>90</v>
+      </c>
+      <c r="G30">
+        <v>823743</v>
       </c>
       <c r="H30" t="s">
         <v>44</v>
       </c>
+      <c r="I30">
+        <v>5.3</v>
+      </c>
+      <c r="J30" t="b">
+        <v>0</v>
+      </c>
+      <c r="K30" t="b">
+        <v>0</v>
+      </c>
       <c r="L30">
         <v>6</v>
       </c>
+      <c r="M30">
+        <v>0.2992</v>
+      </c>
+      <c r="N30">
+        <v>5</v>
+      </c>
+      <c r="O30">
+        <v>116</v>
+      </c>
+      <c r="P30">
+        <v>3.81</v>
+      </c>
+      <c r="Q30">
+        <v>0.2759</v>
+      </c>
+      <c r="R30">
+        <v>0.367</v>
+      </c>
       <c r="S30" t="s">
-        <v>44</v>
-      </c>
-      <c r="V30" t="s">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="T30">
+        <v>0.2236</v>
+      </c>
+      <c r="U30">
+        <v>0.2244</v>
+      </c>
+      <c r="V30">
+        <v>9</v>
+      </c>
+      <c r="W30">
+        <v>0.2194</v>
+      </c>
+      <c r="X30">
+        <v>0.2179</v>
+      </c>
+      <c r="Y30">
+        <v>0.9745</v>
       </c>
       <c r="AA30" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AC30" t="s">
-        <v>44</v>
+        <v>42</v>
+      </c>
+      <c r="AD30">
+        <v>5.9</v>
       </c>
       <c r="AE30" t="s">
-        <v>44</v>
+        <v>46</v>
+      </c>
+      <c r="AF30">
+        <v>0.2907</v>
+      </c>
+      <c r="AG30">
+        <v>1.0262</v>
+      </c>
+      <c r="AH30">
+        <v>0</v>
+      </c>
+      <c r="AM30">
+        <v>5.9</v>
       </c>
     </row>
     <row r="31" spans="1:39" x14ac:dyDescent="0.25">
@@ -3659,41 +3611,89 @@
       <c r="B31" t="s">
         <v>92</v>
       </c>
-      <c r="C31">
-        <v>6.5</v>
-      </c>
-      <c r="D31">
-        <v>110</v>
-      </c>
-      <c r="E31">
-        <v>-132</v>
-      </c>
       <c r="F31" t="s">
-        <v>52</v>
-      </c>
-      <c r="G31" t="s">
-        <v>44</v>
+        <v>41</v>
+      </c>
+      <c r="G31">
+        <v>823831</v>
       </c>
       <c r="H31" t="s">
         <v>44</v>
       </c>
+      <c r="I31">
+        <v>5.5</v>
+      </c>
+      <c r="J31" t="b">
+        <v>0</v>
+      </c>
+      <c r="K31" t="b">
+        <v>0</v>
+      </c>
       <c r="L31">
-        <v>6</v>
+        <v>0</v>
+      </c>
+      <c r="M31">
+        <v>0.2693</v>
+      </c>
+      <c r="N31">
+        <v>5</v>
+      </c>
+      <c r="O31">
+        <v>106</v>
+      </c>
+      <c r="P31">
+        <v>4.02</v>
+      </c>
+      <c r="Q31">
+        <v>0.283</v>
+      </c>
+      <c r="R31">
+        <v>0.346</v>
       </c>
       <c r="S31" t="s">
-        <v>44</v>
-      </c>
-      <c r="V31" t="s">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="T31">
+        <v>0.2447</v>
+      </c>
+      <c r="U31">
+        <v>0.2368</v>
+      </c>
+      <c r="V31">
+        <v>9</v>
+      </c>
+      <c r="W31">
+        <v>0.2076</v>
+      </c>
+      <c r="X31">
+        <v>0.2179</v>
+      </c>
+      <c r="Y31">
+        <v>1.0251</v>
       </c>
       <c r="AA31" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AC31" t="s">
-        <v>44</v>
+        <v>42</v>
+      </c>
+      <c r="AD31">
+        <v>6.93</v>
       </c>
       <c r="AE31" t="s">
-        <v>44</v>
+        <v>59</v>
+      </c>
+      <c r="AF31">
+        <v>0.2741</v>
+      </c>
+      <c r="AG31">
+        <v>1.123</v>
+      </c>
+      <c r="AH31">
+        <v>0.17</v>
+      </c>
+      <c r="AM31">
+        <v>7.1</v>
       </c>
     </row>
     <row r="32" spans="1:39" x14ac:dyDescent="0.25">
@@ -3704,40 +3704,40 @@
         <v>93</v>
       </c>
       <c r="C32">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="D32">
-        <v>105</v>
+        <v>-111</v>
       </c>
       <c r="E32">
-        <v>108</v>
+        <v>-110</v>
       </c>
       <c r="F32" t="s">
-        <v>56</v>
+        <v>90</v>
       </c>
       <c r="G32" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="H32" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="L32">
         <v>6</v>
       </c>
       <c r="S32" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="V32" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AA32" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AC32" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AE32" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
   </sheetData>

--- a/data/k-props/2026-08-22.xlsx
+++ b/data/k-props/2026-08-22.xlsx
@@ -133,163 +133,163 @@
     <t>08/22/2026</t>
   </si>
   <si>
+    <t>Dylan Cease</t>
+  </si>
+  <si>
+    <t>Toronto Blue Jays @ New York Yankees</t>
+  </si>
+  <si>
+    <t>Traditional starter</t>
+  </si>
+  <si>
+    <t>lineup_unweighted_30d_posted</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>&gt;=7</t>
+  </si>
+  <si>
+    <t>Ryan Weathers</t>
+  </si>
+  <si>
+    <t>&lt;6</t>
+  </si>
+  <si>
+    <t>Martín Pérez</t>
+  </si>
+  <si>
+    <t>Atlanta Braves @ Milwaukee Brewers</t>
+  </si>
+  <si>
+    <t>Logan Henderson</t>
+  </si>
+  <si>
+    <t>Jake Irvin</t>
+  </si>
+  <si>
+    <t>Washington Nationals @ Miami Marlins</t>
+  </si>
+  <si>
+    <t>Eury Pérez</t>
+  </si>
+  <si>
+    <t>6-7</t>
+  </si>
+  <si>
+    <t>Andrew Painter</t>
+  </si>
+  <si>
+    <t>St. Louis Cardinals @ Philadelphia Phillies</t>
+  </si>
+  <si>
+    <t>Shane McClanahan</t>
+  </si>
+  <si>
+    <t>Tampa Bay Rays @ Baltimore Orioles</t>
+  </si>
+  <si>
+    <t>Brandon Young</t>
+  </si>
+  <si>
+    <t>Ryan Johnson</t>
+  </si>
+  <si>
+    <t>Los Angeles Angels @ Texas Rangers</t>
+  </si>
+  <si>
+    <t>Cody Bradford</t>
+  </si>
+  <si>
+    <t>Jacob Lopez</t>
+  </si>
+  <si>
+    <t>Athletics @ Houston Astros</t>
+  </si>
+  <si>
+    <t>Hunter Brown</t>
+  </si>
+  <si>
+    <t>Christian Scott</t>
+  </si>
+  <si>
+    <t>New York Mets @ Chicago White Sox</t>
+  </si>
+  <si>
+    <t>Luis Castillo</t>
+  </si>
+  <si>
+    <t>Drew Anderson</t>
+  </si>
+  <si>
+    <t>Detroit Tigers @ Kansas City Royals</t>
+  </si>
+  <si>
+    <t>Limited starter</t>
+  </si>
+  <si>
+    <t>Michael Wacha</t>
+  </si>
+  <si>
+    <t>Jared Jones</t>
+  </si>
+  <si>
+    <t>Pittsburgh Pirates @ Los Angeles Dodgers</t>
+  </si>
+  <si>
+    <t>Tarik Skubal</t>
+  </si>
+  <si>
+    <t>David Peterson</t>
+  </si>
+  <si>
+    <t>Chicago Cubs @ Seattle Mariners</t>
+  </si>
+  <si>
+    <t>Blade Tidwell</t>
+  </si>
+  <si>
+    <t>San Francisco Giants @ Boston Red Sox</t>
+  </si>
+  <si>
+    <t>Patrick Sandoval</t>
+  </si>
+  <si>
+    <t>Rhett Lowder</t>
+  </si>
+  <si>
+    <t>Cincinnati Reds @ Arizona Diamondbacks</t>
+  </si>
+  <si>
+    <t>Michael Soroka</t>
+  </si>
+  <si>
+    <t>Tanner Bibee</t>
+  </si>
+  <si>
+    <t>Cleveland Guardians @ Colorado Rockies</t>
+  </si>
+  <si>
+    <t>Gabriel Hughes</t>
+  </si>
+  <si>
+    <t>Dean Kremer</t>
+  </si>
+  <si>
+    <t>Minnesota Twins @ San Diego Padres</t>
+  </si>
+  <si>
+    <t>lineup_unweighted_30d_projected_regulars</t>
+  </si>
+  <si>
+    <t>Casey Mize</t>
+  </si>
+  <si>
     <t>Eury Perez</t>
   </si>
   <si>
-    <t>Washington Nationals @ Miami Marlins</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>Jake Irvin</t>
-  </si>
-  <si>
-    <t>Traditional starter</t>
-  </si>
-  <si>
-    <t>lineup_unweighted_30d_posted</t>
-  </si>
-  <si>
-    <t>&lt;6</t>
-  </si>
-  <si>
     <t>Quinn Mathews</t>
-  </si>
-  <si>
-    <t>St. Louis Cardinals @ Philadelphia Phillies</t>
-  </si>
-  <si>
-    <t>Andrew Painter</t>
-  </si>
-  <si>
-    <t>Shane McClanahan</t>
-  </si>
-  <si>
-    <t>Tampa Bay Rays @ Baltimore Orioles</t>
-  </si>
-  <si>
-    <t>Brandon Young</t>
-  </si>
-  <si>
-    <t>Cody Bradford</t>
-  </si>
-  <si>
-    <t>Los Angeles Angels @ Texas Rangers</t>
-  </si>
-  <si>
-    <t>lineup_unweighted_30d_projected_regulars</t>
-  </si>
-  <si>
-    <t>Ryan Johnson</t>
-  </si>
-  <si>
-    <t>Christian Scott</t>
-  </si>
-  <si>
-    <t>New York Mets @ Chicago White Sox</t>
-  </si>
-  <si>
-    <t>6-7</t>
-  </si>
-  <si>
-    <t>Luis Castillo</t>
-  </si>
-  <si>
-    <t>Hunter Brown</t>
-  </si>
-  <si>
-    <t>Athletics @ Houston Astros</t>
-  </si>
-  <si>
-    <t>Jacob Lopez</t>
-  </si>
-  <si>
-    <t>Patrick Sandoval</t>
-  </si>
-  <si>
-    <t>San Francisco Giants @ Boston Red Sox</t>
-  </si>
-  <si>
-    <t>Blade Tidwell</t>
-  </si>
-  <si>
-    <t>David Peterson</t>
-  </si>
-  <si>
-    <t>Chicago Cubs @ Seattle Mariners</t>
-  </si>
-  <si>
-    <t>Drew Anderson</t>
-  </si>
-  <si>
-    <t>Detroit Tigers @ Kansas City Royals</t>
-  </si>
-  <si>
-    <t>Limited starter</t>
-  </si>
-  <si>
-    <t>Michael Wacha</t>
-  </si>
-  <si>
-    <t>Jared Jones</t>
-  </si>
-  <si>
-    <t>Pittsburgh Pirates @ Los Angeles Dodgers</t>
-  </si>
-  <si>
-    <t>Tarik Skubal</t>
-  </si>
-  <si>
-    <t>&gt;=7</t>
-  </si>
-  <si>
-    <t>Michael Soroka</t>
-  </si>
-  <si>
-    <t>Cincinnati Reds @ Arizona Diamondbacks</t>
-  </si>
-  <si>
-    <t>Rhett Lowder</t>
-  </si>
-  <si>
-    <t>Gabriel Hughes</t>
-  </si>
-  <si>
-    <t>Cleveland Guardians @ Colorado Rockies</t>
-  </si>
-  <si>
-    <t>Tanner Bibee</t>
-  </si>
-  <si>
-    <t>Casey Mize</t>
-  </si>
-  <si>
-    <t>Minnesota Twins @ San Diego Padres</t>
-  </si>
-  <si>
-    <t>Dean Kremer</t>
-  </si>
-  <si>
-    <t>Dylan Cease</t>
-  </si>
-  <si>
-    <t>Toronto Blue Jays @ New York Yankees</t>
-  </si>
-  <si>
-    <t>Ryan Weathers</t>
-  </si>
-  <si>
-    <t>Martín Pérez</t>
-  </si>
-  <si>
-    <t>Atlanta Braves @ Milwaukee Brewers</t>
-  </si>
-  <si>
-    <t>Logan Henderson</t>
-  </si>
-  <si>
-    <t>Eury Pérez</t>
   </si>
   <si>
     <t>Martin Perez</t>
@@ -806,40 +806,97 @@
         <v>40</v>
       </c>
       <c r="C2">
-        <v>5.5</v>
+        <v>8.5</v>
       </c>
       <c r="D2">
-        <v>-180</v>
+        <v>-115</v>
       </c>
       <c r="E2">
-        <v>130</v>
+        <v>102</v>
       </c>
       <c r="F2" t="s">
         <v>41</v>
       </c>
-      <c r="G2" t="s">
-        <v>42</v>
+      <c r="G2">
+        <v>823509</v>
       </c>
       <c r="H2" t="s">
         <v>42</v>
       </c>
+      <c r="I2">
+        <v>6</v>
+      </c>
+      <c r="J2" t="b">
+        <v>0</v>
+      </c>
+      <c r="K2" t="b">
+        <v>0</v>
+      </c>
       <c r="L2">
-        <v>1</v>
+        <v>6</v>
+      </c>
+      <c r="M2">
+        <v>0.361</v>
+      </c>
+      <c r="N2">
+        <v>5</v>
+      </c>
+      <c r="O2">
+        <v>122</v>
+      </c>
+      <c r="P2">
+        <v>4.01</v>
+      </c>
+      <c r="Q2">
+        <v>0.3443</v>
+      </c>
+      <c r="R2">
+        <v>0.379</v>
       </c>
       <c r="S2" t="s">
-        <v>42</v>
-      </c>
-      <c r="V2" t="s">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="T2">
+        <v>0.2744</v>
+      </c>
+      <c r="U2">
+        <v>0.2725</v>
+      </c>
+      <c r="V2">
+        <v>9</v>
+      </c>
+      <c r="W2">
+        <v>0.2482</v>
+      </c>
+      <c r="X2">
+        <v>0.2188</v>
+      </c>
+      <c r="Y2">
+        <v>1.0348</v>
       </c>
       <c r="AA2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AC2" t="s">
-        <v>42</v>
+        <v>44</v>
+      </c>
+      <c r="AD2">
+        <v>11.11</v>
       </c>
       <c r="AE2" t="s">
-        <v>42</v>
+        <v>45</v>
+      </c>
+      <c r="AF2">
+        <v>0.3546</v>
+      </c>
+      <c r="AG2">
+        <v>1.2545</v>
+      </c>
+      <c r="AH2">
+        <v>0</v>
+      </c>
+      <c r="AM2">
+        <v>11.11</v>
       </c>
     </row>
     <row r="3" spans="1:39" x14ac:dyDescent="0.25">
@@ -847,28 +904,28 @@
         <v>39</v>
       </c>
       <c r="B3" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="C3">
-        <v>2.5</v>
+        <v>5.5</v>
       </c>
       <c r="D3">
-        <v>-105</v>
+        <v>115</v>
       </c>
       <c r="E3">
-        <v>115</v>
+        <v>-128</v>
       </c>
       <c r="F3" t="s">
         <v>41</v>
       </c>
       <c r="G3">
-        <v>823831</v>
+        <v>823509</v>
       </c>
       <c r="H3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I3">
-        <v>4.6</v>
+        <v>5.5</v>
       </c>
       <c r="J3" t="b">
         <v>0</v>
@@ -877,70 +934,70 @@
         <v>0</v>
       </c>
       <c r="L3">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="M3">
-        <v>0.2239</v>
+        <v>0.2518</v>
       </c>
       <c r="N3">
         <v>5</v>
       </c>
       <c r="O3">
-        <v>96</v>
+        <v>112</v>
       </c>
       <c r="P3">
-        <v>4.39</v>
+        <v>4.14</v>
       </c>
       <c r="Q3">
-        <v>0.1458</v>
+        <v>0.1875</v>
       </c>
       <c r="R3">
-        <v>0.324</v>
+        <v>0.359</v>
       </c>
       <c r="S3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="T3">
-        <v>0.2262</v>
+        <v>0.1953</v>
       </c>
       <c r="U3">
-        <v>0.2109</v>
+        <v>0.177</v>
       </c>
       <c r="V3">
         <v>9</v>
       </c>
       <c r="W3">
-        <v>0.2121</v>
+        <v>0.2104</v>
       </c>
       <c r="X3">
-        <v>0.2179</v>
+        <v>0.2188</v>
       </c>
       <c r="Y3">
-        <v>0.9201</v>
+        <v>0.943</v>
       </c>
       <c r="AA3" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AC3" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AD3">
-        <v>3.87</v>
+        <v>4.37</v>
       </c>
       <c r="AE3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AF3">
-        <v>0.1986</v>
+        <v>0.2287</v>
       </c>
       <c r="AG3">
-        <v>1.0382</v>
+        <v>0.8927</v>
       </c>
       <c r="AH3">
         <v>0</v>
       </c>
       <c r="AM3">
-        <v>3.87</v>
+        <v>4.37</v>
       </c>
     </row>
     <row r="4" spans="1:39" x14ac:dyDescent="0.25">
@@ -948,43 +1005,91 @@
         <v>39</v>
       </c>
       <c r="B4" t="s">
-        <v>47</v>
-      </c>
-      <c r="C4">
-        <v>4.5</v>
-      </c>
-      <c r="D4">
-        <v>-115</v>
-      </c>
-      <c r="E4">
-        <v>104</v>
+        <v>48</v>
       </c>
       <c r="F4" t="s">
-        <v>48</v>
-      </c>
-      <c r="G4" t="s">
-        <v>42</v>
+        <v>49</v>
+      </c>
+      <c r="G4">
+        <v>823743</v>
       </c>
       <c r="H4" t="s">
         <v>42</v>
       </c>
+      <c r="I4">
+        <v>5</v>
+      </c>
+      <c r="J4" t="b">
+        <v>0</v>
+      </c>
+      <c r="K4" t="b">
+        <v>0</v>
+      </c>
       <c r="L4">
-        <v>6</v>
+        <v>0</v>
+      </c>
+      <c r="M4">
+        <v>0.1789</v>
+      </c>
+      <c r="N4">
+        <v>5</v>
+      </c>
+      <c r="O4">
+        <v>102</v>
+      </c>
+      <c r="P4">
+        <v>4.12</v>
+      </c>
+      <c r="Q4">
+        <v>0.1569</v>
+      </c>
+      <c r="R4">
+        <v>0.338</v>
       </c>
       <c r="S4" t="s">
-        <v>42</v>
-      </c>
-      <c r="V4" t="s">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="T4">
+        <v>0.2262</v>
+      </c>
+      <c r="U4">
+        <v>0.222</v>
+      </c>
+      <c r="V4">
+        <v>9</v>
+      </c>
+      <c r="W4">
+        <v>0.2197</v>
+      </c>
+      <c r="X4">
+        <v>0.2188</v>
+      </c>
+      <c r="Y4">
+        <v>0.9813</v>
       </c>
       <c r="AA4" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AC4" t="s">
-        <v>42</v>
+        <v>44</v>
+      </c>
+      <c r="AD4">
+        <v>3.62</v>
       </c>
       <c r="AE4" t="s">
-        <v>42</v>
+        <v>47</v>
+      </c>
+      <c r="AF4">
+        <v>0.1715</v>
+      </c>
+      <c r="AG4">
+        <v>1.0342</v>
+      </c>
+      <c r="AH4">
+        <v>0</v>
+      </c>
+      <c r="AM4">
+        <v>3.62</v>
       </c>
     </row>
     <row r="5" spans="1:39" x14ac:dyDescent="0.25">
@@ -992,28 +1097,28 @@
         <v>39</v>
       </c>
       <c r="B5" t="s">
+        <v>50</v>
+      </c>
+      <c r="C5">
+        <v>6.5</v>
+      </c>
+      <c r="D5">
+        <v>-106</v>
+      </c>
+      <c r="E5">
+        <v>-112</v>
+      </c>
+      <c r="F5" t="s">
         <v>49</v>
       </c>
-      <c r="C5">
-        <v>3.5</v>
-      </c>
-      <c r="D5">
-        <v>-150</v>
-      </c>
-      <c r="E5">
-        <v>128</v>
-      </c>
-      <c r="F5" t="s">
-        <v>48</v>
-      </c>
       <c r="G5">
-        <v>823422</v>
+        <v>823743</v>
       </c>
       <c r="H5" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I5">
-        <v>4.7</v>
+        <v>5.3</v>
       </c>
       <c r="J5" t="b">
         <v>0</v>
@@ -1025,67 +1130,67 @@
         <v>6</v>
       </c>
       <c r="M5">
-        <v>0.1854</v>
+        <v>0.2992</v>
       </c>
       <c r="N5">
         <v>5</v>
       </c>
       <c r="O5">
-        <v>98</v>
+        <v>116</v>
       </c>
       <c r="P5">
-        <v>4.49</v>
+        <v>3.81</v>
       </c>
       <c r="Q5">
-        <v>0.2143</v>
+        <v>0.2759</v>
       </c>
       <c r="R5">
-        <v>0.329</v>
+        <v>0.367</v>
       </c>
       <c r="S5" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="T5">
-        <v>0.2004</v>
+        <v>0.2236</v>
       </c>
       <c r="U5">
-        <v>0.1919</v>
+        <v>0.2244</v>
       </c>
       <c r="V5">
         <v>9</v>
       </c>
       <c r="W5">
-        <v>0.2137</v>
+        <v>0.2194</v>
       </c>
       <c r="X5">
-        <v>0.2179</v>
+        <v>0.2188</v>
       </c>
       <c r="Y5">
-        <v>0.8933</v>
+        <v>0.9745</v>
       </c>
       <c r="AA5" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AC5" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AD5">
-        <v>3.38</v>
+        <v>5.88</v>
       </c>
       <c r="AE5" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AF5">
-        <v>0.1949</v>
+        <v>0.2907</v>
       </c>
       <c r="AG5">
-        <v>0.9196</v>
+        <v>1.0221</v>
       </c>
       <c r="AH5">
         <v>0</v>
       </c>
       <c r="AM5">
-        <v>3.38</v>
+        <v>5.88</v>
       </c>
     </row>
     <row r="6" spans="1:39" x14ac:dyDescent="0.25">
@@ -1093,28 +1198,28 @@
         <v>39</v>
       </c>
       <c r="B6" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C6">
-        <v>4.5</v>
+        <v>2.5</v>
       </c>
       <c r="D6">
-        <v>-101</v>
+        <v>-105</v>
       </c>
       <c r="E6">
-        <v>-118</v>
+        <v>115</v>
       </c>
       <c r="F6" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G6">
-        <v>824798</v>
+        <v>823831</v>
       </c>
       <c r="H6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I6">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="J6" t="b">
         <v>0</v>
@@ -1123,70 +1228,70 @@
         <v>0</v>
       </c>
       <c r="L6">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="M6">
-        <v>0.2222</v>
+        <v>0.2259</v>
       </c>
       <c r="N6">
         <v>5</v>
       </c>
       <c r="O6">
-        <v>91</v>
+        <v>101</v>
       </c>
       <c r="P6">
-        <v>4.13</v>
+        <v>4.41</v>
       </c>
       <c r="Q6">
-        <v>0.1868</v>
+        <v>0.1485</v>
       </c>
       <c r="R6">
-        <v>0.313</v>
+        <v>0.336</v>
       </c>
       <c r="S6" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="T6">
-        <v>0.2472</v>
+        <v>0.2262</v>
       </c>
       <c r="U6">
-        <v>0.2345</v>
+        <v>0.2109</v>
       </c>
       <c r="V6">
         <v>9</v>
       </c>
       <c r="W6">
-        <v>0.2573</v>
+        <v>0.2121</v>
       </c>
       <c r="X6">
-        <v>0.2179</v>
+        <v>0.2188</v>
       </c>
       <c r="Y6">
-        <v>1.0352</v>
+        <v>0.9201</v>
       </c>
       <c r="AA6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AC6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AD6">
-        <v>4.99</v>
+        <v>3.95</v>
       </c>
       <c r="AE6" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AF6">
-        <v>0.2111</v>
+        <v>0.1999</v>
       </c>
       <c r="AG6">
-        <v>1.1343</v>
+        <v>1.0341</v>
       </c>
       <c r="AH6">
         <v>0</v>
       </c>
       <c r="AM6">
-        <v>4.99</v>
+        <v>3.95</v>
       </c>
     </row>
     <row r="7" spans="1:39" x14ac:dyDescent="0.25">
@@ -1194,28 +1299,19 @@
         <v>39</v>
       </c>
       <c r="B7" t="s">
+        <v>53</v>
+      </c>
+      <c r="F7" t="s">
         <v>52</v>
       </c>
-      <c r="C7">
-        <v>3.5</v>
-      </c>
-      <c r="D7">
-        <v>-135</v>
-      </c>
-      <c r="E7">
-        <v>110</v>
-      </c>
-      <c r="F7" t="s">
-        <v>51</v>
-      </c>
       <c r="G7">
-        <v>824798</v>
+        <v>823831</v>
       </c>
       <c r="H7" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I7">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="J7" t="b">
         <v>0</v>
@@ -1224,70 +1320,70 @@
         <v>0</v>
       </c>
       <c r="L7">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M7">
-        <v>0.1893</v>
+        <v>0.2686</v>
       </c>
       <c r="N7">
         <v>5</v>
       </c>
       <c r="O7">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="P7">
-        <v>4.31</v>
+        <v>4.03</v>
       </c>
       <c r="Q7">
-        <v>0.188</v>
+        <v>0.2793</v>
       </c>
       <c r="R7">
-        <v>0.369</v>
+        <v>0.357</v>
       </c>
       <c r="S7" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="T7">
-        <v>0.1752</v>
+        <v>0.2447</v>
       </c>
       <c r="U7">
-        <v>0.1744</v>
+        <v>0.2368</v>
       </c>
       <c r="V7">
         <v>9</v>
       </c>
       <c r="W7">
-        <v>0.189</v>
+        <v>0.2076</v>
       </c>
       <c r="X7">
-        <v>0.2179</v>
+        <v>0.2188</v>
       </c>
       <c r="Y7">
-        <v>0.88</v>
+        <v>1.0251</v>
       </c>
       <c r="AA7" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AC7" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AD7">
-        <v>3.23</v>
+        <v>6.93</v>
       </c>
       <c r="AE7" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="AF7">
-        <v>0.1889</v>
+        <v>0.2724</v>
       </c>
       <c r="AG7">
-        <v>0.804</v>
+        <v>1.1185</v>
       </c>
       <c r="AH7">
-        <v>0</v>
+        <v>0.17</v>
       </c>
       <c r="AM7">
-        <v>3.23</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="8" spans="1:39" x14ac:dyDescent="0.25">
@@ -1295,28 +1391,28 @@
         <v>39</v>
       </c>
       <c r="B8" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C8">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="D8">
-        <v>-142</v>
+        <v>-150</v>
       </c>
       <c r="E8">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="F8" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="G8">
-        <v>822858</v>
+        <v>823422</v>
       </c>
       <c r="H8" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I8">
-        <v>5.1</v>
+        <v>4.7</v>
       </c>
       <c r="J8" t="b">
         <v>0</v>
@@ -1328,67 +1424,67 @@
         <v>6</v>
       </c>
       <c r="M8">
-        <v>0.1538</v>
+        <v>0.1854</v>
       </c>
       <c r="N8">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O8">
-        <v>65</v>
+        <v>98</v>
       </c>
       <c r="P8">
-        <v>4.24</v>
+        <v>4.49</v>
       </c>
       <c r="Q8">
-        <v>0.1538</v>
+        <v>0.2143</v>
       </c>
       <c r="R8">
-        <v>0.245</v>
+        <v>0.329</v>
       </c>
       <c r="S8" t="s">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="T8">
-        <v>0.2715</v>
+        <v>0.2004</v>
       </c>
       <c r="U8">
-        <v>0.2585</v>
+        <v>0.1919</v>
       </c>
       <c r="V8">
         <v>9</v>
       </c>
       <c r="W8">
-        <v>0.2562</v>
+        <v>0.2137</v>
       </c>
       <c r="X8">
-        <v>0.2179</v>
+        <v>0.2188</v>
       </c>
       <c r="Y8">
-        <v>1.0326</v>
+        <v>0.8933</v>
       </c>
       <c r="AA8" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AC8" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AD8">
-        <v>4.29</v>
+        <v>3.37</v>
       </c>
       <c r="AE8" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AF8">
-        <v>0.1538</v>
+        <v>0.1949</v>
       </c>
       <c r="AG8">
-        <v>1.2458</v>
+        <v>0.916</v>
       </c>
       <c r="AH8">
         <v>0</v>
       </c>
       <c r="AM8">
-        <v>4.29</v>
+        <v>3.37</v>
       </c>
     </row>
     <row r="9" spans="1:39" x14ac:dyDescent="0.25">
@@ -1396,28 +1492,28 @@
         <v>39</v>
       </c>
       <c r="B9" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C9">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="D9">
-        <v>-149</v>
+        <v>-101</v>
       </c>
       <c r="E9">
-        <v>129</v>
+        <v>-118</v>
       </c>
       <c r="F9" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="G9">
-        <v>822858</v>
+        <v>824798</v>
       </c>
       <c r="H9" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I9">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="J9" t="b">
         <v>0</v>
@@ -1426,70 +1522,70 @@
         <v>0</v>
       </c>
       <c r="L9">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M9">
-        <v>0.1734</v>
+        <v>0.2222</v>
       </c>
       <c r="N9">
         <v>5</v>
       </c>
       <c r="O9">
-        <v>102</v>
+        <v>91</v>
       </c>
       <c r="P9">
-        <v>4.49</v>
+        <v>4.13</v>
       </c>
       <c r="Q9">
-        <v>0.1667</v>
+        <v>0.1868</v>
       </c>
       <c r="R9">
-        <v>0.338</v>
+        <v>0.313</v>
       </c>
       <c r="S9" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="T9">
-        <v>0.2663</v>
+        <v>0.2472</v>
       </c>
       <c r="U9">
-        <v>0.2461</v>
+        <v>0.2345</v>
       </c>
       <c r="V9">
         <v>9</v>
       </c>
       <c r="W9">
-        <v>0.2245</v>
+        <v>0.2573</v>
       </c>
       <c r="X9">
-        <v>0.2179</v>
+        <v>0.2188</v>
       </c>
       <c r="Y9">
-        <v>1.0657</v>
+        <v>1.0352</v>
       </c>
       <c r="AA9" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AC9" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AD9">
-        <v>4.62</v>
+        <v>4.97</v>
       </c>
       <c r="AE9" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AF9">
-        <v>0.1711</v>
+        <v>0.2111</v>
       </c>
       <c r="AG9">
-        <v>1.222</v>
+        <v>1.1299</v>
       </c>
       <c r="AH9">
         <v>0</v>
       </c>
       <c r="AM9">
-        <v>4.62</v>
+        <v>4.97</v>
       </c>
     </row>
     <row r="10" spans="1:39" x14ac:dyDescent="0.25">
@@ -1497,28 +1593,28 @@
         <v>39</v>
       </c>
       <c r="B10" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C10">
-        <v>5.5</v>
+        <v>3.5</v>
       </c>
       <c r="D10">
-        <v>-145</v>
+        <v>-135</v>
       </c>
       <c r="E10">
-        <v>126</v>
+        <v>110</v>
       </c>
       <c r="F10" t="s">
         <v>58</v>
       </c>
       <c r="G10">
-        <v>824560</v>
+        <v>824798</v>
       </c>
       <c r="H10" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I10">
-        <v>4.7</v>
+        <v>5.6</v>
       </c>
       <c r="J10" t="b">
         <v>0</v>
@@ -1530,67 +1626,67 @@
         <v>5</v>
       </c>
       <c r="M10">
-        <v>0.2861</v>
+        <v>0.1893</v>
       </c>
       <c r="N10">
         <v>5</v>
       </c>
       <c r="O10">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="P10">
-        <v>4.33</v>
+        <v>4.31</v>
       </c>
       <c r="Q10">
-        <v>0.2895</v>
+        <v>0.188</v>
       </c>
       <c r="R10">
-        <v>0.363</v>
+        <v>0.369</v>
       </c>
       <c r="S10" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="T10">
-        <v>0.2375</v>
+        <v>0.1752</v>
       </c>
       <c r="U10">
-        <v>0.2438</v>
+        <v>0.1744</v>
       </c>
       <c r="V10">
         <v>9</v>
       </c>
       <c r="W10">
-        <v>0.2358</v>
+        <v>0.189</v>
       </c>
       <c r="X10">
-        <v>0.2179</v>
+        <v>0.2188</v>
       </c>
       <c r="Y10">
-        <v>1.0743</v>
+        <v>0.88</v>
       </c>
       <c r="AA10" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AC10" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AD10">
-        <v>6.86</v>
+        <v>3.21</v>
       </c>
       <c r="AE10" t="s">
-        <v>59</v>
+        <v>47</v>
       </c>
       <c r="AF10">
-        <v>0.2873</v>
+        <v>0.1889</v>
       </c>
       <c r="AG10">
-        <v>1.09</v>
+        <v>0.8009</v>
       </c>
       <c r="AH10">
-        <v>0.17</v>
+        <v>0</v>
       </c>
       <c r="AM10">
-        <v>7.03</v>
+        <v>3.21</v>
       </c>
     </row>
     <row r="11" spans="1:39" x14ac:dyDescent="0.25">
@@ -1601,25 +1697,25 @@
         <v>60</v>
       </c>
       <c r="C11">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="D11">
-        <v>-113</v>
+        <v>-149</v>
       </c>
       <c r="E11">
-        <v>100</v>
+        <v>129</v>
       </c>
       <c r="F11" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="G11">
-        <v>824560</v>
+        <v>822858</v>
       </c>
       <c r="H11" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I11">
-        <v>5.2</v>
+        <v>4.6</v>
       </c>
       <c r="J11" t="b">
         <v>0</v>
@@ -1628,70 +1724,70 @@
         <v>0</v>
       </c>
       <c r="L11">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M11">
-        <v>0.2008</v>
+        <v>0.1734</v>
       </c>
       <c r="N11">
         <v>5</v>
       </c>
       <c r="O11">
-        <v>118</v>
+        <v>102</v>
       </c>
       <c r="P11">
-        <v>4.4</v>
+        <v>4.49</v>
       </c>
       <c r="Q11">
-        <v>0.178</v>
+        <v>0.1667</v>
       </c>
       <c r="R11">
-        <v>0.371</v>
+        <v>0.338</v>
       </c>
       <c r="S11" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="T11">
-        <v>0.2529</v>
+        <v>0.2663</v>
       </c>
       <c r="U11">
-        <v>0.2462</v>
+        <v>0.2461</v>
       </c>
       <c r="V11">
         <v>9</v>
       </c>
       <c r="W11">
-        <v>0.2247</v>
+        <v>0.2245</v>
       </c>
       <c r="X11">
-        <v>0.2179</v>
+        <v>0.2188</v>
       </c>
       <c r="Y11">
-        <v>0.9809</v>
+        <v>1.0657</v>
       </c>
       <c r="AA11" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AC11" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AD11">
-        <v>5.02</v>
+        <v>4.6</v>
       </c>
       <c r="AE11" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AF11">
-        <v>0.1923</v>
+        <v>0.1711</v>
       </c>
       <c r="AG11">
-        <v>1.1607</v>
+        <v>1.2172</v>
       </c>
       <c r="AH11">
         <v>0</v>
       </c>
       <c r="AM11">
-        <v>5.02</v>
+        <v>4.6</v>
       </c>
     </row>
     <row r="12" spans="1:39" x14ac:dyDescent="0.25">
@@ -1699,28 +1795,28 @@
         <v>39</v>
       </c>
       <c r="B12" t="s">
+        <v>62</v>
+      </c>
+      <c r="C12">
+        <v>4.5</v>
+      </c>
+      <c r="D12">
+        <v>-142</v>
+      </c>
+      <c r="E12">
+        <v>121</v>
+      </c>
+      <c r="F12" t="s">
         <v>61</v>
       </c>
-      <c r="C12">
-        <v>5.5</v>
-      </c>
-      <c r="D12">
-        <v>-128</v>
-      </c>
-      <c r="E12">
-        <v>111</v>
-      </c>
-      <c r="F12" t="s">
-        <v>62</v>
-      </c>
       <c r="G12">
-        <v>824151</v>
+        <v>822858</v>
       </c>
       <c r="H12" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I12">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="J12" t="b">
         <v>0</v>
@@ -1729,70 +1825,70 @@
         <v>0</v>
       </c>
       <c r="L12">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M12">
-        <v>0.2474</v>
+        <v>0.1538</v>
       </c>
       <c r="N12">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O12">
-        <v>114</v>
+        <v>65</v>
       </c>
       <c r="P12">
         <v>4.24</v>
       </c>
       <c r="Q12">
-        <v>0.2544</v>
+        <v>0.1538</v>
       </c>
       <c r="R12">
-        <v>0.363</v>
+        <v>0.245</v>
       </c>
       <c r="S12" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="T12">
-        <v>0.1952</v>
+        <v>0.3002</v>
       </c>
       <c r="U12">
-        <v>0.1898</v>
+        <v>0.2881</v>
       </c>
       <c r="V12">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="W12">
-        <v>0.2118</v>
+        <v>0.2562</v>
       </c>
       <c r="X12">
-        <v>0.2179</v>
+        <v>0.2188</v>
       </c>
       <c r="Y12">
-        <v>1.0455</v>
+        <v>1.0991</v>
       </c>
       <c r="AA12" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AC12" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AD12">
-        <v>5.24</v>
+        <v>5.03</v>
       </c>
       <c r="AE12" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AF12">
-        <v>0.25</v>
+        <v>0.1538</v>
       </c>
       <c r="AG12">
-        <v>0.8957</v>
+        <v>1.3724</v>
       </c>
       <c r="AH12">
         <v>0</v>
       </c>
       <c r="AM12">
-        <v>5.24</v>
+        <v>5.03</v>
       </c>
     </row>
     <row r="13" spans="1:39" x14ac:dyDescent="0.25">
@@ -1812,13 +1908,13 @@
         <v>105</v>
       </c>
       <c r="F13" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="G13">
         <v>824151</v>
       </c>
       <c r="H13" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I13">
         <v>4.7</v>
@@ -1851,7 +1947,7 @@
         <v>0.365</v>
       </c>
       <c r="S13" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="T13">
         <v>0.1981</v>
@@ -1866,34 +1962,34 @@
         <v>0.2052</v>
       </c>
       <c r="X13">
-        <v>0.2179</v>
+        <v>0.2188</v>
       </c>
       <c r="Y13">
         <v>0.9272</v>
       </c>
       <c r="AA13" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AC13" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AD13">
-        <v>4.1</v>
+        <v>4.08</v>
       </c>
       <c r="AE13" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AF13">
         <v>0.2315</v>
       </c>
       <c r="AG13">
-        <v>0.9093</v>
+        <v>0.9057</v>
       </c>
       <c r="AH13">
         <v>0</v>
       </c>
       <c r="AM13">
-        <v>4.1</v>
+        <v>4.08</v>
       </c>
     </row>
     <row r="14" spans="1:39" x14ac:dyDescent="0.25">
@@ -1901,28 +1997,28 @@
         <v>39</v>
       </c>
       <c r="B14" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C14">
         <v>5.5</v>
       </c>
       <c r="D14">
-        <v>-110</v>
+        <v>-128</v>
       </c>
       <c r="E14">
-        <v>-110</v>
+        <v>111</v>
       </c>
       <c r="F14" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G14">
-        <v>824718</v>
+        <v>824151</v>
       </c>
       <c r="H14" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I14">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="J14" t="b">
         <v>0</v>
@@ -1931,70 +2027,70 @@
         <v>0</v>
       </c>
       <c r="L14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M14">
-        <v>0.2188</v>
+        <v>0.2474</v>
       </c>
       <c r="N14">
         <v>5</v>
       </c>
       <c r="O14">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="P14">
-        <v>4.71</v>
+        <v>4.24</v>
       </c>
       <c r="Q14">
-        <v>0.2119</v>
+        <v>0.2544</v>
       </c>
       <c r="R14">
-        <v>0.371</v>
+        <v>0.363</v>
       </c>
       <c r="S14" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="T14">
-        <v>0.23</v>
+        <v>0.1952</v>
       </c>
       <c r="U14">
-        <v>0.2146</v>
+        <v>0.1898</v>
       </c>
       <c r="V14">
         <v>9</v>
       </c>
       <c r="W14">
-        <v>0.2353</v>
+        <v>0.2118</v>
       </c>
       <c r="X14">
-        <v>0.2179</v>
+        <v>0.2188</v>
       </c>
       <c r="Y14">
-        <v>0.985</v>
+        <v>1.0455</v>
       </c>
       <c r="AA14" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AC14" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AD14">
-        <v>5.14</v>
+        <v>5.22</v>
       </c>
       <c r="AE14" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AF14">
-        <v>0.2162</v>
+        <v>0.25</v>
       </c>
       <c r="AG14">
-        <v>1.0557</v>
+        <v>0.8922</v>
       </c>
       <c r="AH14">
         <v>0</v>
       </c>
       <c r="AM14">
-        <v>5.14</v>
+        <v>5.22</v>
       </c>
     </row>
     <row r="15" spans="1:39" x14ac:dyDescent="0.25">
@@ -2005,25 +2101,25 @@
         <v>66</v>
       </c>
       <c r="C15">
-        <v>3.5</v>
+        <v>5.5</v>
       </c>
       <c r="D15">
-        <v>-113</v>
+        <v>-145</v>
       </c>
       <c r="E15">
-        <v>-105</v>
+        <v>126</v>
       </c>
       <c r="F15" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="G15">
-        <v>824718</v>
+        <v>824560</v>
       </c>
       <c r="H15" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I15">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="J15" t="b">
         <v>0</v>
@@ -2032,70 +2128,70 @@
         <v>0</v>
       </c>
       <c r="L15">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M15">
-        <v>0.1818</v>
+        <v>0.2861</v>
       </c>
       <c r="N15">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O15">
-        <v>63</v>
+        <v>114</v>
       </c>
       <c r="P15">
-        <v>4.07</v>
+        <v>4.33</v>
       </c>
       <c r="Q15">
-        <v>0.1587</v>
+        <v>0.2895</v>
       </c>
       <c r="R15">
-        <v>0.24</v>
+        <v>0.363</v>
       </c>
       <c r="S15" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="T15">
-        <v>0.1867</v>
+        <v>0.2375</v>
       </c>
       <c r="U15">
-        <v>0.1921</v>
+        <v>0.2438</v>
       </c>
       <c r="V15">
         <v>9</v>
       </c>
       <c r="W15">
-        <v>0.2142</v>
+        <v>0.2358</v>
       </c>
       <c r="X15">
-        <v>0.2179</v>
+        <v>0.2188</v>
       </c>
       <c r="Y15">
-        <v>0.9673</v>
+        <v>1.0743</v>
       </c>
       <c r="AA15" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AC15" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AD15">
-        <v>2.98</v>
+        <v>6.83</v>
       </c>
       <c r="AE15" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="AF15">
-        <v>0.1763</v>
+        <v>0.2873</v>
       </c>
       <c r="AG15">
-        <v>0.857</v>
+        <v>1.0857</v>
       </c>
       <c r="AH15">
-        <v>0</v>
+        <v>0.17</v>
       </c>
       <c r="AM15">
-        <v>2.98</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16" spans="1:39" x14ac:dyDescent="0.25">
@@ -2103,28 +2199,28 @@
         <v>39</v>
       </c>
       <c r="B16" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C16">
         <v>4.5</v>
       </c>
       <c r="D16">
-        <v>115</v>
+        <v>-113</v>
       </c>
       <c r="E16">
-        <v>-133</v>
+        <v>100</v>
       </c>
       <c r="F16" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G16">
-        <v>823100</v>
+        <v>824560</v>
       </c>
       <c r="H16" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I16">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="J16" t="b">
         <v>0</v>
@@ -2133,70 +2229,70 @@
         <v>0</v>
       </c>
       <c r="L16">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M16">
-        <v>0.1874</v>
+        <v>0.2008</v>
       </c>
       <c r="N16">
         <v>5</v>
       </c>
       <c r="O16">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="P16">
-        <v>4.51</v>
+        <v>4.4</v>
       </c>
       <c r="Q16">
-        <v>0.1983</v>
+        <v>0.178</v>
       </c>
       <c r="R16">
-        <v>0.377</v>
+        <v>0.371</v>
       </c>
       <c r="S16" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="T16">
-        <v>0.1985</v>
+        <v>0.2529</v>
       </c>
       <c r="U16">
-        <v>0.2026</v>
+        <v>0.2462</v>
       </c>
       <c r="V16">
         <v>9</v>
       </c>
       <c r="W16">
-        <v>0.2401</v>
+        <v>0.2247</v>
       </c>
       <c r="X16">
-        <v>0.2179</v>
+        <v>0.2188</v>
       </c>
       <c r="Y16">
-        <v>0.9578</v>
+        <v>0.9809</v>
       </c>
       <c r="AA16" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AC16" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AD16">
-        <v>3.79</v>
+        <v>5</v>
       </c>
       <c r="AE16" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AF16">
-        <v>0.1915</v>
+        <v>0.1923</v>
       </c>
       <c r="AG16">
-        <v>0.9111</v>
+        <v>1.1562</v>
       </c>
       <c r="AH16">
         <v>0</v>
       </c>
       <c r="AM16">
-        <v>3.79</v>
+        <v>5</v>
       </c>
     </row>
     <row r="17" spans="1:39" x14ac:dyDescent="0.25">
@@ -2255,7 +2351,7 @@
         <v>0.288</v>
       </c>
       <c r="S17" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="T17">
         <v>0.1852</v>
@@ -2270,34 +2366,34 @@
         <v>0.2081</v>
       </c>
       <c r="X17">
-        <v>0.2179</v>
+        <v>0.2188</v>
       </c>
       <c r="Y17">
         <v>0.8912</v>
       </c>
       <c r="AA17" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AC17" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AD17">
-        <v>3.43</v>
+        <v>3.41</v>
       </c>
       <c r="AE17" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AF17">
         <v>0.2641</v>
       </c>
       <c r="AG17">
-        <v>0.8498</v>
+        <v>0.8465</v>
       </c>
       <c r="AH17">
         <v>0</v>
       </c>
       <c r="AM17">
-        <v>3.43</v>
+        <v>3.41</v>
       </c>
     </row>
     <row r="18" spans="1:39" x14ac:dyDescent="0.25">
@@ -2323,7 +2419,7 @@
         <v>824073</v>
       </c>
       <c r="H18" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I18">
         <v>6.2</v>
@@ -2356,7 +2452,7 @@
         <v>0.379</v>
       </c>
       <c r="S18" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="T18">
         <v>0.1867</v>
@@ -2371,34 +2467,34 @@
         <v>0.2227</v>
       </c>
       <c r="X18">
-        <v>0.2179</v>
+        <v>0.2188</v>
       </c>
       <c r="Y18">
         <v>0.9419</v>
       </c>
       <c r="AA18" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AC18" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AD18">
-        <v>3.61</v>
+        <v>3.6</v>
       </c>
       <c r="AE18" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AF18">
         <v>0.1769</v>
       </c>
       <c r="AG18">
-        <v>0.8567</v>
+        <v>0.8533</v>
       </c>
       <c r="AH18">
         <v>0</v>
       </c>
       <c r="AM18">
-        <v>3.61</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="19" spans="1:39" x14ac:dyDescent="0.25">
@@ -2424,7 +2520,7 @@
         <v>823910</v>
       </c>
       <c r="H19" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I19">
         <v>4.6</v>
@@ -2457,7 +2553,7 @@
         <v>0.346</v>
       </c>
       <c r="S19" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="T19">
         <v>0.2208</v>
@@ -2472,34 +2568,34 @@
         <v>0.2068</v>
       </c>
       <c r="X19">
-        <v>0.2179</v>
+        <v>0.2188</v>
       </c>
       <c r="Y19">
         <v>0.994</v>
       </c>
       <c r="AA19" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AC19" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AD19">
-        <v>4.9</v>
+        <v>4.89</v>
       </c>
       <c r="AE19" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AF19">
         <v>0.2534</v>
       </c>
       <c r="AG19">
-        <v>1.0135</v>
+        <v>1.0095</v>
       </c>
       <c r="AH19">
         <v>0</v>
       </c>
       <c r="AM19">
-        <v>4.9</v>
+        <v>4.89</v>
       </c>
     </row>
     <row r="20" spans="1:39" x14ac:dyDescent="0.25">
@@ -2525,7 +2621,7 @@
         <v>823910</v>
       </c>
       <c r="H20" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I20">
         <v>6</v>
@@ -2558,7 +2654,7 @@
         <v>0.385</v>
       </c>
       <c r="S20" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="T20">
         <v>0.2485</v>
@@ -2573,34 +2669,34 @@
         <v>0.2559</v>
       </c>
       <c r="X20">
-        <v>0.2179</v>
+        <v>0.2188</v>
       </c>
       <c r="Y20">
         <v>1.1003</v>
       </c>
       <c r="AA20" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AC20" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AD20">
-        <v>8.84</v>
+        <v>8.8</v>
       </c>
       <c r="AE20" t="s">
-        <v>76</v>
+        <v>45</v>
       </c>
       <c r="AF20">
         <v>0.3001</v>
       </c>
       <c r="AG20">
-        <v>1.1404</v>
+        <v>1.1359</v>
       </c>
       <c r="AH20">
         <v>0</v>
       </c>
       <c r="AM20">
-        <v>8.84</v>
+        <v>8.8</v>
       </c>
     </row>
     <row r="21" spans="1:39" x14ac:dyDescent="0.25">
@@ -2608,28 +2704,28 @@
         <v>39</v>
       </c>
       <c r="B21" t="s">
+        <v>76</v>
+      </c>
+      <c r="C21">
+        <v>4.5</v>
+      </c>
+      <c r="D21">
+        <v>115</v>
+      </c>
+      <c r="E21">
+        <v>-133</v>
+      </c>
+      <c r="F21" t="s">
         <v>77</v>
       </c>
-      <c r="C21">
-        <v>5.5</v>
-      </c>
-      <c r="D21">
-        <v>-150</v>
-      </c>
-      <c r="E21">
-        <v>124</v>
-      </c>
-      <c r="F21" t="s">
-        <v>78</v>
-      </c>
       <c r="G21">
-        <v>825044</v>
+        <v>823100</v>
       </c>
       <c r="H21" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I21">
-        <v>5.4</v>
+        <v>5</v>
       </c>
       <c r="J21" t="b">
         <v>0</v>
@@ -2641,67 +2737,67 @@
         <v>6</v>
       </c>
       <c r="M21">
-        <v>0.2347</v>
+        <v>0.1874</v>
       </c>
       <c r="N21">
         <v>5</v>
       </c>
       <c r="O21">
-        <v>95</v>
+        <v>121</v>
       </c>
       <c r="P21">
-        <v>4.08</v>
+        <v>4.51</v>
       </c>
       <c r="Q21">
-        <v>0.2316</v>
+        <v>0.1983</v>
       </c>
       <c r="R21">
-        <v>0.322</v>
+        <v>0.377</v>
       </c>
       <c r="S21" t="s">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="T21">
-        <v>0.2819</v>
+        <v>0.1985</v>
       </c>
       <c r="U21">
-        <v>0.2818</v>
+        <v>0.2026</v>
       </c>
       <c r="V21">
         <v>9</v>
       </c>
       <c r="W21">
-        <v>0.2557</v>
+        <v>0.2401</v>
       </c>
       <c r="X21">
-        <v>0.2179</v>
+        <v>0.2188</v>
       </c>
       <c r="Y21">
-        <v>1.0246</v>
+        <v>0.9578</v>
       </c>
       <c r="AA21" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AC21" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AD21">
-        <v>6.83</v>
+        <v>3.77</v>
       </c>
       <c r="AE21" t="s">
-        <v>59</v>
+        <v>47</v>
       </c>
       <c r="AF21">
-        <v>0.2337</v>
+        <v>0.1915</v>
       </c>
       <c r="AG21">
-        <v>1.2936</v>
+        <v>0.9075</v>
       </c>
       <c r="AH21">
-        <v>0.17</v>
+        <v>0</v>
       </c>
       <c r="AM21">
-        <v>7</v>
+        <v>3.77</v>
       </c>
     </row>
     <row r="22" spans="1:39" x14ac:dyDescent="0.25">
@@ -2709,28 +2805,28 @@
         <v>39</v>
       </c>
       <c r="B22" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C22">
         <v>3.5</v>
       </c>
       <c r="D22">
-        <v>102</v>
+        <v>-113</v>
       </c>
       <c r="E22">
-        <v>-115</v>
+        <v>-105</v>
       </c>
       <c r="F22" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G22">
-        <v>825044</v>
+        <v>824718</v>
       </c>
       <c r="H22" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I22">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="J22" t="b">
         <v>0</v>
@@ -2742,67 +2838,67 @@
         <v>6</v>
       </c>
       <c r="M22">
-        <v>0.1814</v>
+        <v>0.1818</v>
       </c>
       <c r="N22">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O22">
-        <v>117</v>
+        <v>63</v>
       </c>
       <c r="P22">
-        <v>4.48</v>
+        <v>4.07</v>
       </c>
       <c r="Q22">
-        <v>0.1795</v>
+        <v>0.1587</v>
       </c>
       <c r="R22">
-        <v>0.369</v>
+        <v>0.24</v>
       </c>
       <c r="S22" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="T22">
-        <v>0.167</v>
+        <v>0.1867</v>
       </c>
       <c r="U22">
-        <v>0.1663</v>
+        <v>0.1921</v>
       </c>
       <c r="V22">
         <v>9</v>
       </c>
       <c r="W22">
-        <v>0.1988</v>
+        <v>0.2142</v>
       </c>
       <c r="X22">
-        <v>0.2179</v>
+        <v>0.2188</v>
       </c>
       <c r="Y22">
-        <v>0.88</v>
+        <v>0.9673</v>
       </c>
       <c r="AA22" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AC22" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AD22">
-        <v>2.7</v>
+        <v>2.96</v>
       </c>
       <c r="AE22" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AF22">
-        <v>0.1807</v>
+        <v>0.1763</v>
       </c>
       <c r="AG22">
-        <v>0.7662</v>
+        <v>0.8536</v>
       </c>
       <c r="AH22">
         <v>0</v>
       </c>
       <c r="AM22">
-        <v>2.7</v>
+        <v>2.96</v>
       </c>
     </row>
     <row r="23" spans="1:39" x14ac:dyDescent="0.25">
@@ -2813,25 +2909,25 @@
         <v>80</v>
       </c>
       <c r="C23">
-        <v>3.5</v>
+        <v>5.5</v>
       </c>
       <c r="D23">
-        <v>145</v>
+        <v>-110</v>
       </c>
       <c r="E23">
-        <v>-167</v>
+        <v>-110</v>
       </c>
       <c r="F23" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="G23">
-        <v>824316</v>
+        <v>824718</v>
       </c>
       <c r="H23" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I23">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="J23" t="b">
         <v>0</v>
@@ -2843,67 +2939,67 @@
         <v>6</v>
       </c>
       <c r="M23">
-        <v>0.2012</v>
+        <v>0.2188</v>
       </c>
       <c r="N23">
         <v>5</v>
       </c>
       <c r="O23">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="P23">
-        <v>4.35</v>
+        <v>4.71</v>
       </c>
       <c r="Q23">
-        <v>0.1759</v>
+        <v>0.2119</v>
       </c>
       <c r="R23">
-        <v>0.351</v>
+        <v>0.371</v>
       </c>
       <c r="S23" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="T23">
-        <v>0.1724</v>
+        <v>0.23</v>
       </c>
       <c r="U23">
-        <v>0.1742</v>
+        <v>0.2146</v>
       </c>
       <c r="V23">
         <v>9</v>
       </c>
       <c r="W23">
-        <v>0.2137</v>
+        <v>0.2353</v>
       </c>
       <c r="X23">
-        <v>0.2179</v>
+        <v>0.2188</v>
       </c>
       <c r="Y23">
-        <v>0.88</v>
+        <v>0.985</v>
       </c>
       <c r="AA23" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AC23" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AD23">
-        <v>2.89</v>
+        <v>5.12</v>
       </c>
       <c r="AE23" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AF23">
-        <v>0.1924</v>
+        <v>0.2162</v>
       </c>
       <c r="AG23">
-        <v>0.791</v>
+        <v>1.0515</v>
       </c>
       <c r="AH23">
         <v>0</v>
       </c>
       <c r="AM23">
-        <v>2.89</v>
+        <v>5.12</v>
       </c>
     </row>
     <row r="24" spans="1:39" x14ac:dyDescent="0.25">
@@ -2911,28 +3007,28 @@
         <v>39</v>
       </c>
       <c r="B24" t="s">
+        <v>81</v>
+      </c>
+      <c r="C24">
+        <v>3.5</v>
+      </c>
+      <c r="D24">
+        <v>102</v>
+      </c>
+      <c r="E24">
+        <v>-115</v>
+      </c>
+      <c r="F24" t="s">
         <v>82</v>
       </c>
-      <c r="C24">
-        <v>4.5</v>
-      </c>
-      <c r="D24">
-        <v>-102</v>
-      </c>
-      <c r="E24">
-        <v>-113</v>
-      </c>
-      <c r="F24" t="s">
-        <v>81</v>
-      </c>
       <c r="G24">
-        <v>824316</v>
+        <v>825044</v>
       </c>
       <c r="H24" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I24">
-        <v>5.8</v>
+        <v>4.9</v>
       </c>
       <c r="J24" t="b">
         <v>0</v>
@@ -2944,67 +3040,67 @@
         <v>6</v>
       </c>
       <c r="M24">
-        <v>0.1909</v>
+        <v>0.1814</v>
       </c>
       <c r="N24">
         <v>5</v>
       </c>
       <c r="O24">
-        <v>131</v>
+        <v>117</v>
       </c>
       <c r="P24">
-        <v>4.08</v>
+        <v>4.48</v>
       </c>
       <c r="Q24">
-        <v>0.1908</v>
+        <v>0.1795</v>
       </c>
       <c r="R24">
-        <v>0.396</v>
+        <v>0.369</v>
       </c>
       <c r="S24" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="T24">
-        <v>0.2188</v>
+        <v>0.167</v>
       </c>
       <c r="U24">
-        <v>0.2075</v>
+        <v>0.1663</v>
       </c>
       <c r="V24">
         <v>9</v>
       </c>
       <c r="W24">
-        <v>0.2178</v>
+        <v>0.1988</v>
       </c>
       <c r="X24">
-        <v>0.2179</v>
+        <v>0.2188</v>
       </c>
       <c r="Y24">
-        <v>0.9455</v>
+        <v>0.88</v>
       </c>
       <c r="AA24" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AC24" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AD24">
-        <v>4.27</v>
+        <v>2.69</v>
       </c>
       <c r="AE24" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AF24">
-        <v>0.1909</v>
+        <v>0.1807</v>
       </c>
       <c r="AG24">
-        <v>1.0043</v>
+        <v>0.7632</v>
       </c>
       <c r="AH24">
         <v>0</v>
       </c>
       <c r="AM24">
-        <v>4.27</v>
+        <v>2.69</v>
       </c>
     </row>
     <row r="25" spans="1:39" x14ac:dyDescent="0.25">
@@ -3015,22 +3111,22 @@
         <v>83</v>
       </c>
       <c r="C25">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="D25">
-        <v>-108</v>
+        <v>-150</v>
       </c>
       <c r="E25">
-        <v>-102</v>
+        <v>124</v>
       </c>
       <c r="F25" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="G25">
-        <v>823261</v>
+        <v>825044</v>
       </c>
       <c r="H25" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I25">
         <v>5.4</v>
@@ -3045,67 +3141,67 @@
         <v>6</v>
       </c>
       <c r="M25">
-        <v>0.2328</v>
+        <v>0.2347</v>
       </c>
       <c r="N25">
         <v>5</v>
       </c>
       <c r="O25">
-        <v>104</v>
+        <v>95</v>
       </c>
       <c r="P25">
-        <v>4</v>
+        <v>4.08</v>
       </c>
       <c r="Q25">
-        <v>0.1731</v>
+        <v>0.2316</v>
       </c>
       <c r="R25">
-        <v>0.342</v>
+        <v>0.322</v>
       </c>
       <c r="S25" t="s">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="T25">
-        <v>0.1983</v>
+        <v>0.279</v>
       </c>
       <c r="U25">
-        <v>0.1939</v>
+        <v>0.2807</v>
       </c>
       <c r="V25">
         <v>9</v>
       </c>
       <c r="W25">
-        <v>0.2101</v>
+        <v>0.2557</v>
       </c>
       <c r="X25">
-        <v>0.2179</v>
+        <v>0.2188</v>
       </c>
       <c r="Y25">
-        <v>0.9967</v>
+        <v>1.0455</v>
       </c>
       <c r="AA25" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AC25" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AD25">
-        <v>4.14</v>
+        <v>6.87</v>
       </c>
       <c r="AE25" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="AF25">
-        <v>0.2124</v>
+        <v>0.2337</v>
       </c>
       <c r="AG25">
-        <v>0.9102</v>
+        <v>1.2753</v>
       </c>
       <c r="AH25">
-        <v>0</v>
+        <v>0.17</v>
       </c>
       <c r="AM25">
-        <v>4.14</v>
+        <v>7.04</v>
       </c>
     </row>
     <row r="26" spans="1:39" x14ac:dyDescent="0.25">
@@ -3113,28 +3209,28 @@
         <v>39</v>
       </c>
       <c r="B26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C26">
         <v>4.5</v>
       </c>
       <c r="D26">
-        <v>107</v>
+        <v>-102</v>
       </c>
       <c r="E26">
-        <v>-128</v>
+        <v>-113</v>
       </c>
       <c r="F26" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G26">
-        <v>823261</v>
+        <v>824316</v>
       </c>
       <c r="H26" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I26">
-        <v>5.3</v>
+        <v>5.8</v>
       </c>
       <c r="J26" t="b">
         <v>0</v>
@@ -3146,67 +3242,67 @@
         <v>6</v>
       </c>
       <c r="M26">
-        <v>0.2442</v>
+        <v>0.1909</v>
       </c>
       <c r="N26">
         <v>5</v>
       </c>
       <c r="O26">
-        <v>114</v>
+        <v>131</v>
       </c>
       <c r="P26">
-        <v>4.07</v>
+        <v>4.08</v>
       </c>
       <c r="Q26">
-        <v>0.2105</v>
+        <v>0.1908</v>
       </c>
       <c r="R26">
-        <v>0.363</v>
+        <v>0.396</v>
       </c>
       <c r="S26" t="s">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="T26">
-        <v>0.1876</v>
+        <v>0.2188</v>
       </c>
       <c r="U26">
-        <v>0.1898</v>
+        <v>0.2075</v>
       </c>
       <c r="V26">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W26">
-        <v>0.2166</v>
+        <v>0.2178</v>
       </c>
       <c r="X26">
-        <v>0.2179</v>
+        <v>0.2188</v>
       </c>
       <c r="Y26">
-        <v>0.9947</v>
+        <v>0.9455</v>
       </c>
       <c r="AA26" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AC26" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AD26">
-        <v>4.31</v>
+        <v>4.26</v>
       </c>
       <c r="AE26" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AF26">
-        <v>0.232</v>
+        <v>0.1909</v>
       </c>
       <c r="AG26">
-        <v>0.8608</v>
+        <v>1.0003</v>
       </c>
       <c r="AH26">
         <v>0</v>
       </c>
       <c r="AM26">
-        <v>4.31</v>
+        <v>4.26</v>
       </c>
     </row>
     <row r="27" spans="1:39" x14ac:dyDescent="0.25">
@@ -3217,25 +3313,25 @@
         <v>86</v>
       </c>
       <c r="C27">
-        <v>8.5</v>
+        <v>3.5</v>
       </c>
       <c r="D27">
-        <v>-115</v>
+        <v>145</v>
       </c>
       <c r="E27">
-        <v>102</v>
+        <v>-167</v>
       </c>
       <c r="F27" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="G27">
-        <v>823509</v>
+        <v>824316</v>
       </c>
       <c r="H27" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I27">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J27" t="b">
         <v>0</v>
@@ -3247,67 +3343,67 @@
         <v>6</v>
       </c>
       <c r="M27">
-        <v>0.361</v>
+        <v>0.2012</v>
       </c>
       <c r="N27">
         <v>5</v>
       </c>
       <c r="O27">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="P27">
-        <v>4.01</v>
+        <v>4.35</v>
       </c>
       <c r="Q27">
-        <v>0.3443</v>
+        <v>0.1759</v>
       </c>
       <c r="R27">
-        <v>0.379</v>
+        <v>0.351</v>
       </c>
       <c r="S27" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="T27">
-        <v>0.2744</v>
+        <v>0.1724</v>
       </c>
       <c r="U27">
-        <v>0.2725</v>
+        <v>0.1742</v>
       </c>
       <c r="V27">
         <v>9</v>
       </c>
       <c r="W27">
-        <v>0.2482</v>
+        <v>0.2137</v>
       </c>
       <c r="X27">
-        <v>0.2179</v>
+        <v>0.2188</v>
       </c>
       <c r="Y27">
-        <v>1.0348</v>
+        <v>0.88</v>
       </c>
       <c r="AA27" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AC27" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AD27">
-        <v>11.15</v>
+        <v>2.88</v>
       </c>
       <c r="AE27" t="s">
-        <v>76</v>
+        <v>47</v>
       </c>
       <c r="AF27">
-        <v>0.3546</v>
+        <v>0.1924</v>
       </c>
       <c r="AG27">
-        <v>1.2595</v>
+        <v>0.7879</v>
       </c>
       <c r="AH27">
         <v>0</v>
       </c>
       <c r="AM27">
-        <v>11.15</v>
+        <v>2.88</v>
       </c>
     </row>
     <row r="28" spans="1:39" x14ac:dyDescent="0.25">
@@ -3315,28 +3411,28 @@
         <v>39</v>
       </c>
       <c r="B28" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C28">
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
       <c r="D28">
-        <v>115</v>
+        <v>107</v>
       </c>
       <c r="E28">
         <v>-128</v>
       </c>
       <c r="F28" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G28">
-        <v>823509</v>
+        <v>823261</v>
       </c>
       <c r="H28" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I28">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="J28" t="b">
         <v>0</v>
@@ -3348,67 +3444,67 @@
         <v>6</v>
       </c>
       <c r="M28">
-        <v>0.2518</v>
+        <v>0.2442</v>
       </c>
       <c r="N28">
         <v>5</v>
       </c>
       <c r="O28">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="P28">
-        <v>4.14</v>
+        <v>4.07</v>
       </c>
       <c r="Q28">
-        <v>0.1875</v>
+        <v>0.2105</v>
       </c>
       <c r="R28">
-        <v>0.359</v>
+        <v>0.363</v>
       </c>
       <c r="S28" t="s">
-        <v>45</v>
+        <v>89</v>
       </c>
       <c r="T28">
-        <v>0.1953</v>
+        <v>0.1876</v>
       </c>
       <c r="U28">
-        <v>0.177</v>
+        <v>0.1898</v>
       </c>
       <c r="V28">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W28">
-        <v>0.2104</v>
+        <v>0.2166</v>
       </c>
       <c r="X28">
-        <v>0.2179</v>
+        <v>0.2188</v>
       </c>
       <c r="Y28">
-        <v>0.943</v>
+        <v>0.9947</v>
       </c>
       <c r="AA28" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AC28" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AD28">
-        <v>4.39</v>
+        <v>4.29</v>
       </c>
       <c r="AE28" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AF28">
-        <v>0.2287</v>
+        <v>0.232</v>
       </c>
       <c r="AG28">
-        <v>0.8963</v>
+        <v>0.8574</v>
       </c>
       <c r="AH28">
         <v>0</v>
       </c>
       <c r="AM28">
-        <v>4.39</v>
+        <v>4.29</v>
       </c>
     </row>
     <row r="29" spans="1:39" x14ac:dyDescent="0.25">
@@ -3416,91 +3512,100 @@
         <v>39</v>
       </c>
       <c r="B29" t="s">
+        <v>90</v>
+      </c>
+      <c r="C29">
+        <v>4.5</v>
+      </c>
+      <c r="D29">
+        <v>-108</v>
+      </c>
+      <c r="E29">
+        <v>-102</v>
+      </c>
+      <c r="F29" t="s">
+        <v>88</v>
+      </c>
+      <c r="G29">
+        <v>823261</v>
+      </c>
+      <c r="H29" t="s">
+        <v>42</v>
+      </c>
+      <c r="I29">
+        <v>5.4</v>
+      </c>
+      <c r="J29" t="b">
+        <v>0</v>
+      </c>
+      <c r="K29" t="b">
+        <v>0</v>
+      </c>
+      <c r="L29">
+        <v>6</v>
+      </c>
+      <c r="M29">
+        <v>0.2328</v>
+      </c>
+      <c r="N29">
+        <v>5</v>
+      </c>
+      <c r="O29">
+        <v>104</v>
+      </c>
+      <c r="P29">
+        <v>4</v>
+      </c>
+      <c r="Q29">
+        <v>0.1731</v>
+      </c>
+      <c r="R29">
+        <v>0.342</v>
+      </c>
+      <c r="S29" t="s">
         <v>89</v>
       </c>
-      <c r="F29" t="s">
-        <v>90</v>
-      </c>
-      <c r="G29">
-        <v>823743</v>
-      </c>
-      <c r="H29" t="s">
-        <v>44</v>
-      </c>
-      <c r="I29">
-        <v>5</v>
-      </c>
-      <c r="J29" t="b">
-        <v>0</v>
-      </c>
-      <c r="K29" t="b">
-        <v>0</v>
-      </c>
-      <c r="L29">
-        <v>0</v>
-      </c>
-      <c r="M29">
-        <v>0.1789</v>
-      </c>
-      <c r="N29">
-        <v>5</v>
-      </c>
-      <c r="O29">
-        <v>102</v>
-      </c>
-      <c r="P29">
-        <v>4.12</v>
-      </c>
-      <c r="Q29">
-        <v>0.1569</v>
-      </c>
-      <c r="R29">
-        <v>0.338</v>
-      </c>
-      <c r="S29" t="s">
-        <v>45</v>
-      </c>
       <c r="T29">
-        <v>0.2262</v>
+        <v>0.1983</v>
       </c>
       <c r="U29">
-        <v>0.222</v>
+        <v>0.1939</v>
       </c>
       <c r="V29">
         <v>9</v>
       </c>
       <c r="W29">
-        <v>0.2197</v>
+        <v>0.2101</v>
       </c>
       <c r="X29">
-        <v>0.2179</v>
+        <v>0.2188</v>
       </c>
       <c r="Y29">
-        <v>0.9813</v>
+        <v>0.9967</v>
       </c>
       <c r="AA29" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AC29" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AD29">
-        <v>3.63</v>
+        <v>4.12</v>
       </c>
       <c r="AE29" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AF29">
-        <v>0.1715</v>
+        <v>0.2124</v>
       </c>
       <c r="AG29">
-        <v>1.0383</v>
+        <v>0.9066</v>
       </c>
       <c r="AH29">
         <v>0</v>
       </c>
       <c r="AM29">
-        <v>3.63</v>
+        <v>4.12</v>
       </c>
     </row>
     <row r="30" spans="1:39" x14ac:dyDescent="0.25">
@@ -3511,97 +3616,40 @@
         <v>91</v>
       </c>
       <c r="C30">
-        <v>6.5</v>
+        <v>5.5</v>
       </c>
       <c r="D30">
-        <v>-106</v>
+        <v>-180</v>
       </c>
       <c r="E30">
-        <v>-112</v>
+        <v>130</v>
       </c>
       <c r="F30" t="s">
-        <v>90</v>
-      </c>
-      <c r="G30">
-        <v>823743</v>
+        <v>52</v>
+      </c>
+      <c r="G30" t="s">
+        <v>44</v>
       </c>
       <c r="H30" t="s">
         <v>44</v>
       </c>
-      <c r="I30">
-        <v>5.3</v>
-      </c>
-      <c r="J30" t="b">
-        <v>0</v>
-      </c>
-      <c r="K30" t="b">
-        <v>0</v>
-      </c>
       <c r="L30">
-        <v>6</v>
-      </c>
-      <c r="M30">
-        <v>0.2992</v>
-      </c>
-      <c r="N30">
-        <v>5</v>
-      </c>
-      <c r="O30">
-        <v>116</v>
-      </c>
-      <c r="P30">
-        <v>3.81</v>
-      </c>
-      <c r="Q30">
-        <v>0.2759</v>
-      </c>
-      <c r="R30">
-        <v>0.367</v>
+        <v>1</v>
       </c>
       <c r="S30" t="s">
-        <v>45</v>
-      </c>
-      <c r="T30">
-        <v>0.2236</v>
-      </c>
-      <c r="U30">
-        <v>0.2244</v>
-      </c>
-      <c r="V30">
-        <v>9</v>
-      </c>
-      <c r="W30">
-        <v>0.2194</v>
-      </c>
-      <c r="X30">
-        <v>0.2179</v>
-      </c>
-      <c r="Y30">
-        <v>0.9745</v>
+        <v>44</v>
+      </c>
+      <c r="V30" t="s">
+        <v>44</v>
       </c>
       <c r="AA30" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AC30" t="s">
-        <v>42</v>
-      </c>
-      <c r="AD30">
-        <v>5.9</v>
+        <v>44</v>
       </c>
       <c r="AE30" t="s">
-        <v>46</v>
-      </c>
-      <c r="AF30">
-        <v>0.2907</v>
-      </c>
-      <c r="AG30">
-        <v>1.0262</v>
-      </c>
-      <c r="AH30">
-        <v>0</v>
-      </c>
-      <c r="AM30">
-        <v>5.9</v>
+        <v>44</v>
       </c>
     </row>
     <row r="31" spans="1:39" x14ac:dyDescent="0.25">
@@ -3611,89 +3659,41 @@
       <c r="B31" t="s">
         <v>92</v>
       </c>
+      <c r="C31">
+        <v>4.5</v>
+      </c>
+      <c r="D31">
+        <v>-115</v>
+      </c>
+      <c r="E31">
+        <v>104</v>
+      </c>
       <c r="F31" t="s">
-        <v>41</v>
-      </c>
-      <c r="G31">
-        <v>823831</v>
+        <v>56</v>
+      </c>
+      <c r="G31" t="s">
+        <v>44</v>
       </c>
       <c r="H31" t="s">
         <v>44</v>
       </c>
-      <c r="I31">
-        <v>5.5</v>
-      </c>
-      <c r="J31" t="b">
-        <v>0</v>
-      </c>
-      <c r="K31" t="b">
-        <v>0</v>
-      </c>
       <c r="L31">
-        <v>0</v>
-      </c>
-      <c r="M31">
-        <v>0.2693</v>
-      </c>
-      <c r="N31">
-        <v>5</v>
-      </c>
-      <c r="O31">
-        <v>106</v>
-      </c>
-      <c r="P31">
-        <v>4.02</v>
-      </c>
-      <c r="Q31">
-        <v>0.283</v>
-      </c>
-      <c r="R31">
-        <v>0.346</v>
+        <v>6</v>
       </c>
       <c r="S31" t="s">
-        <v>45</v>
-      </c>
-      <c r="T31">
-        <v>0.2447</v>
-      </c>
-      <c r="U31">
-        <v>0.2368</v>
-      </c>
-      <c r="V31">
-        <v>9</v>
-      </c>
-      <c r="W31">
-        <v>0.2076</v>
-      </c>
-      <c r="X31">
-        <v>0.2179</v>
-      </c>
-      <c r="Y31">
-        <v>1.0251</v>
+        <v>44</v>
+      </c>
+      <c r="V31" t="s">
+        <v>44</v>
       </c>
       <c r="AA31" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AC31" t="s">
-        <v>42</v>
-      </c>
-      <c r="AD31">
-        <v>6.93</v>
+        <v>44</v>
       </c>
       <c r="AE31" t="s">
-        <v>59</v>
-      </c>
-      <c r="AF31">
-        <v>0.2741</v>
-      </c>
-      <c r="AG31">
-        <v>1.123</v>
-      </c>
-      <c r="AH31">
-        <v>0.17</v>
-      </c>
-      <c r="AM31">
-        <v>7.1</v>
+        <v>44</v>
       </c>
     </row>
     <row r="32" spans="1:39" x14ac:dyDescent="0.25">
@@ -3713,31 +3713,31 @@
         <v>-110</v>
       </c>
       <c r="F32" t="s">
-        <v>90</v>
+        <v>49</v>
       </c>
       <c r="G32" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="H32" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="L32">
         <v>6</v>
       </c>
       <c r="S32" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="V32" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AA32" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AC32" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AE32" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
   </sheetData>

--- a/data/k-props/2026-08-22.xlsx
+++ b/data/k-props/2026-08-22.xlsx
@@ -199,6 +199,9 @@
     <t>Los Angeles Angels @ Texas Rangers</t>
   </si>
   <si>
+    <t>Limited starter</t>
+  </si>
+  <si>
     <t>Cody Bradford</t>
   </si>
   <si>
@@ -226,7 +229,7 @@
     <t>Detroit Tigers @ Kansas City Royals</t>
   </si>
   <si>
-    <t>Limited starter</t>
+    <t>Opener / bullpen game</t>
   </si>
   <si>
     <t>Michael Wacha</t>
@@ -278,9 +281,6 @@
   </si>
   <si>
     <t>Minnesota Twins @ San Diego Padres</t>
-  </si>
-  <si>
-    <t>lineup_unweighted_30d_projected_regulars</t>
   </si>
   <si>
     <t>Casey Mize</t>
@@ -869,7 +869,7 @@
         <v>0.2482</v>
       </c>
       <c r="X2">
-        <v>0.2188</v>
+        <v>0.2199</v>
       </c>
       <c r="Y2">
         <v>1.0348</v>
@@ -881,7 +881,7 @@
         <v>44</v>
       </c>
       <c r="AD2">
-        <v>11.11</v>
+        <v>11.05</v>
       </c>
       <c r="AE2" t="s">
         <v>45</v>
@@ -890,13 +890,13 @@
         <v>0.3546</v>
       </c>
       <c r="AG2">
-        <v>1.2545</v>
+        <v>1.2483</v>
       </c>
       <c r="AH2">
         <v>0</v>
       </c>
       <c r="AM2">
-        <v>11.11</v>
+        <v>11.05</v>
       </c>
     </row>
     <row r="3" spans="1:39" x14ac:dyDescent="0.25">
@@ -970,7 +970,7 @@
         <v>0.2104</v>
       </c>
       <c r="X3">
-        <v>0.2188</v>
+        <v>0.2199</v>
       </c>
       <c r="Y3">
         <v>0.943</v>
@@ -982,7 +982,7 @@
         <v>44</v>
       </c>
       <c r="AD3">
-        <v>4.37</v>
+        <v>4.35</v>
       </c>
       <c r="AE3" t="s">
         <v>47</v>
@@ -991,13 +991,13 @@
         <v>0.2287</v>
       </c>
       <c r="AG3">
-        <v>0.8927</v>
+        <v>0.8883</v>
       </c>
       <c r="AH3">
         <v>0</v>
       </c>
       <c r="AM3">
-        <v>4.37</v>
+        <v>4.35</v>
       </c>
     </row>
     <row r="4" spans="1:39" x14ac:dyDescent="0.25">
@@ -1062,7 +1062,7 @@
         <v>0.2197</v>
       </c>
       <c r="X4">
-        <v>0.2188</v>
+        <v>0.2199</v>
       </c>
       <c r="Y4">
         <v>0.9813</v>
@@ -1074,7 +1074,7 @@
         <v>44</v>
       </c>
       <c r="AD4">
-        <v>3.62</v>
+        <v>3.6</v>
       </c>
       <c r="AE4" t="s">
         <v>47</v>
@@ -1083,13 +1083,13 @@
         <v>0.1715</v>
       </c>
       <c r="AG4">
-        <v>1.0342</v>
+        <v>1.029</v>
       </c>
       <c r="AH4">
         <v>0</v>
       </c>
       <c r="AM4">
-        <v>3.62</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="5" spans="1:39" x14ac:dyDescent="0.25">
@@ -1163,7 +1163,7 @@
         <v>0.2194</v>
       </c>
       <c r="X5">
-        <v>0.2188</v>
+        <v>0.2199</v>
       </c>
       <c r="Y5">
         <v>0.9745</v>
@@ -1175,7 +1175,7 @@
         <v>44</v>
       </c>
       <c r="AD5">
-        <v>5.88</v>
+        <v>5.85</v>
       </c>
       <c r="AE5" t="s">
         <v>47</v>
@@ -1184,13 +1184,13 @@
         <v>0.2907</v>
       </c>
       <c r="AG5">
-        <v>1.0221</v>
+        <v>1.0171</v>
       </c>
       <c r="AH5">
         <v>0</v>
       </c>
       <c r="AM5">
-        <v>5.88</v>
+        <v>5.85</v>
       </c>
     </row>
     <row r="6" spans="1:39" x14ac:dyDescent="0.25">
@@ -1219,7 +1219,7 @@
         <v>42</v>
       </c>
       <c r="I6">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="J6" t="b">
         <v>0</v>
@@ -1231,22 +1231,22 @@
         <v>2</v>
       </c>
       <c r="M6">
-        <v>0.2259</v>
+        <v>0.2242</v>
       </c>
       <c r="N6">
         <v>5</v>
       </c>
       <c r="O6">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="P6">
-        <v>4.41</v>
+        <v>4.38</v>
       </c>
       <c r="Q6">
-        <v>0.1485</v>
+        <v>0.1622</v>
       </c>
       <c r="R6">
-        <v>0.336</v>
+        <v>0.357</v>
       </c>
       <c r="S6" t="s">
         <v>43</v>
@@ -1261,10 +1261,10 @@
         <v>9</v>
       </c>
       <c r="W6">
-        <v>0.2121</v>
+        <v>0.2118</v>
       </c>
       <c r="X6">
-        <v>0.2188</v>
+        <v>0.2199</v>
       </c>
       <c r="Y6">
         <v>0.9201</v>
@@ -1276,22 +1276,22 @@
         <v>44</v>
       </c>
       <c r="AD6">
-        <v>3.95</v>
+        <v>4.05</v>
       </c>
       <c r="AE6" t="s">
         <v>47</v>
       </c>
       <c r="AF6">
-        <v>0.1999</v>
+        <v>0.2021</v>
       </c>
       <c r="AG6">
-        <v>1.0341</v>
+        <v>1.029</v>
       </c>
       <c r="AH6">
         <v>0</v>
       </c>
       <c r="AM6">
-        <v>3.95</v>
+        <v>4.05</v>
       </c>
     </row>
     <row r="7" spans="1:39" x14ac:dyDescent="0.25">
@@ -1311,7 +1311,7 @@
         <v>42</v>
       </c>
       <c r="I7">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="J7" t="b">
         <v>0</v>
@@ -1323,22 +1323,22 @@
         <v>0</v>
       </c>
       <c r="M7">
-        <v>0.2686</v>
+        <v>0.266</v>
       </c>
       <c r="N7">
         <v>5</v>
       </c>
       <c r="O7">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="P7">
         <v>4.03</v>
       </c>
       <c r="Q7">
-        <v>0.2793</v>
+        <v>0.2672</v>
       </c>
       <c r="R7">
-        <v>0.357</v>
+        <v>0.367</v>
       </c>
       <c r="S7" t="s">
         <v>43</v>
@@ -1353,10 +1353,10 @@
         <v>9</v>
       </c>
       <c r="W7">
-        <v>0.2076</v>
+        <v>0.2074</v>
       </c>
       <c r="X7">
-        <v>0.2188</v>
+        <v>0.2199</v>
       </c>
       <c r="Y7">
         <v>1.0251</v>
@@ -1368,22 +1368,22 @@
         <v>44</v>
       </c>
       <c r="AD7">
-        <v>6.93</v>
+        <v>6.81</v>
       </c>
       <c r="AE7" t="s">
         <v>54</v>
       </c>
       <c r="AF7">
-        <v>0.2724</v>
+        <v>0.2665</v>
       </c>
       <c r="AG7">
-        <v>1.1185</v>
+        <v>1.113</v>
       </c>
       <c r="AH7">
         <v>0.17</v>
       </c>
       <c r="AM7">
-        <v>7.1</v>
+        <v>6.98</v>
       </c>
     </row>
     <row r="8" spans="1:39" x14ac:dyDescent="0.25">
@@ -1424,22 +1424,22 @@
         <v>6</v>
       </c>
       <c r="M8">
-        <v>0.1854</v>
+        <v>0.19</v>
       </c>
       <c r="N8">
         <v>5</v>
       </c>
       <c r="O8">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="P8">
-        <v>4.49</v>
+        <v>4.43</v>
       </c>
       <c r="Q8">
-        <v>0.2143</v>
+        <v>0.2277</v>
       </c>
       <c r="R8">
-        <v>0.329</v>
+        <v>0.336</v>
       </c>
       <c r="S8" t="s">
         <v>43</v>
@@ -1457,7 +1457,7 @@
         <v>0.2137</v>
       </c>
       <c r="X8">
-        <v>0.2188</v>
+        <v>0.2199</v>
       </c>
       <c r="Y8">
         <v>0.8933</v>
@@ -1469,22 +1469,22 @@
         <v>44</v>
       </c>
       <c r="AD8">
-        <v>3.37</v>
+        <v>3.45</v>
       </c>
       <c r="AE8" t="s">
         <v>47</v>
       </c>
       <c r="AF8">
-        <v>0.1949</v>
+        <v>0.2027</v>
       </c>
       <c r="AG8">
-        <v>0.916</v>
+        <v>0.9115</v>
       </c>
       <c r="AH8">
         <v>0</v>
       </c>
       <c r="AM8">
-        <v>3.37</v>
+        <v>3.45</v>
       </c>
     </row>
     <row r="9" spans="1:39" x14ac:dyDescent="0.25">
@@ -1513,7 +1513,7 @@
         <v>42</v>
       </c>
       <c r="I9">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="J9" t="b">
         <v>0</v>
@@ -1525,22 +1525,22 @@
         <v>5</v>
       </c>
       <c r="M9">
-        <v>0.2222</v>
+        <v>0.222</v>
       </c>
       <c r="N9">
         <v>5</v>
       </c>
       <c r="O9">
-        <v>91</v>
+        <v>77</v>
       </c>
       <c r="P9">
-        <v>4.13</v>
+        <v>4.14</v>
       </c>
       <c r="Q9">
-        <v>0.1868</v>
+        <v>0.1688</v>
       </c>
       <c r="R9">
-        <v>0.313</v>
+        <v>0.278</v>
       </c>
       <c r="S9" t="s">
         <v>43</v>
@@ -1558,7 +1558,7 @@
         <v>0.2573</v>
       </c>
       <c r="X9">
-        <v>0.2188</v>
+        <v>0.2199</v>
       </c>
       <c r="Y9">
         <v>1.0352</v>
@@ -1570,22 +1570,22 @@
         <v>44</v>
       </c>
       <c r="AD9">
-        <v>4.97</v>
+        <v>4.69</v>
       </c>
       <c r="AE9" t="s">
         <v>47</v>
       </c>
       <c r="AF9">
-        <v>0.2111</v>
+        <v>0.2072</v>
       </c>
       <c r="AG9">
-        <v>1.1299</v>
+        <v>1.1243</v>
       </c>
       <c r="AH9">
         <v>0</v>
       </c>
       <c r="AM9">
-        <v>4.97</v>
+        <v>4.69</v>
       </c>
     </row>
     <row r="10" spans="1:39" x14ac:dyDescent="0.25">
@@ -1614,7 +1614,7 @@
         <v>42</v>
       </c>
       <c r="I10">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="J10" t="b">
         <v>0</v>
@@ -1626,22 +1626,22 @@
         <v>5</v>
       </c>
       <c r="M10">
-        <v>0.1893</v>
+        <v>0.1864</v>
       </c>
       <c r="N10">
         <v>5</v>
       </c>
       <c r="O10">
-        <v>117</v>
+        <v>100</v>
       </c>
       <c r="P10">
-        <v>4.31</v>
+        <v>4.3</v>
       </c>
       <c r="Q10">
-        <v>0.188</v>
+        <v>0.16</v>
       </c>
       <c r="R10">
-        <v>0.369</v>
+        <v>0.333</v>
       </c>
       <c r="S10" t="s">
         <v>43</v>
@@ -1659,7 +1659,7 @@
         <v>0.189</v>
       </c>
       <c r="X10">
-        <v>0.2188</v>
+        <v>0.2199</v>
       </c>
       <c r="Y10">
         <v>0.88</v>
@@ -1671,22 +1671,22 @@
         <v>44</v>
       </c>
       <c r="AD10">
-        <v>3.21</v>
+        <v>2.92</v>
       </c>
       <c r="AE10" t="s">
         <v>47</v>
       </c>
       <c r="AF10">
-        <v>0.1889</v>
+        <v>0.1776</v>
       </c>
       <c r="AG10">
-        <v>0.8009</v>
+        <v>0.7969</v>
       </c>
       <c r="AH10">
         <v>0</v>
       </c>
       <c r="AM10">
-        <v>3.21</v>
+        <v>2.92</v>
       </c>
     </row>
     <row r="11" spans="1:39" x14ac:dyDescent="0.25">
@@ -1712,10 +1712,10 @@
         <v>822858</v>
       </c>
       <c r="H11" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="I11">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="J11" t="b">
         <v>0</v>
@@ -1727,22 +1727,22 @@
         <v>6</v>
       </c>
       <c r="M11">
-        <v>0.1734</v>
+        <v>0.1709</v>
       </c>
       <c r="N11">
         <v>5</v>
       </c>
       <c r="O11">
-        <v>102</v>
+        <v>88</v>
       </c>
       <c r="P11">
-        <v>4.49</v>
+        <v>4.46</v>
       </c>
       <c r="Q11">
-        <v>0.1667</v>
+        <v>0.1477</v>
       </c>
       <c r="R11">
-        <v>0.338</v>
+        <v>0.306</v>
       </c>
       <c r="S11" t="s">
         <v>43</v>
@@ -1760,7 +1760,7 @@
         <v>0.2245</v>
       </c>
       <c r="X11">
-        <v>0.2188</v>
+        <v>0.2199</v>
       </c>
       <c r="Y11">
         <v>1.0657</v>
@@ -1772,22 +1772,22 @@
         <v>44</v>
       </c>
       <c r="AD11">
-        <v>4.6</v>
+        <v>4.16</v>
       </c>
       <c r="AE11" t="s">
         <v>47</v>
       </c>
       <c r="AF11">
-        <v>0.1711</v>
+        <v>0.1638</v>
       </c>
       <c r="AG11">
-        <v>1.2172</v>
+        <v>1.2112</v>
       </c>
       <c r="AH11">
         <v>0</v>
       </c>
       <c r="AM11">
-        <v>4.6</v>
+        <v>4.16</v>
       </c>
     </row>
     <row r="12" spans="1:39" x14ac:dyDescent="0.25">
@@ -1795,7 +1795,7 @@
         <v>39</v>
       </c>
       <c r="B12" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C12">
         <v>4.5</v>
@@ -1813,10 +1813,10 @@
         <v>822858</v>
       </c>
       <c r="H12" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="I12">
-        <v>5.1</v>
+        <v>4.3</v>
       </c>
       <c r="J12" t="b">
         <v>0</v>
@@ -1828,22 +1828,22 @@
         <v>6</v>
       </c>
       <c r="M12">
-        <v>0.1538</v>
+        <v>0.1507</v>
       </c>
       <c r="N12">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O12">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="P12">
-        <v>4.24</v>
+        <v>4.21</v>
       </c>
       <c r="Q12">
-        <v>0.1538</v>
+        <v>0.1507</v>
       </c>
       <c r="R12">
-        <v>0.245</v>
+        <v>0.267</v>
       </c>
       <c r="S12" t="s">
         <v>43</v>
@@ -1861,7 +1861,7 @@
         <v>0.2562</v>
       </c>
       <c r="X12">
-        <v>0.2188</v>
+        <v>0.2199</v>
       </c>
       <c r="Y12">
         <v>1.0991</v>
@@ -1873,22 +1873,22 @@
         <v>44</v>
       </c>
       <c r="AD12">
-        <v>5.03</v>
+        <v>4.13</v>
       </c>
       <c r="AE12" t="s">
         <v>47</v>
       </c>
       <c r="AF12">
-        <v>0.1538</v>
+        <v>0.1507</v>
       </c>
       <c r="AG12">
-        <v>1.3724</v>
+        <v>1.3656</v>
       </c>
       <c r="AH12">
         <v>0</v>
       </c>
       <c r="AM12">
-        <v>5.03</v>
+        <v>4.13</v>
       </c>
     </row>
     <row r="13" spans="1:39" x14ac:dyDescent="0.25">
@@ -1896,7 +1896,7 @@
         <v>39</v>
       </c>
       <c r="B13" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C13">
         <v>4.5</v>
@@ -1908,16 +1908,16 @@
         <v>105</v>
       </c>
       <c r="F13" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G13">
         <v>824151</v>
       </c>
       <c r="H13" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="I13">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="J13" t="b">
         <v>0</v>
@@ -1929,22 +1929,22 @@
         <v>5</v>
       </c>
       <c r="M13">
-        <v>0.2045</v>
+        <v>0.2075</v>
       </c>
       <c r="N13">
         <v>5</v>
       </c>
       <c r="O13">
-        <v>115</v>
+        <v>98</v>
       </c>
       <c r="P13">
-        <v>4.5</v>
+        <v>4.49</v>
       </c>
       <c r="Q13">
-        <v>0.2783</v>
+        <v>0.3061</v>
       </c>
       <c r="R13">
-        <v>0.365</v>
+        <v>0.329</v>
       </c>
       <c r="S13" t="s">
         <v>43</v>
@@ -1962,7 +1962,7 @@
         <v>0.2052</v>
       </c>
       <c r="X13">
-        <v>0.2188</v>
+        <v>0.2199</v>
       </c>
       <c r="Y13">
         <v>0.9272</v>
@@ -1974,22 +1974,22 @@
         <v>44</v>
       </c>
       <c r="AD13">
-        <v>4.08</v>
+        <v>4</v>
       </c>
       <c r="AE13" t="s">
         <v>47</v>
       </c>
       <c r="AF13">
-        <v>0.2315</v>
+        <v>0.2386</v>
       </c>
       <c r="AG13">
-        <v>0.9057</v>
+        <v>0.9012</v>
       </c>
       <c r="AH13">
         <v>0</v>
       </c>
       <c r="AM13">
-        <v>4.08</v>
+        <v>4</v>
       </c>
     </row>
     <row r="14" spans="1:39" x14ac:dyDescent="0.25">
@@ -1997,7 +1997,7 @@
         <v>39</v>
       </c>
       <c r="B14" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C14">
         <v>5.5</v>
@@ -2009,7 +2009,7 @@
         <v>111</v>
       </c>
       <c r="F14" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G14">
         <v>824151</v>
@@ -2018,7 +2018,7 @@
         <v>42</v>
       </c>
       <c r="I14">
-        <v>5.3</v>
+        <v>5</v>
       </c>
       <c r="J14" t="b">
         <v>0</v>
@@ -2030,22 +2030,22 @@
         <v>5</v>
       </c>
       <c r="M14">
-        <v>0.2474</v>
+        <v>0.2441</v>
       </c>
       <c r="N14">
         <v>5</v>
       </c>
       <c r="O14">
-        <v>114</v>
+        <v>97</v>
       </c>
       <c r="P14">
-        <v>4.24</v>
+        <v>4.23</v>
       </c>
       <c r="Q14">
-        <v>0.2544</v>
+        <v>0.2268</v>
       </c>
       <c r="R14">
-        <v>0.363</v>
+        <v>0.327</v>
       </c>
       <c r="S14" t="s">
         <v>43</v>
@@ -2063,7 +2063,7 @@
         <v>0.2118</v>
       </c>
       <c r="X14">
-        <v>0.2188</v>
+        <v>0.2199</v>
       </c>
       <c r="Y14">
         <v>1.0455</v>
@@ -2075,22 +2075,22 @@
         <v>44</v>
       </c>
       <c r="AD14">
-        <v>5.22</v>
+        <v>4.66</v>
       </c>
       <c r="AE14" t="s">
         <v>47</v>
       </c>
       <c r="AF14">
-        <v>0.25</v>
+        <v>0.2384</v>
       </c>
       <c r="AG14">
-        <v>0.8922</v>
+        <v>0.8878</v>
       </c>
       <c r="AH14">
         <v>0</v>
       </c>
       <c r="AM14">
-        <v>5.22</v>
+        <v>4.66</v>
       </c>
     </row>
     <row r="15" spans="1:39" x14ac:dyDescent="0.25">
@@ -2098,7 +2098,7 @@
         <v>39</v>
       </c>
       <c r="B15" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C15">
         <v>5.5</v>
@@ -2110,7 +2110,7 @@
         <v>126</v>
       </c>
       <c r="F15" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G15">
         <v>824560</v>
@@ -2119,7 +2119,7 @@
         <v>42</v>
       </c>
       <c r="I15">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="J15" t="b">
         <v>0</v>
@@ -2131,22 +2131,22 @@
         <v>5</v>
       </c>
       <c r="M15">
-        <v>0.2861</v>
+        <v>0.2865</v>
       </c>
       <c r="N15">
         <v>5</v>
       </c>
       <c r="O15">
-        <v>114</v>
+        <v>99</v>
       </c>
       <c r="P15">
-        <v>4.33</v>
+        <v>4.32</v>
       </c>
       <c r="Q15">
-        <v>0.2895</v>
+        <v>0.2828</v>
       </c>
       <c r="R15">
-        <v>0.363</v>
+        <v>0.331</v>
       </c>
       <c r="S15" t="s">
         <v>43</v>
@@ -2164,7 +2164,7 @@
         <v>0.2358</v>
       </c>
       <c r="X15">
-        <v>0.2188</v>
+        <v>0.2199</v>
       </c>
       <c r="Y15">
         <v>1.0743</v>
@@ -2176,22 +2176,22 @@
         <v>44</v>
       </c>
       <c r="AD15">
-        <v>6.83</v>
+        <v>6.45</v>
       </c>
       <c r="AE15" t="s">
         <v>54</v>
       </c>
       <c r="AF15">
-        <v>0.2873</v>
+        <v>0.2853</v>
       </c>
       <c r="AG15">
-        <v>1.0857</v>
+        <v>1.0803</v>
       </c>
       <c r="AH15">
         <v>0.17</v>
       </c>
       <c r="AM15">
-        <v>7</v>
+        <v>6.62</v>
       </c>
     </row>
     <row r="16" spans="1:39" x14ac:dyDescent="0.25">
@@ -2199,7 +2199,7 @@
         <v>39</v>
       </c>
       <c r="B16" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C16">
         <v>4.5</v>
@@ -2211,7 +2211,7 @@
         <v>100</v>
       </c>
       <c r="F16" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G16">
         <v>824560</v>
@@ -2220,7 +2220,7 @@
         <v>42</v>
       </c>
       <c r="I16">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="J16" t="b">
         <v>0</v>
@@ -2232,22 +2232,22 @@
         <v>5</v>
       </c>
       <c r="M16">
-        <v>0.2008</v>
+        <v>0.2027</v>
       </c>
       <c r="N16">
         <v>5</v>
       </c>
       <c r="O16">
-        <v>118</v>
+        <v>97</v>
       </c>
       <c r="P16">
-        <v>4.4</v>
+        <v>4.41</v>
       </c>
       <c r="Q16">
-        <v>0.178</v>
+        <v>0.2165</v>
       </c>
       <c r="R16">
-        <v>0.371</v>
+        <v>0.327</v>
       </c>
       <c r="S16" t="s">
         <v>43</v>
@@ -2265,7 +2265,7 @@
         <v>0.2247</v>
       </c>
       <c r="X16">
-        <v>0.2188</v>
+        <v>0.2199</v>
       </c>
       <c r="Y16">
         <v>0.9809</v>
@@ -2277,22 +2277,22 @@
         <v>44</v>
       </c>
       <c r="AD16">
-        <v>5</v>
+        <v>5.17</v>
       </c>
       <c r="AE16" t="s">
         <v>47</v>
       </c>
       <c r="AF16">
-        <v>0.1923</v>
+        <v>0.2072</v>
       </c>
       <c r="AG16">
-        <v>1.1562</v>
+        <v>1.1504</v>
       </c>
       <c r="AH16">
         <v>0</v>
       </c>
       <c r="AM16">
-        <v>5</v>
+        <v>5.17</v>
       </c>
     </row>
     <row r="17" spans="1:39" x14ac:dyDescent="0.25">
@@ -2300,7 +2300,7 @@
         <v>39</v>
       </c>
       <c r="B17" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C17">
         <v>4.5</v>
@@ -2312,19 +2312,19 @@
         <v>-160</v>
       </c>
       <c r="F17" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G17">
         <v>824073</v>
       </c>
       <c r="H17" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I17">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K17" t="b">
         <v>0</v>
@@ -2333,22 +2333,22 @@
         <v>6</v>
       </c>
       <c r="M17">
-        <v>0.2661</v>
+        <v>0.2659</v>
       </c>
       <c r="N17">
         <v>5</v>
       </c>
       <c r="O17">
-        <v>81</v>
+        <v>67</v>
       </c>
       <c r="P17">
         <v>4.28</v>
       </c>
       <c r="Q17">
-        <v>0.2593</v>
+        <v>0.2239</v>
       </c>
       <c r="R17">
-        <v>0.288</v>
+        <v>0.251</v>
       </c>
       <c r="S17" t="s">
         <v>43</v>
@@ -2366,7 +2366,7 @@
         <v>0.2081</v>
       </c>
       <c r="X17">
-        <v>0.2188</v>
+        <v>0.2199</v>
       </c>
       <c r="Y17">
         <v>0.8912</v>
@@ -2378,22 +2378,22 @@
         <v>44</v>
       </c>
       <c r="AD17">
-        <v>3.41</v>
+        <v>2.46</v>
       </c>
       <c r="AE17" t="s">
         <v>47</v>
       </c>
       <c r="AF17">
-        <v>0.2641</v>
+        <v>0.2553</v>
       </c>
       <c r="AG17">
-        <v>0.8465</v>
+        <v>0.8423</v>
       </c>
       <c r="AH17">
         <v>0</v>
       </c>
       <c r="AM17">
-        <v>3.41</v>
+        <v>2.46</v>
       </c>
     </row>
     <row r="18" spans="1:39" x14ac:dyDescent="0.25">
@@ -2401,7 +2401,7 @@
         <v>39</v>
       </c>
       <c r="B18" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C18">
         <v>4.5</v>
@@ -2413,7 +2413,7 @@
         <v>-151</v>
       </c>
       <c r="F18" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G18">
         <v>824073</v>
@@ -2422,7 +2422,7 @@
         <v>42</v>
       </c>
       <c r="I18">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="J18" t="b">
         <v>0</v>
@@ -2434,22 +2434,22 @@
         <v>6</v>
       </c>
       <c r="M18">
-        <v>0.1899</v>
+        <v>0.1884</v>
       </c>
       <c r="N18">
         <v>5</v>
       </c>
       <c r="O18">
-        <v>122</v>
+        <v>99</v>
       </c>
       <c r="P18">
-        <v>4.06</v>
+        <v>4.07</v>
       </c>
       <c r="Q18">
-        <v>0.1557</v>
+        <v>0.1616</v>
       </c>
       <c r="R18">
-        <v>0.379</v>
+        <v>0.331</v>
       </c>
       <c r="S18" t="s">
         <v>43</v>
@@ -2467,7 +2467,7 @@
         <v>0.2227</v>
       </c>
       <c r="X18">
-        <v>0.2188</v>
+        <v>0.2199</v>
       </c>
       <c r="Y18">
         <v>0.9419</v>
@@ -2479,22 +2479,22 @@
         <v>44</v>
       </c>
       <c r="AD18">
-        <v>3.6</v>
+        <v>3.52</v>
       </c>
       <c r="AE18" t="s">
         <v>47</v>
       </c>
       <c r="AF18">
-        <v>0.1769</v>
+        <v>0.1795</v>
       </c>
       <c r="AG18">
-        <v>0.8533</v>
+        <v>0.8491</v>
       </c>
       <c r="AH18">
         <v>0</v>
       </c>
       <c r="AM18">
-        <v>3.6</v>
+        <v>3.52</v>
       </c>
     </row>
     <row r="19" spans="1:39" x14ac:dyDescent="0.25">
@@ -2502,7 +2502,7 @@
         <v>39</v>
       </c>
       <c r="B19" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C19">
         <v>4.5</v>
@@ -2514,16 +2514,16 @@
         <v>118</v>
       </c>
       <c r="F19" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G19">
         <v>823910</v>
       </c>
       <c r="H19" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="I19">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="J19" t="b">
         <v>0</v>
@@ -2535,22 +2535,22 @@
         <v>6</v>
       </c>
       <c r="M19">
-        <v>0.2677</v>
+        <v>0.2721</v>
       </c>
       <c r="N19">
         <v>5</v>
       </c>
       <c r="O19">
-        <v>106</v>
+        <v>88</v>
       </c>
       <c r="P19">
-        <v>4.2</v>
+        <v>4.18</v>
       </c>
       <c r="Q19">
-        <v>0.2264</v>
+        <v>0.2386</v>
       </c>
       <c r="R19">
-        <v>0.346</v>
+        <v>0.306</v>
       </c>
       <c r="S19" t="s">
         <v>43</v>
@@ -2568,7 +2568,7 @@
         <v>0.2068</v>
       </c>
       <c r="X19">
-        <v>0.2188</v>
+        <v>0.2199</v>
       </c>
       <c r="Y19">
         <v>0.994</v>
@@ -2580,22 +2580,22 @@
         <v>44</v>
       </c>
       <c r="AD19">
-        <v>4.89</v>
+        <v>4.74</v>
       </c>
       <c r="AE19" t="s">
         <v>47</v>
       </c>
       <c r="AF19">
-        <v>0.2534</v>
+        <v>0.2618</v>
       </c>
       <c r="AG19">
-        <v>1.0095</v>
+        <v>1.0045</v>
       </c>
       <c r="AH19">
         <v>0</v>
       </c>
       <c r="AM19">
-        <v>4.89</v>
+        <v>4.74</v>
       </c>
     </row>
     <row r="20" spans="1:39" x14ac:dyDescent="0.25">
@@ -2603,7 +2603,7 @@
         <v>39</v>
       </c>
       <c r="B20" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C20">
         <v>8.5</v>
@@ -2615,7 +2615,7 @@
         <v>-126</v>
       </c>
       <c r="F20" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G20">
         <v>823910</v>
@@ -2624,7 +2624,7 @@
         <v>42</v>
       </c>
       <c r="I20">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="J20" t="b">
         <v>0</v>
@@ -2636,22 +2636,22 @@
         <v>6</v>
       </c>
       <c r="M20">
-        <v>0.3027</v>
+        <v>0.2987</v>
       </c>
       <c r="N20">
         <v>5</v>
       </c>
       <c r="O20">
-        <v>125</v>
+        <v>104</v>
       </c>
       <c r="P20">
-        <v>3.92</v>
+        <v>3.94</v>
       </c>
       <c r="Q20">
-        <v>0.296</v>
+        <v>0.2404</v>
       </c>
       <c r="R20">
-        <v>0.385</v>
+        <v>0.342</v>
       </c>
       <c r="S20" t="s">
         <v>43</v>
@@ -2669,7 +2669,7 @@
         <v>0.2559</v>
       </c>
       <c r="X20">
-        <v>0.2188</v>
+        <v>0.2199</v>
       </c>
       <c r="Y20">
         <v>1.1003</v>
@@ -2681,22 +2681,22 @@
         <v>44</v>
       </c>
       <c r="AD20">
-        <v>8.8</v>
+        <v>7.83</v>
       </c>
       <c r="AE20" t="s">
         <v>45</v>
       </c>
       <c r="AF20">
-        <v>0.3001</v>
+        <v>0.2787</v>
       </c>
       <c r="AG20">
-        <v>1.1359</v>
+        <v>1.1303</v>
       </c>
       <c r="AH20">
         <v>0</v>
       </c>
       <c r="AM20">
-        <v>8.8</v>
+        <v>7.83</v>
       </c>
     </row>
     <row r="21" spans="1:39" x14ac:dyDescent="0.25">
@@ -2704,7 +2704,7 @@
         <v>39</v>
       </c>
       <c r="B21" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C21">
         <v>4.5</v>
@@ -2716,7 +2716,7 @@
         <v>-133</v>
       </c>
       <c r="F21" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G21">
         <v>823100</v>
@@ -2725,7 +2725,7 @@
         <v>42</v>
       </c>
       <c r="I21">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="J21" t="b">
         <v>0</v>
@@ -2737,31 +2737,31 @@
         <v>6</v>
       </c>
       <c r="M21">
-        <v>0.1874</v>
+        <v>0.1898</v>
       </c>
       <c r="N21">
         <v>5</v>
       </c>
       <c r="O21">
-        <v>121</v>
+        <v>101</v>
       </c>
       <c r="P21">
         <v>4.51</v>
       </c>
       <c r="Q21">
-        <v>0.1983</v>
+        <v>0.2178</v>
       </c>
       <c r="R21">
-        <v>0.377</v>
+        <v>0.336</v>
       </c>
       <c r="S21" t="s">
         <v>43</v>
       </c>
       <c r="T21">
-        <v>0.1985</v>
+        <v>0.2178</v>
       </c>
       <c r="U21">
-        <v>0.2026</v>
+        <v>0.2132</v>
       </c>
       <c r="V21">
         <v>9</v>
@@ -2770,10 +2770,10 @@
         <v>0.2401</v>
       </c>
       <c r="X21">
-        <v>0.2188</v>
+        <v>0.2199</v>
       </c>
       <c r="Y21">
-        <v>0.9578</v>
+        <v>0.9735</v>
       </c>
       <c r="AA21" t="s">
         <v>44</v>
@@ -2782,22 +2782,22 @@
         <v>44</v>
       </c>
       <c r="AD21">
-        <v>3.77</v>
+        <v>4.14</v>
       </c>
       <c r="AE21" t="s">
         <v>47</v>
       </c>
       <c r="AF21">
-        <v>0.1915</v>
+        <v>0.1992</v>
       </c>
       <c r="AG21">
-        <v>0.9075</v>
+        <v>0.9906</v>
       </c>
       <c r="AH21">
         <v>0</v>
       </c>
       <c r="AM21">
-        <v>3.77</v>
+        <v>4.14</v>
       </c>
     </row>
     <row r="22" spans="1:39" x14ac:dyDescent="0.25">
@@ -2805,7 +2805,7 @@
         <v>39</v>
       </c>
       <c r="B22" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C22">
         <v>3.5</v>
@@ -2817,16 +2817,16 @@
         <v>-105</v>
       </c>
       <c r="F22" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G22">
         <v>824718</v>
       </c>
       <c r="H22" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="I22">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J22" t="b">
         <v>0</v>
@@ -2838,22 +2838,22 @@
         <v>6</v>
       </c>
       <c r="M22">
-        <v>0.1818</v>
+        <v>0.2035</v>
       </c>
       <c r="N22">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O22">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="P22">
-        <v>4.07</v>
+        <v>4.04</v>
       </c>
       <c r="Q22">
-        <v>0.1587</v>
+        <v>0.197</v>
       </c>
       <c r="R22">
-        <v>0.24</v>
+        <v>0.248</v>
       </c>
       <c r="S22" t="s">
         <v>43</v>
@@ -2871,7 +2871,7 @@
         <v>0.2142</v>
       </c>
       <c r="X22">
-        <v>0.2188</v>
+        <v>0.2199</v>
       </c>
       <c r="Y22">
         <v>0.9673</v>
@@ -2883,22 +2883,22 @@
         <v>44</v>
       </c>
       <c r="AD22">
-        <v>2.96</v>
+        <v>2.68</v>
       </c>
       <c r="AE22" t="s">
         <v>47</v>
       </c>
       <c r="AF22">
-        <v>0.1763</v>
+        <v>0.2019</v>
       </c>
       <c r="AG22">
-        <v>0.8536</v>
+        <v>0.8493</v>
       </c>
       <c r="AH22">
         <v>0</v>
       </c>
       <c r="AM22">
-        <v>2.96</v>
+        <v>2.68</v>
       </c>
     </row>
     <row r="23" spans="1:39" x14ac:dyDescent="0.25">
@@ -2906,7 +2906,7 @@
         <v>39</v>
       </c>
       <c r="B23" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C23">
         <v>5.5</v>
@@ -2918,16 +2918,16 @@
         <v>-110</v>
       </c>
       <c r="F23" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G23">
         <v>824718</v>
       </c>
       <c r="H23" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="I23">
-        <v>4.9</v>
+        <v>4.4</v>
       </c>
       <c r="J23" t="b">
         <v>0</v>
@@ -2939,22 +2939,22 @@
         <v>6</v>
       </c>
       <c r="M23">
-        <v>0.2188</v>
+        <v>0.2195</v>
       </c>
       <c r="N23">
         <v>5</v>
       </c>
       <c r="O23">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="P23">
-        <v>4.71</v>
+        <v>4.69</v>
       </c>
       <c r="Q23">
-        <v>0.2119</v>
+        <v>0.2277</v>
       </c>
       <c r="R23">
-        <v>0.371</v>
+        <v>0.336</v>
       </c>
       <c r="S23" t="s">
         <v>43</v>
@@ -2972,7 +2972,7 @@
         <v>0.2353</v>
       </c>
       <c r="X23">
-        <v>0.2188</v>
+        <v>0.2199</v>
       </c>
       <c r="Y23">
         <v>0.985</v>
@@ -2984,22 +2984,22 @@
         <v>44</v>
       </c>
       <c r="AD23">
-        <v>5.12</v>
+        <v>4.7</v>
       </c>
       <c r="AE23" t="s">
         <v>47</v>
       </c>
       <c r="AF23">
-        <v>0.2162</v>
+        <v>0.2223</v>
       </c>
       <c r="AG23">
-        <v>1.0515</v>
+        <v>1.0463</v>
       </c>
       <c r="AH23">
         <v>0</v>
       </c>
       <c r="AM23">
-        <v>5.12</v>
+        <v>4.7</v>
       </c>
     </row>
     <row r="24" spans="1:39" x14ac:dyDescent="0.25">
@@ -3007,7 +3007,7 @@
         <v>39</v>
       </c>
       <c r="B24" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C24">
         <v>3.5</v>
@@ -3019,7 +3019,7 @@
         <v>-115</v>
       </c>
       <c r="F24" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G24">
         <v>825044</v>
@@ -3073,7 +3073,7 @@
         <v>0.1988</v>
       </c>
       <c r="X24">
-        <v>0.2188</v>
+        <v>0.2199</v>
       </c>
       <c r="Y24">
         <v>0.88</v>
@@ -3085,7 +3085,7 @@
         <v>44</v>
       </c>
       <c r="AD24">
-        <v>2.69</v>
+        <v>2.67</v>
       </c>
       <c r="AE24" t="s">
         <v>47</v>
@@ -3094,13 +3094,13 @@
         <v>0.1807</v>
       </c>
       <c r="AG24">
-        <v>0.7632</v>
+        <v>0.7594</v>
       </c>
       <c r="AH24">
         <v>0</v>
       </c>
       <c r="AM24">
-        <v>2.69</v>
+        <v>2.67</v>
       </c>
     </row>
     <row r="25" spans="1:39" x14ac:dyDescent="0.25">
@@ -3108,7 +3108,7 @@
         <v>39</v>
       </c>
       <c r="B25" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C25">
         <v>5.5</v>
@@ -3120,7 +3120,7 @@
         <v>124</v>
       </c>
       <c r="F25" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G25">
         <v>825044</v>
@@ -3174,7 +3174,7 @@
         <v>0.2557</v>
       </c>
       <c r="X25">
-        <v>0.2188</v>
+        <v>0.2199</v>
       </c>
       <c r="Y25">
         <v>1.0455</v>
@@ -3186,7 +3186,7 @@
         <v>44</v>
       </c>
       <c r="AD25">
-        <v>6.87</v>
+        <v>6.84</v>
       </c>
       <c r="AE25" t="s">
         <v>54</v>
@@ -3195,13 +3195,13 @@
         <v>0.2337</v>
       </c>
       <c r="AG25">
-        <v>1.2753</v>
+        <v>1.269</v>
       </c>
       <c r="AH25">
         <v>0.17</v>
       </c>
       <c r="AM25">
-        <v>7.04</v>
+        <v>7.01</v>
       </c>
     </row>
     <row r="26" spans="1:39" x14ac:dyDescent="0.25">
@@ -3209,7 +3209,7 @@
         <v>39</v>
       </c>
       <c r="B26" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C26">
         <v>4.5</v>
@@ -3221,7 +3221,7 @@
         <v>-113</v>
       </c>
       <c r="F26" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="G26">
         <v>824316</v>
@@ -3275,7 +3275,7 @@
         <v>0.2178</v>
       </c>
       <c r="X26">
-        <v>0.2188</v>
+        <v>0.2199</v>
       </c>
       <c r="Y26">
         <v>0.9455</v>
@@ -3287,7 +3287,7 @@
         <v>44</v>
       </c>
       <c r="AD26">
-        <v>4.26</v>
+        <v>4.23</v>
       </c>
       <c r="AE26" t="s">
         <v>47</v>
@@ -3296,13 +3296,13 @@
         <v>0.1909</v>
       </c>
       <c r="AG26">
-        <v>1.0003</v>
+        <v>0.9954</v>
       </c>
       <c r="AH26">
         <v>0</v>
       </c>
       <c r="AM26">
-        <v>4.26</v>
+        <v>4.23</v>
       </c>
     </row>
     <row r="27" spans="1:39" x14ac:dyDescent="0.25">
@@ -3310,7 +3310,7 @@
         <v>39</v>
       </c>
       <c r="B27" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C27">
         <v>3.5</v>
@@ -3322,7 +3322,7 @@
         <v>-167</v>
       </c>
       <c r="F27" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="G27">
         <v>824316</v>
@@ -3376,7 +3376,7 @@
         <v>0.2137</v>
       </c>
       <c r="X27">
-        <v>0.2188</v>
+        <v>0.2199</v>
       </c>
       <c r="Y27">
         <v>0.88</v>
@@ -3388,7 +3388,7 @@
         <v>44</v>
       </c>
       <c r="AD27">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="AE27" t="s">
         <v>47</v>
@@ -3397,13 +3397,13 @@
         <v>0.1924</v>
       </c>
       <c r="AG27">
-        <v>0.7879</v>
+        <v>0.784</v>
       </c>
       <c r="AH27">
         <v>0</v>
       </c>
       <c r="AM27">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
     </row>
     <row r="28" spans="1:39" x14ac:dyDescent="0.25">
@@ -3411,7 +3411,7 @@
         <v>39</v>
       </c>
       <c r="B28" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C28">
         <v>4.5</v>
@@ -3423,7 +3423,7 @@
         <v>-128</v>
       </c>
       <c r="F28" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="G28">
         <v>823261</v>
@@ -3462,25 +3462,25 @@
         <v>0.363</v>
       </c>
       <c r="S28" t="s">
-        <v>89</v>
+        <v>43</v>
       </c>
       <c r="T28">
-        <v>0.1876</v>
+        <v>0.1929</v>
       </c>
       <c r="U28">
-        <v>0.1898</v>
+        <v>0.1923</v>
       </c>
       <c r="V28">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W28">
         <v>0.2166</v>
       </c>
       <c r="X28">
-        <v>0.2188</v>
+        <v>0.2199</v>
       </c>
       <c r="Y28">
-        <v>0.9947</v>
+        <v>0.9907</v>
       </c>
       <c r="AA28" t="s">
         <v>44</v>
@@ -3489,7 +3489,7 @@
         <v>44</v>
       </c>
       <c r="AD28">
-        <v>4.29</v>
+        <v>4.38</v>
       </c>
       <c r="AE28" t="s">
         <v>47</v>
@@ -3498,13 +3498,13 @@
         <v>0.232</v>
       </c>
       <c r="AG28">
-        <v>0.8574</v>
+        <v>0.8773</v>
       </c>
       <c r="AH28">
         <v>0</v>
       </c>
       <c r="AM28">
-        <v>4.29</v>
+        <v>4.38</v>
       </c>
     </row>
     <row r="29" spans="1:39" x14ac:dyDescent="0.25">
@@ -3524,7 +3524,7 @@
         <v>-102</v>
       </c>
       <c r="F29" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="G29">
         <v>823261</v>
@@ -3563,13 +3563,13 @@
         <v>0.342</v>
       </c>
       <c r="S29" t="s">
-        <v>89</v>
+        <v>43</v>
       </c>
       <c r="T29">
-        <v>0.1983</v>
+        <v>0.2065</v>
       </c>
       <c r="U29">
-        <v>0.1939</v>
+        <v>0.1967</v>
       </c>
       <c r="V29">
         <v>9</v>
@@ -3578,10 +3578,10 @@
         <v>0.2101</v>
       </c>
       <c r="X29">
-        <v>0.2188</v>
+        <v>0.2199</v>
       </c>
       <c r="Y29">
-        <v>0.9967</v>
+        <v>0.9951</v>
       </c>
       <c r="AA29" t="s">
         <v>44</v>
@@ -3590,7 +3590,7 @@
         <v>44</v>
       </c>
       <c r="AD29">
-        <v>4.12</v>
+        <v>4.26</v>
       </c>
       <c r="AE29" t="s">
         <v>47</v>
@@ -3599,13 +3599,13 @@
         <v>0.2124</v>
       </c>
       <c r="AG29">
-        <v>0.9066</v>
+        <v>0.9392</v>
       </c>
       <c r="AH29">
         <v>0</v>
       </c>
       <c r="AM29">
-        <v>4.12</v>
+        <v>4.26</v>
       </c>
     </row>
     <row r="30" spans="1:39" x14ac:dyDescent="0.25">

--- a/data/k-props/2026-08-22.xlsx
+++ b/data/k-props/2026-08-22.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="98">
   <si>
     <t>date</t>
   </si>
@@ -145,24 +145,33 @@
     <t>lineup_unweighted_30d_posted</t>
   </si>
   <si>
+    <t>U</t>
+  </si>
+  <si>
+    <t>L</t>
+  </si>
+  <si>
+    <t>&gt;=7</t>
+  </si>
+  <si>
+    <t>Ryan Weathers</t>
+  </si>
+  <si>
+    <t>W</t>
+  </si>
+  <si>
+    <t>&lt;6</t>
+  </si>
+  <si>
+    <t>Martín Pérez</t>
+  </si>
+  <si>
+    <t>Atlanta Braves @ Milwaukee Brewers</t>
+  </si>
+  <si>
     <t/>
   </si>
   <si>
-    <t>&gt;=7</t>
-  </si>
-  <si>
-    <t>Ryan Weathers</t>
-  </si>
-  <si>
-    <t>&lt;6</t>
-  </si>
-  <si>
-    <t>Martín Pérez</t>
-  </si>
-  <si>
-    <t>Atlanta Braves @ Milwaukee Brewers</t>
-  </si>
-  <si>
     <t>Logan Henderson</t>
   </si>
   <si>
@@ -170,6 +179,9 @@
   </si>
   <si>
     <t>Washington Nationals @ Miami Marlins</t>
+  </si>
+  <si>
+    <t>O</t>
   </si>
   <si>
     <t>Eury Pérez</t>
@@ -874,17 +886,23 @@
       <c r="Y2">
         <v>1.0348</v>
       </c>
+      <c r="Z2">
+        <v>8</v>
+      </c>
       <c r="AA2" t="s">
         <v>44</v>
       </c>
+      <c r="AB2">
+        <v>2.55</v>
+      </c>
       <c r="AC2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AD2">
         <v>11.05</v>
       </c>
       <c r="AE2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AF2">
         <v>0.3546</v>
@@ -894,6 +912,18 @@
       </c>
       <c r="AH2">
         <v>0</v>
+      </c>
+      <c r="AI2">
+        <v>-3.05</v>
+      </c>
+      <c r="AJ2">
+        <v>3.05</v>
+      </c>
+      <c r="AK2">
+        <v>-3.05</v>
+      </c>
+      <c r="AL2">
+        <v>3.05</v>
       </c>
       <c r="AM2">
         <v>11.05</v>
@@ -904,7 +934,7 @@
         <v>39</v>
       </c>
       <c r="B3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C3">
         <v>5.5</v>
@@ -975,17 +1005,23 @@
       <c r="Y3">
         <v>0.943</v>
       </c>
+      <c r="Z3">
+        <v>3</v>
+      </c>
       <c r="AA3" t="s">
         <v>44</v>
       </c>
+      <c r="AB3">
+        <v>-1.15</v>
+      </c>
       <c r="AC3" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="AD3">
         <v>4.35</v>
       </c>
       <c r="AE3" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="AF3">
         <v>0.2287</v>
@@ -995,6 +1031,18 @@
       </c>
       <c r="AH3">
         <v>0</v>
+      </c>
+      <c r="AI3">
+        <v>-1.35</v>
+      </c>
+      <c r="AJ3">
+        <v>1.35</v>
+      </c>
+      <c r="AK3">
+        <v>-1.35</v>
+      </c>
+      <c r="AL3">
+        <v>1.35</v>
       </c>
       <c r="AM3">
         <v>4.35</v>
@@ -1005,10 +1053,10 @@
         <v>39</v>
       </c>
       <c r="B4" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F4" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="G4">
         <v>823743</v>
@@ -1068,16 +1116,16 @@
         <v>0.9813</v>
       </c>
       <c r="AA4" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="AC4" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="AD4">
         <v>3.6</v>
       </c>
       <c r="AE4" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="AF4">
         <v>0.1715</v>
@@ -1097,7 +1145,7 @@
         <v>39</v>
       </c>
       <c r="B5" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="C5">
         <v>6.5</v>
@@ -1109,7 +1157,7 @@
         <v>-112</v>
       </c>
       <c r="F5" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="G5">
         <v>823743</v>
@@ -1168,17 +1216,23 @@
       <c r="Y5">
         <v>0.9745</v>
       </c>
+      <c r="Z5">
+        <v>4</v>
+      </c>
       <c r="AA5" t="s">
         <v>44</v>
       </c>
+      <c r="AB5">
+        <v>-0.65</v>
+      </c>
       <c r="AC5" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="AD5">
         <v>5.85</v>
       </c>
       <c r="AE5" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="AF5">
         <v>0.2907</v>
@@ -1188,6 +1242,18 @@
       </c>
       <c r="AH5">
         <v>0</v>
+      </c>
+      <c r="AI5">
+        <v>-1.85</v>
+      </c>
+      <c r="AJ5">
+        <v>1.85</v>
+      </c>
+      <c r="AK5">
+        <v>-1.85</v>
+      </c>
+      <c r="AL5">
+        <v>1.85</v>
       </c>
       <c r="AM5">
         <v>5.85</v>
@@ -1198,7 +1264,7 @@
         <v>39</v>
       </c>
       <c r="B6" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="C6">
         <v>2.5</v>
@@ -1210,7 +1276,7 @@
         <v>115</v>
       </c>
       <c r="F6" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="G6">
         <v>823831</v>
@@ -1269,17 +1335,23 @@
       <c r="Y6">
         <v>0.9201</v>
       </c>
+      <c r="Z6">
+        <v>4</v>
+      </c>
       <c r="AA6" t="s">
-        <v>44</v>
+        <v>56</v>
+      </c>
+      <c r="AB6">
+        <v>1.55</v>
       </c>
       <c r="AC6" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="AD6">
         <v>4.05</v>
       </c>
       <c r="AE6" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="AF6">
         <v>0.2021</v>
@@ -1289,6 +1361,18 @@
       </c>
       <c r="AH6">
         <v>0</v>
+      </c>
+      <c r="AI6">
+        <v>-0.05</v>
+      </c>
+      <c r="AJ6">
+        <v>0.05</v>
+      </c>
+      <c r="AK6">
+        <v>-0.05</v>
+      </c>
+      <c r="AL6">
+        <v>0.05</v>
       </c>
       <c r="AM6">
         <v>4.05</v>
@@ -1299,10 +1383,10 @@
         <v>39</v>
       </c>
       <c r="B7" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="F7" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="G7">
         <v>823831</v>
@@ -1362,16 +1446,16 @@
         <v>1.0251</v>
       </c>
       <c r="AA7" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="AC7" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="AD7">
         <v>6.81</v>
       </c>
       <c r="AE7" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="AF7">
         <v>0.2665</v>
@@ -1391,7 +1475,7 @@
         <v>39</v>
       </c>
       <c r="B8" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="C8">
         <v>3.5</v>
@@ -1403,7 +1487,7 @@
         <v>128</v>
       </c>
       <c r="F8" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="G8">
         <v>823422</v>
@@ -1462,17 +1546,23 @@
       <c r="Y8">
         <v>0.8933</v>
       </c>
+      <c r="Z8">
+        <v>8</v>
+      </c>
       <c r="AA8" t="s">
-        <v>44</v>
+        <v>56</v>
+      </c>
+      <c r="AB8">
+        <v>-0.05</v>
       </c>
       <c r="AC8" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="AD8">
         <v>3.45</v>
       </c>
       <c r="AE8" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="AF8">
         <v>0.2027</v>
@@ -1482,6 +1572,18 @@
       </c>
       <c r="AH8">
         <v>0</v>
+      </c>
+      <c r="AI8">
+        <v>4.55</v>
+      </c>
+      <c r="AJ8">
+        <v>4.55</v>
+      </c>
+      <c r="AK8">
+        <v>4.55</v>
+      </c>
+      <c r="AL8">
+        <v>4.55</v>
       </c>
       <c r="AM8">
         <v>3.45</v>
@@ -1492,7 +1594,7 @@
         <v>39</v>
       </c>
       <c r="B9" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="C9">
         <v>4.5</v>
@@ -1504,7 +1606,7 @@
         <v>-118</v>
       </c>
       <c r="F9" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="G9">
         <v>824798</v>
@@ -1563,17 +1665,23 @@
       <c r="Y9">
         <v>1.0352</v>
       </c>
+      <c r="Z9">
+        <v>5</v>
+      </c>
       <c r="AA9" t="s">
-        <v>44</v>
+        <v>56</v>
+      </c>
+      <c r="AB9">
+        <v>0.19</v>
       </c>
       <c r="AC9" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="AD9">
         <v>4.69</v>
       </c>
       <c r="AE9" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="AF9">
         <v>0.2072</v>
@@ -1583,6 +1691,18 @@
       </c>
       <c r="AH9">
         <v>0</v>
+      </c>
+      <c r="AI9">
+        <v>0.31</v>
+      </c>
+      <c r="AJ9">
+        <v>0.31</v>
+      </c>
+      <c r="AK9">
+        <v>0.31</v>
+      </c>
+      <c r="AL9">
+        <v>0.31</v>
       </c>
       <c r="AM9">
         <v>4.69</v>
@@ -1593,7 +1713,7 @@
         <v>39</v>
       </c>
       <c r="B10" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="C10">
         <v>3.5</v>
@@ -1605,7 +1725,7 @@
         <v>110</v>
       </c>
       <c r="F10" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="G10">
         <v>824798</v>
@@ -1664,17 +1784,23 @@
       <c r="Y10">
         <v>0.88</v>
       </c>
+      <c r="Z10">
+        <v>3</v>
+      </c>
       <c r="AA10" t="s">
         <v>44</v>
       </c>
+      <c r="AB10">
+        <v>-0.58</v>
+      </c>
       <c r="AC10" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="AD10">
         <v>2.92</v>
       </c>
       <c r="AE10" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="AF10">
         <v>0.1776</v>
@@ -1684,6 +1810,18 @@
       </c>
       <c r="AH10">
         <v>0</v>
+      </c>
+      <c r="AI10">
+        <v>0.08</v>
+      </c>
+      <c r="AJ10">
+        <v>0.08</v>
+      </c>
+      <c r="AK10">
+        <v>0.08</v>
+      </c>
+      <c r="AL10">
+        <v>0.08</v>
       </c>
       <c r="AM10">
         <v>2.92</v>
@@ -1694,7 +1832,7 @@
         <v>39</v>
       </c>
       <c r="B11" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="C11">
         <v>3.5</v>
@@ -1706,13 +1844,13 @@
         <v>129</v>
       </c>
       <c r="F11" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="G11">
         <v>822858</v>
       </c>
       <c r="H11" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="I11">
         <v>4.4</v>
@@ -1765,17 +1903,23 @@
       <c r="Y11">
         <v>1.0657</v>
       </c>
+      <c r="Z11">
+        <v>3</v>
+      </c>
       <c r="AA11" t="s">
         <v>44</v>
       </c>
+      <c r="AB11">
+        <v>0.66</v>
+      </c>
       <c r="AC11" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="AD11">
         <v>4.16</v>
       </c>
       <c r="AE11" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="AF11">
         <v>0.1638</v>
@@ -1785,6 +1929,18 @@
       </c>
       <c r="AH11">
         <v>0</v>
+      </c>
+      <c r="AI11">
+        <v>-1.16</v>
+      </c>
+      <c r="AJ11">
+        <v>1.16</v>
+      </c>
+      <c r="AK11">
+        <v>-1.16</v>
+      </c>
+      <c r="AL11">
+        <v>1.16</v>
       </c>
       <c r="AM11">
         <v>4.16</v>
@@ -1795,7 +1951,7 @@
         <v>39</v>
       </c>
       <c r="B12" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="C12">
         <v>4.5</v>
@@ -1807,13 +1963,13 @@
         <v>121</v>
       </c>
       <c r="F12" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="G12">
         <v>822858</v>
       </c>
       <c r="H12" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="I12">
         <v>4.3</v>
@@ -1866,17 +2022,23 @@
       <c r="Y12">
         <v>1.0991</v>
       </c>
+      <c r="Z12">
+        <v>3</v>
+      </c>
       <c r="AA12" t="s">
         <v>44</v>
       </c>
+      <c r="AB12">
+        <v>-0.37</v>
+      </c>
       <c r="AC12" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="AD12">
         <v>4.13</v>
       </c>
       <c r="AE12" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="AF12">
         <v>0.1507</v>
@@ -1886,6 +2048,18 @@
       </c>
       <c r="AH12">
         <v>0</v>
+      </c>
+      <c r="AI12">
+        <v>-1.13</v>
+      </c>
+      <c r="AJ12">
+        <v>1.13</v>
+      </c>
+      <c r="AK12">
+        <v>-1.13</v>
+      </c>
+      <c r="AL12">
+        <v>1.13</v>
       </c>
       <c r="AM12">
         <v>4.13</v>
@@ -1896,7 +2070,7 @@
         <v>39</v>
       </c>
       <c r="B13" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="C13">
         <v>4.5</v>
@@ -1908,13 +2082,13 @@
         <v>105</v>
       </c>
       <c r="F13" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="G13">
         <v>824151</v>
       </c>
       <c r="H13" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="I13">
         <v>4.5</v>
@@ -1967,17 +2141,23 @@
       <c r="Y13">
         <v>0.9272</v>
       </c>
+      <c r="Z13">
+        <v>9</v>
+      </c>
       <c r="AA13" t="s">
-        <v>44</v>
+        <v>56</v>
+      </c>
+      <c r="AB13">
+        <v>-0.5</v>
       </c>
       <c r="AC13" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="AD13">
         <v>4</v>
       </c>
       <c r="AE13" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="AF13">
         <v>0.2386</v>
@@ -1987,6 +2167,18 @@
       </c>
       <c r="AH13">
         <v>0</v>
+      </c>
+      <c r="AI13">
+        <v>5</v>
+      </c>
+      <c r="AJ13">
+        <v>5</v>
+      </c>
+      <c r="AK13">
+        <v>5</v>
+      </c>
+      <c r="AL13">
+        <v>5</v>
       </c>
       <c r="AM13">
         <v>4</v>
@@ -1997,7 +2189,7 @@
         <v>39</v>
       </c>
       <c r="B14" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="C14">
         <v>5.5</v>
@@ -2009,7 +2201,7 @@
         <v>111</v>
       </c>
       <c r="F14" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="G14">
         <v>824151</v>
@@ -2068,17 +2260,23 @@
       <c r="Y14">
         <v>1.0455</v>
       </c>
+      <c r="Z14">
+        <v>4</v>
+      </c>
       <c r="AA14" t="s">
         <v>44</v>
       </c>
+      <c r="AB14">
+        <v>-0.84</v>
+      </c>
       <c r="AC14" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="AD14">
         <v>4.66</v>
       </c>
       <c r="AE14" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="AF14">
         <v>0.2384</v>
@@ -2088,6 +2286,18 @@
       </c>
       <c r="AH14">
         <v>0</v>
+      </c>
+      <c r="AI14">
+        <v>-0.66</v>
+      </c>
+      <c r="AJ14">
+        <v>0.66</v>
+      </c>
+      <c r="AK14">
+        <v>-0.66</v>
+      </c>
+      <c r="AL14">
+        <v>0.66</v>
       </c>
       <c r="AM14">
         <v>4.66</v>
@@ -2098,7 +2308,7 @@
         <v>39</v>
       </c>
       <c r="B15" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="C15">
         <v>5.5</v>
@@ -2110,7 +2320,7 @@
         <v>126</v>
       </c>
       <c r="F15" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="G15">
         <v>824560</v>
@@ -2169,17 +2379,23 @@
       <c r="Y15">
         <v>1.0743</v>
       </c>
+      <c r="Z15">
+        <v>6</v>
+      </c>
       <c r="AA15" t="s">
-        <v>44</v>
+        <v>56</v>
+      </c>
+      <c r="AB15">
+        <v>1.12</v>
       </c>
       <c r="AC15" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="AD15">
         <v>6.45</v>
       </c>
       <c r="AE15" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="AF15">
         <v>0.2853</v>
@@ -2189,6 +2405,18 @@
       </c>
       <c r="AH15">
         <v>0.17</v>
+      </c>
+      <c r="AI15">
+        <v>-0.45</v>
+      </c>
+      <c r="AJ15">
+        <v>0.45</v>
+      </c>
+      <c r="AK15">
+        <v>-0.62</v>
+      </c>
+      <c r="AL15">
+        <v>0.62</v>
       </c>
       <c r="AM15">
         <v>6.62</v>
@@ -2199,7 +2427,7 @@
         <v>39</v>
       </c>
       <c r="B16" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="C16">
         <v>4.5</v>
@@ -2211,7 +2439,7 @@
         <v>100</v>
       </c>
       <c r="F16" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="G16">
         <v>824560</v>
@@ -2270,17 +2498,23 @@
       <c r="Y16">
         <v>0.9809</v>
       </c>
+      <c r="Z16">
+        <v>3</v>
+      </c>
       <c r="AA16" t="s">
         <v>44</v>
       </c>
+      <c r="AB16">
+        <v>0.67</v>
+      </c>
       <c r="AC16" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="AD16">
         <v>5.17</v>
       </c>
       <c r="AE16" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="AF16">
         <v>0.2072</v>
@@ -2290,6 +2524,18 @@
       </c>
       <c r="AH16">
         <v>0</v>
+      </c>
+      <c r="AI16">
+        <v>-2.17</v>
+      </c>
+      <c r="AJ16">
+        <v>2.17</v>
+      </c>
+      <c r="AK16">
+        <v>-2.17</v>
+      </c>
+      <c r="AL16">
+        <v>2.17</v>
       </c>
       <c r="AM16">
         <v>5.17</v>
@@ -2300,7 +2546,7 @@
         <v>39</v>
       </c>
       <c r="B17" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="C17">
         <v>4.5</v>
@@ -2312,13 +2558,13 @@
         <v>-160</v>
       </c>
       <c r="F17" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="G17">
         <v>824073</v>
       </c>
       <c r="H17" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="I17">
         <v>3</v>
@@ -2371,17 +2617,23 @@
       <c r="Y17">
         <v>0.8912</v>
       </c>
+      <c r="Z17">
+        <v>4</v>
+      </c>
       <c r="AA17" t="s">
         <v>44</v>
       </c>
+      <c r="AB17">
+        <v>-2.04</v>
+      </c>
       <c r="AC17" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="AD17">
         <v>2.46</v>
       </c>
       <c r="AE17" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="AF17">
         <v>0.2553</v>
@@ -2391,6 +2643,18 @@
       </c>
       <c r="AH17">
         <v>0</v>
+      </c>
+      <c r="AI17">
+        <v>1.54</v>
+      </c>
+      <c r="AJ17">
+        <v>1.54</v>
+      </c>
+      <c r="AK17">
+        <v>1.54</v>
+      </c>
+      <c r="AL17">
+        <v>1.54</v>
       </c>
       <c r="AM17">
         <v>2.46</v>
@@ -2401,7 +2665,7 @@
         <v>39</v>
       </c>
       <c r="B18" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="C18">
         <v>4.5</v>
@@ -2413,7 +2677,7 @@
         <v>-151</v>
       </c>
       <c r="F18" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="G18">
         <v>824073</v>
@@ -2472,17 +2736,23 @@
       <c r="Y18">
         <v>0.9419</v>
       </c>
+      <c r="Z18">
+        <v>6</v>
+      </c>
       <c r="AA18" t="s">
-        <v>44</v>
+        <v>56</v>
+      </c>
+      <c r="AB18">
+        <v>-0.98</v>
       </c>
       <c r="AC18" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AD18">
         <v>3.52</v>
       </c>
       <c r="AE18" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="AF18">
         <v>0.1795</v>
@@ -2492,6 +2762,18 @@
       </c>
       <c r="AH18">
         <v>0</v>
+      </c>
+      <c r="AI18">
+        <v>2.48</v>
+      </c>
+      <c r="AJ18">
+        <v>2.48</v>
+      </c>
+      <c r="AK18">
+        <v>2.48</v>
+      </c>
+      <c r="AL18">
+        <v>2.48</v>
       </c>
       <c r="AM18">
         <v>3.52</v>
@@ -2502,7 +2784,7 @@
         <v>39</v>
       </c>
       <c r="B19" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="C19">
         <v>4.5</v>
@@ -2514,13 +2796,13 @@
         <v>118</v>
       </c>
       <c r="F19" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="G19">
         <v>823910</v>
       </c>
       <c r="H19" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="I19">
         <v>4.3</v>
@@ -2573,17 +2855,23 @@
       <c r="Y19">
         <v>0.994</v>
       </c>
+      <c r="Z19">
+        <v>5</v>
+      </c>
       <c r="AA19" t="s">
-        <v>44</v>
+        <v>56</v>
+      </c>
+      <c r="AB19">
+        <v>0.24</v>
       </c>
       <c r="AC19" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="AD19">
         <v>4.74</v>
       </c>
       <c r="AE19" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="AF19">
         <v>0.2618</v>
@@ -2593,6 +2881,18 @@
       </c>
       <c r="AH19">
         <v>0</v>
+      </c>
+      <c r="AI19">
+        <v>0.26</v>
+      </c>
+      <c r="AJ19">
+        <v>0.26</v>
+      </c>
+      <c r="AK19">
+        <v>0.26</v>
+      </c>
+      <c r="AL19">
+        <v>0.26</v>
       </c>
       <c r="AM19">
         <v>4.74</v>
@@ -2603,7 +2903,7 @@
         <v>39</v>
       </c>
       <c r="B20" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="C20">
         <v>8.5</v>
@@ -2615,7 +2915,7 @@
         <v>-126</v>
       </c>
       <c r="F20" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="G20">
         <v>823910</v>
@@ -2674,17 +2974,23 @@
       <c r="Y20">
         <v>1.1003</v>
       </c>
+      <c r="Z20">
+        <v>11</v>
+      </c>
       <c r="AA20" t="s">
-        <v>44</v>
+        <v>56</v>
+      </c>
+      <c r="AB20">
+        <v>-0.67</v>
       </c>
       <c r="AC20" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="AD20">
         <v>7.83</v>
       </c>
       <c r="AE20" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AF20">
         <v>0.2787</v>
@@ -2694,6 +3000,18 @@
       </c>
       <c r="AH20">
         <v>0</v>
+      </c>
+      <c r="AI20">
+        <v>3.17</v>
+      </c>
+      <c r="AJ20">
+        <v>3.17</v>
+      </c>
+      <c r="AK20">
+        <v>3.17</v>
+      </c>
+      <c r="AL20">
+        <v>3.17</v>
       </c>
       <c r="AM20">
         <v>7.83</v>
@@ -2704,7 +3022,7 @@
         <v>39</v>
       </c>
       <c r="B21" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="C21">
         <v>4.5</v>
@@ -2716,7 +3034,7 @@
         <v>-133</v>
       </c>
       <c r="F21" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="G21">
         <v>823100</v>
@@ -2775,17 +3093,23 @@
       <c r="Y21">
         <v>0.9735</v>
       </c>
+      <c r="Z21">
+        <v>8</v>
+      </c>
       <c r="AA21" t="s">
-        <v>44</v>
+        <v>56</v>
+      </c>
+      <c r="AB21">
+        <v>-0.36</v>
       </c>
       <c r="AC21" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="AD21">
         <v>4.14</v>
       </c>
       <c r="AE21" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="AF21">
         <v>0.1992</v>
@@ -2795,6 +3119,18 @@
       </c>
       <c r="AH21">
         <v>0</v>
+      </c>
+      <c r="AI21">
+        <v>3.86</v>
+      </c>
+      <c r="AJ21">
+        <v>3.86</v>
+      </c>
+      <c r="AK21">
+        <v>3.86</v>
+      </c>
+      <c r="AL21">
+        <v>3.86</v>
       </c>
       <c r="AM21">
         <v>4.14</v>
@@ -2805,7 +3141,7 @@
         <v>39</v>
       </c>
       <c r="B22" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="C22">
         <v>3.5</v>
@@ -2817,13 +3153,13 @@
         <v>-105</v>
       </c>
       <c r="F22" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="G22">
         <v>824718</v>
       </c>
       <c r="H22" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="I22">
         <v>4</v>
@@ -2876,17 +3212,23 @@
       <c r="Y22">
         <v>0.9673</v>
       </c>
+      <c r="Z22">
+        <v>7</v>
+      </c>
       <c r="AA22" t="s">
-        <v>44</v>
+        <v>56</v>
+      </c>
+      <c r="AB22">
+        <v>-0.82</v>
       </c>
       <c r="AC22" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AD22">
         <v>2.68</v>
       </c>
       <c r="AE22" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="AF22">
         <v>0.2019</v>
@@ -2896,6 +3238,18 @@
       </c>
       <c r="AH22">
         <v>0</v>
+      </c>
+      <c r="AI22">
+        <v>4.32</v>
+      </c>
+      <c r="AJ22">
+        <v>4.32</v>
+      </c>
+      <c r="AK22">
+        <v>4.32</v>
+      </c>
+      <c r="AL22">
+        <v>4.32</v>
       </c>
       <c r="AM22">
         <v>2.68</v>
@@ -2906,7 +3260,7 @@
         <v>39</v>
       </c>
       <c r="B23" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="C23">
         <v>5.5</v>
@@ -2918,13 +3272,13 @@
         <v>-110</v>
       </c>
       <c r="F23" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="G23">
         <v>824718</v>
       </c>
       <c r="H23" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="I23">
         <v>4.4</v>
@@ -2977,17 +3331,23 @@
       <c r="Y23">
         <v>0.985</v>
       </c>
+      <c r="Z23">
+        <v>6</v>
+      </c>
       <c r="AA23" t="s">
-        <v>44</v>
+        <v>56</v>
+      </c>
+      <c r="AB23">
+        <v>-0.8</v>
       </c>
       <c r="AC23" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AD23">
         <v>4.7</v>
       </c>
       <c r="AE23" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="AF23">
         <v>0.2223</v>
@@ -2997,6 +3357,18 @@
       </c>
       <c r="AH23">
         <v>0</v>
+      </c>
+      <c r="AI23">
+        <v>1.3</v>
+      </c>
+      <c r="AJ23">
+        <v>1.3</v>
+      </c>
+      <c r="AK23">
+        <v>1.3</v>
+      </c>
+      <c r="AL23">
+        <v>1.3</v>
       </c>
       <c r="AM23">
         <v>4.7</v>
@@ -3007,7 +3379,7 @@
         <v>39</v>
       </c>
       <c r="B24" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="C24">
         <v>3.5</v>
@@ -3019,7 +3391,7 @@
         <v>-115</v>
       </c>
       <c r="F24" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="G24">
         <v>825044</v>
@@ -3078,17 +3450,23 @@
       <c r="Y24">
         <v>0.88</v>
       </c>
+      <c r="Z24">
+        <v>1</v>
+      </c>
       <c r="AA24" t="s">
         <v>44</v>
       </c>
+      <c r="AB24">
+        <v>-0.83</v>
+      </c>
       <c r="AC24" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="AD24">
         <v>2.67</v>
       </c>
       <c r="AE24" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="AF24">
         <v>0.1807</v>
@@ -3098,6 +3476,18 @@
       </c>
       <c r="AH24">
         <v>0</v>
+      </c>
+      <c r="AI24">
+        <v>-1.67</v>
+      </c>
+      <c r="AJ24">
+        <v>1.67</v>
+      </c>
+      <c r="AK24">
+        <v>-1.67</v>
+      </c>
+      <c r="AL24">
+        <v>1.67</v>
       </c>
       <c r="AM24">
         <v>2.67</v>
@@ -3108,7 +3498,7 @@
         <v>39</v>
       </c>
       <c r="B25" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="C25">
         <v>5.5</v>
@@ -3120,7 +3510,7 @@
         <v>124</v>
       </c>
       <c r="F25" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="G25">
         <v>825044</v>
@@ -3179,17 +3569,23 @@
       <c r="Y25">
         <v>1.0455</v>
       </c>
+      <c r="Z25">
+        <v>3</v>
+      </c>
       <c r="AA25" t="s">
         <v>44</v>
       </c>
+      <c r="AB25">
+        <v>1.51</v>
+      </c>
       <c r="AC25" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AD25">
         <v>6.84</v>
       </c>
       <c r="AE25" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="AF25">
         <v>0.2337</v>
@@ -3199,6 +3595,18 @@
       </c>
       <c r="AH25">
         <v>0.17</v>
+      </c>
+      <c r="AI25">
+        <v>-3.84</v>
+      </c>
+      <c r="AJ25">
+        <v>3.84</v>
+      </c>
+      <c r="AK25">
+        <v>-4.01</v>
+      </c>
+      <c r="AL25">
+        <v>4.01</v>
       </c>
       <c r="AM25">
         <v>7.01</v>
@@ -3209,7 +3617,7 @@
         <v>39</v>
       </c>
       <c r="B26" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="C26">
         <v>4.5</v>
@@ -3221,7 +3629,7 @@
         <v>-113</v>
       </c>
       <c r="F26" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="G26">
         <v>824316</v>
@@ -3280,17 +3688,23 @@
       <c r="Y26">
         <v>0.9455</v>
       </c>
+      <c r="Z26">
+        <v>6</v>
+      </c>
       <c r="AA26" t="s">
-        <v>44</v>
+        <v>56</v>
+      </c>
+      <c r="AB26">
+        <v>-0.27</v>
       </c>
       <c r="AC26" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="AD26">
         <v>4.23</v>
       </c>
       <c r="AE26" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="AF26">
         <v>0.1909</v>
@@ -3300,6 +3714,18 @@
       </c>
       <c r="AH26">
         <v>0</v>
+      </c>
+      <c r="AI26">
+        <v>1.77</v>
+      </c>
+      <c r="AJ26">
+        <v>1.77</v>
+      </c>
+      <c r="AK26">
+        <v>1.77</v>
+      </c>
+      <c r="AL26">
+        <v>1.77</v>
       </c>
       <c r="AM26">
         <v>4.23</v>
@@ -3310,7 +3736,7 @@
         <v>39</v>
       </c>
       <c r="B27" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="C27">
         <v>3.5</v>
@@ -3322,7 +3748,7 @@
         <v>-167</v>
       </c>
       <c r="F27" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="G27">
         <v>824316</v>
@@ -3381,17 +3807,23 @@
       <c r="Y27">
         <v>0.88</v>
       </c>
+      <c r="Z27">
+        <v>2</v>
+      </c>
       <c r="AA27" t="s">
         <v>44</v>
       </c>
+      <c r="AB27">
+        <v>-0.64</v>
+      </c>
       <c r="AC27" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="AD27">
         <v>2.86</v>
       </c>
       <c r="AE27" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="AF27">
         <v>0.1924</v>
@@ -3401,6 +3833,18 @@
       </c>
       <c r="AH27">
         <v>0</v>
+      </c>
+      <c r="AI27">
+        <v>-0.86</v>
+      </c>
+      <c r="AJ27">
+        <v>0.86</v>
+      </c>
+      <c r="AK27">
+        <v>-0.86</v>
+      </c>
+      <c r="AL27">
+        <v>0.86</v>
       </c>
       <c r="AM27">
         <v>2.86</v>
@@ -3411,7 +3855,7 @@
         <v>39</v>
       </c>
       <c r="B28" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="C28">
         <v>4.5</v>
@@ -3423,7 +3867,7 @@
         <v>-128</v>
       </c>
       <c r="F28" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="G28">
         <v>823261</v>
@@ -3482,17 +3926,23 @@
       <c r="Y28">
         <v>0.9907</v>
       </c>
+      <c r="Z28">
+        <v>5</v>
+      </c>
       <c r="AA28" t="s">
-        <v>44</v>
+        <v>56</v>
+      </c>
+      <c r="AB28">
+        <v>-0.12</v>
       </c>
       <c r="AC28" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="AD28">
         <v>4.38</v>
       </c>
       <c r="AE28" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="AF28">
         <v>0.232</v>
@@ -3502,6 +3952,18 @@
       </c>
       <c r="AH28">
         <v>0</v>
+      </c>
+      <c r="AI28">
+        <v>0.62</v>
+      </c>
+      <c r="AJ28">
+        <v>0.62</v>
+      </c>
+      <c r="AK28">
+        <v>0.62</v>
+      </c>
+      <c r="AL28">
+        <v>0.62</v>
       </c>
       <c r="AM28">
         <v>4.38</v>
@@ -3512,7 +3974,7 @@
         <v>39</v>
       </c>
       <c r="B29" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="C29">
         <v>4.5</v>
@@ -3524,7 +3986,7 @@
         <v>-102</v>
       </c>
       <c r="F29" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="G29">
         <v>823261</v>
@@ -3583,17 +4045,23 @@
       <c r="Y29">
         <v>0.9951</v>
       </c>
+      <c r="Z29">
+        <v>0</v>
+      </c>
       <c r="AA29" t="s">
         <v>44</v>
       </c>
+      <c r="AB29">
+        <v>-0.24</v>
+      </c>
       <c r="AC29" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="AD29">
         <v>4.26</v>
       </c>
       <c r="AE29" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="AF29">
         <v>0.2124</v>
@@ -3603,6 +4071,18 @@
       </c>
       <c r="AH29">
         <v>0</v>
+      </c>
+      <c r="AI29">
+        <v>-4.26</v>
+      </c>
+      <c r="AJ29">
+        <v>4.26</v>
+      </c>
+      <c r="AK29">
+        <v>-4.26</v>
+      </c>
+      <c r="AL29">
+        <v>4.26</v>
       </c>
       <c r="AM29">
         <v>4.26</v>
@@ -3613,7 +4093,7 @@
         <v>39</v>
       </c>
       <c r="B30" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="C30">
         <v>5.5</v>
@@ -3625,31 +4105,31 @@
         <v>130</v>
       </c>
       <c r="F30" t="s">
+        <v>55</v>
+      </c>
+      <c r="G30" t="s">
         <v>52</v>
       </c>
-      <c r="G30" t="s">
-        <v>44</v>
-      </c>
       <c r="H30" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="L30">
         <v>1</v>
       </c>
       <c r="S30" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="V30" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="AA30" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="AC30" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="AE30" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
     </row>
     <row r="31" spans="1:39" x14ac:dyDescent="0.25">
@@ -3657,7 +4137,7 @@
         <v>39</v>
       </c>
       <c r="B31" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="C31">
         <v>4.5</v>
@@ -3669,31 +4149,31 @@
         <v>104</v>
       </c>
       <c r="F31" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="G31" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="H31" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="L31">
         <v>6</v>
       </c>
       <c r="S31" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="V31" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="AA31" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="AC31" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="AE31" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
     </row>
     <row r="32" spans="1:39" x14ac:dyDescent="0.25">
@@ -3701,7 +4181,7 @@
         <v>39</v>
       </c>
       <c r="B32" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="C32">
         <v>3.5</v>
@@ -3713,31 +4193,31 @@
         <v>-110</v>
       </c>
       <c r="F32" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="G32" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="H32" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="L32">
         <v>6</v>
       </c>
       <c r="S32" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="V32" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="AA32" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="AC32" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="AE32" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
     </row>
   </sheetData>
